--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1020" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="626">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -228,12 +228,6 @@
   </si>
   <si>
     <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XUBOTTOMDELAY", "instance": "XUBOTTOMDELAY", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE</t>
-  </si>
-  <si>
-    <t>OKREF03249 - {"path": "XWALTZ,XceleraCORE,XceleraSERVICE", "instance": "XceleraSERVICE", "symbol": "enable_ibias", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
@@ -434,12 +428,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog11/CELERAservice.v:166: error: port ``celkelvin_CELG'' is not a port of Xreference.
-1 error(s) during elaboration.
-</t>
-  </si>
-  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -464,6 +452,9 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
   </si>
   <si>
@@ -485,6 +476,9 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
     <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
@@ -503,6 +497,9 @@
     <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
   </si>
   <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
   </si>
   <si>
@@ -521,16 +518,13 @@
     <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
+    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -1337,6 +1331,12 @@
     <t>DFTtm8t</t>
   </si>
   <si>
+    <t>dft_hex0x1A</t>
+  </si>
+  <si>
+    <t>0x1A</t>
+  </si>
+  <si>
     <t>dft_hex0x03</t>
   </si>
   <si>
@@ -1367,6 +1367,12 @@
     <t>dft_hex0x08</t>
   </si>
   <si>
+    <t>dft_hex0x1B</t>
+  </si>
+  <si>
+    <t>0x1B</t>
+  </si>
+  <si>
     <t>dft_hex0x09</t>
   </si>
   <si>
@@ -1382,6 +1388,15 @@
     <t>dft_hex0x0C</t>
   </si>
   <si>
+    <t>dft_hex0x1C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1D</t>
+  </si>
+  <si>
+    <t>0x1D</t>
+  </si>
+  <si>
     <t>dft_hex0x0D</t>
   </si>
   <si>
@@ -1397,12 +1412,21 @@
     <t>dft_hex0x0F</t>
   </si>
   <si>
+    <t>dft_hex0x1E</t>
+  </si>
+  <si>
+    <t>0x1E</t>
+  </si>
+  <si>
     <t>dft_hex0x10</t>
   </si>
   <si>
     <t>dft_hex0x11</t>
   </si>
   <si>
+    <t>dft_hex0x1F</t>
+  </si>
+  <si>
     <t>dft_hex0x12</t>
   </si>
   <si>
@@ -1424,6 +1448,12 @@
     <t>dft_hex0x18</t>
   </si>
   <si>
+    <t>dft_hex0x20</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
     <t>dft_hex0x19</t>
   </si>
   <si>
@@ -1451,18 +1481,18 @@
     <t>193</t>
   </si>
   <si>
+    <t>noconn</t>
+  </si>
+  <si>
+    <t>155</t>
+  </si>
+  <si>
     <t>nand2</t>
   </si>
   <si>
     <t>148</t>
   </si>
   <si>
-    <t>noconn</t>
-  </si>
-  <si>
-    <t>131</t>
-  </si>
-  <si>
     <t>dbuf</t>
   </si>
   <si>
@@ -1508,7 +1538,7 @@
     <t>dftmodule</t>
   </si>
   <si>
-    <t>25</t>
+    <t>32</t>
   </si>
   <si>
     <t>dfthijack</t>
@@ -1572,6 +1602,9 @@
   </si>
   <si>
     <t>amux2</t>
+  </si>
+  <si>
+    <t>wrapper</t>
   </si>
   <si>
     <t>vbuffer</t>
@@ -2294,7 +2327,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2359,82 +2392,72 @@
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>41</v>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2449,7 +2472,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2469,7 +2492,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2484,7 +2507,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -2499,17 +2522,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2524,12 +2547,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2544,17 +2567,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -2569,12 +2592,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -2589,7 +2612,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2604,157 +2627,152 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2769,7 +2787,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2999,17 +3017,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -3019,222 +3037,257 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A61"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="1" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="1" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>136</v>
+      <c r="A29" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
         <v>135</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>142</v>
+      <c r="A48" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
-        <v>143</v>
+      <c r="A51" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" s="1" t="s">
-        <v>145</v>
+      <c r="A55" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
-        <v>79</v>
+      <c r="A58" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="1" t="s">
         <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -3249,17 +3302,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -3274,52 +3327,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -3334,81 +3387,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" t="s">
         <v>162</v>
-      </c>
-      <c r="B5" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" t="s">
         <v>164</v>
-      </c>
-      <c r="B6" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>167</v>
+      </c>
+      <c r="B9" t="s">
         <v>168</v>
-      </c>
-      <c r="B9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>169</v>
+      </c>
+      <c r="B10" t="s">
         <v>170</v>
-      </c>
-      <c r="B10" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3416,1268 +3469,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B20" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B27" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" t="s">
         <v>187</v>
-      </c>
-      <c r="B29" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
+        <v>190</v>
+      </c>
+      <c r="B32" t="s">
         <v>191</v>
-      </c>
-      <c r="B32" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>192</v>
+      </c>
+      <c r="B33" t="s">
         <v>193</v>
-      </c>
-      <c r="B33" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" t="s">
         <v>195</v>
-      </c>
-      <c r="B34" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" t="s">
         <v>197</v>
-      </c>
-      <c r="B35" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" t="s">
         <v>199</v>
-      </c>
-      <c r="B36" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" t="s">
         <v>203</v>
-      </c>
-      <c r="B39" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>207</v>
+      </c>
+      <c r="B43" t="s">
         <v>208</v>
-      </c>
-      <c r="B43" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" t="s">
         <v>211</v>
-      </c>
-      <c r="B46" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B49" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B50" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B51" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
+        <v>217</v>
+      </c>
+      <c r="B52" t="s">
         <v>218</v>
-      </c>
-      <c r="B52" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>220</v>
+      </c>
+      <c r="B55" t="s">
         <v>221</v>
-      </c>
-      <c r="B55" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
+        <v>222</v>
+      </c>
+      <c r="B56" t="s">
         <v>223</v>
-      </c>
-      <c r="B56" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
+        <v>230</v>
+      </c>
+      <c r="B64" t="s">
         <v>231</v>
-      </c>
-      <c r="B64" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>234</v>
+      </c>
+      <c r="B67" t="s">
         <v>235</v>
-      </c>
-      <c r="B67" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
+        <v>236</v>
+      </c>
+      <c r="B68" t="s">
         <v>237</v>
-      </c>
-      <c r="B68" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B69" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B70" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B77" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B78" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B79" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>248</v>
+      </c>
+      <c r="B80" t="s">
         <v>249</v>
-      </c>
-      <c r="B80" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" t="s">
         <v>251</v>
-      </c>
-      <c r="B81" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B82" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B88" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B89" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
+        <v>260</v>
+      </c>
+      <c r="B90" t="s">
         <v>261</v>
-      </c>
-      <c r="B90" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B92" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B93" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B94" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B95" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B97" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B98" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B99" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B100" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
+        <v>272</v>
+      </c>
+      <c r="B101" t="s">
         <v>273</v>
-      </c>
-      <c r="B101" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B102" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B103" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>277</v>
+      </c>
+      <c r="B106" t="s">
         <v>278</v>
-      </c>
-      <c r="B106" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>279</v>
+      </c>
+      <c r="B107" t="s">
         <v>280</v>
-      </c>
-      <c r="B107" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>281</v>
+      </c>
+      <c r="B108" t="s">
         <v>282</v>
-      </c>
-      <c r="B108" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>283</v>
+      </c>
+      <c r="B109" t="s">
         <v>284</v>
-      </c>
-      <c r="B109" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>285</v>
+      </c>
+      <c r="B110" t="s">
         <v>286</v>
-      </c>
-      <c r="B110" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>287</v>
+      </c>
+      <c r="B111" t="s">
         <v>288</v>
-      </c>
-      <c r="B111" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
+        <v>289</v>
+      </c>
+      <c r="B112" t="s">
         <v>290</v>
-      </c>
-      <c r="B112" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B113" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>160</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B116" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>294</v>
+      </c>
+      <c r="B117" t="s">
         <v>295</v>
-      </c>
-      <c r="B117" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>296</v>
+      </c>
+      <c r="B118" t="s">
         <v>297</v>
-      </c>
-      <c r="B118" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>298</v>
+      </c>
+      <c r="B119" t="s">
         <v>299</v>
-      </c>
-      <c r="B119" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>300</v>
+      </c>
+      <c r="B120" t="s">
         <v>301</v>
-      </c>
-      <c r="B120" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>302</v>
+      </c>
+      <c r="B121" t="s">
         <v>303</v>
-      </c>
-      <c r="B121" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
+        <v>304</v>
+      </c>
+      <c r="B122" t="s">
         <v>305</v>
-      </c>
-      <c r="B122" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B123" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B124" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B125" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>309</v>
+      </c>
+      <c r="B126" t="s">
         <v>310</v>
-      </c>
-      <c r="B126" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>311</v>
+      </c>
+      <c r="B127" t="s">
         <v>312</v>
-      </c>
-      <c r="B127" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>313</v>
+      </c>
+      <c r="B128" t="s">
         <v>314</v>
-      </c>
-      <c r="B128" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>315</v>
+      </c>
+      <c r="B129" t="s">
         <v>316</v>
-      </c>
-      <c r="B129" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
+        <v>317</v>
+      </c>
+      <c r="B130" t="s">
         <v>318</v>
-      </c>
-      <c r="B130" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B131" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B132" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B133" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B134" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B135" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>324</v>
+      </c>
+      <c r="B136" t="s">
         <v>325</v>
-      </c>
-      <c r="B136" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>326</v>
+      </c>
+      <c r="B137" t="s">
         <v>327</v>
-      </c>
-      <c r="B137" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>328</v>
+      </c>
+      <c r="B138" t="s">
         <v>329</v>
-      </c>
-      <c r="B138" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>330</v>
+      </c>
+      <c r="B139" t="s">
         <v>331</v>
-      </c>
-      <c r="B139" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
+        <v>332</v>
+      </c>
+      <c r="B140" t="s">
         <v>333</v>
-      </c>
-      <c r="B140" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B141" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B142" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B143" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B144" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B145" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B146" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B147" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B148" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>342</v>
+      </c>
+      <c r="B149" t="s">
         <v>343</v>
-      </c>
-      <c r="B149" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>344</v>
+      </c>
+      <c r="B150" t="s">
         <v>345</v>
-      </c>
-      <c r="B150" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>346</v>
+      </c>
+      <c r="B151" t="s">
         <v>347</v>
-      </c>
-      <c r="B151" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>348</v>
+      </c>
+      <c r="B152" t="s">
         <v>349</v>
-      </c>
-      <c r="B152" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>350</v>
+      </c>
+      <c r="B153" t="s">
         <v>351</v>
-      </c>
-      <c r="B153" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>352</v>
+      </c>
+      <c r="B154" t="s">
         <v>353</v>
-      </c>
-      <c r="B154" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>354</v>
+      </c>
+      <c r="B155" t="s">
         <v>355</v>
-      </c>
-      <c r="B155" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>356</v>
+      </c>
+      <c r="B156" t="s">
         <v>357</v>
-      </c>
-      <c r="B156" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>358</v>
+      </c>
+      <c r="B157" t="s">
         <v>359</v>
-      </c>
-      <c r="B157" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>360</v>
+      </c>
+      <c r="B158" t="s">
         <v>361</v>
-      </c>
-      <c r="B158" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>362</v>
+      </c>
+      <c r="B159" t="s">
         <v>363</v>
-      </c>
-      <c r="B159" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>364</v>
+      </c>
+      <c r="B160" t="s">
         <v>365</v>
-      </c>
-      <c r="B160" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>366</v>
+      </c>
+      <c r="B161" t="s">
         <v>367</v>
-      </c>
-      <c r="B161" t="s">
-        <v>368</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>368</v>
+      </c>
+      <c r="B162" t="s">
         <v>369</v>
-      </c>
-      <c r="B162" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>370</v>
+      </c>
+      <c r="B163" t="s">
         <v>371</v>
-      </c>
-      <c r="B163" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>372</v>
+      </c>
+      <c r="B164" t="s">
         <v>373</v>
-      </c>
-      <c r="B164" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>374</v>
+      </c>
+      <c r="B165" t="s">
         <v>375</v>
-      </c>
-      <c r="B165" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B166" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B167" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B168" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B169" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>380</v>
+      </c>
+      <c r="B170" t="s">
         <v>381</v>
-      </c>
-      <c r="B170" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>382</v>
+      </c>
+      <c r="B171" t="s">
         <v>383</v>
-      </c>
-      <c r="B171" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>384</v>
+      </c>
+      <c r="B172" t="s">
         <v>385</v>
-      </c>
-      <c r="B172" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
+        <v>386</v>
+      </c>
+      <c r="B173" t="s">
         <v>387</v>
-      </c>
-      <c r="B173" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B174" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B175" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B176" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B177" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B178" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
+        <v>393</v>
+      </c>
+      <c r="B179" t="s">
         <v>394</v>
-      </c>
-      <c r="B179" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B180" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
   </sheetData>
@@ -4692,47 +4745,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4740,15 +4793,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4756,7 +4809,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -4771,7 +4824,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -4781,87 +4834,87 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>400</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B5" t="s">
+        <v>411</v>
+      </c>
+      <c r="C5" t="s">
+        <v>331</v>
+      </c>
+      <c r="D5" t="s">
         <v>412</v>
-      </c>
-      <c r="C5" t="s">
-        <v>332</v>
-      </c>
-      <c r="D5" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B6" t="s">
+        <v>413</v>
+      </c>
+      <c r="C6" t="s">
+        <v>333</v>
+      </c>
+      <c r="D6" t="s">
         <v>414</v>
-      </c>
-      <c r="C6" t="s">
-        <v>334</v>
-      </c>
-      <c r="D6" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C7" t="s">
         <v>416</v>
       </c>
-      <c r="C7" t="s">
-        <v>192</v>
-      </c>
       <c r="D7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" t="s">
         <v>418</v>
-      </c>
-      <c r="C8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D8" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4872,113 +4925,113 @@
         <v>419</v>
       </c>
       <c r="C9" t="s">
-        <v>420</v>
+        <v>381</v>
       </c>
       <c r="D9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
+        <v>420</v>
+      </c>
+      <c r="C10" t="s">
         <v>421</v>
       </c>
-      <c r="C10" t="s">
-        <v>422</v>
-      </c>
       <c r="D10" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B11" t="s">
+        <v>422</v>
+      </c>
+      <c r="C11" t="s">
         <v>423</v>
       </c>
-      <c r="C11" t="s">
-        <v>424</v>
-      </c>
       <c r="D11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s">
+        <v>424</v>
+      </c>
+      <c r="C12" t="s">
         <v>425</v>
       </c>
-      <c r="C12" t="s">
-        <v>384</v>
-      </c>
       <c r="D12" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s">
         <v>426</v>
       </c>
       <c r="C13" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="D13" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s">
         <v>427</v>
       </c>
       <c r="C14" t="s">
-        <v>388</v>
+        <v>428</v>
       </c>
       <c r="D14" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C15" t="s">
-        <v>429</v>
+        <v>385</v>
       </c>
       <c r="D15" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s">
         <v>430</v>
       </c>
       <c r="C16" t="s">
-        <v>330</v>
+        <v>387</v>
       </c>
       <c r="D16" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s">
         <v>431</v>
@@ -4987,175 +5040,273 @@
         <v>432</v>
       </c>
       <c r="D17" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B18" t="s">
         <v>433</v>
       </c>
       <c r="C18" t="s">
-        <v>434</v>
+        <v>329</v>
       </c>
       <c r="D18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B19" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="D19" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="B20" t="s">
+        <v>435</v>
+      </c>
+      <c r="C20" t="s">
         <v>436</v>
       </c>
-      <c r="C20" t="s">
-        <v>302</v>
-      </c>
       <c r="D20" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>135</v>
       </c>
       <c r="B21" t="s">
         <v>437</v>
       </c>
       <c r="C21" t="s">
-        <v>304</v>
+        <v>438</v>
       </c>
       <c r="D21" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B22" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C22" t="s">
-        <v>306</v>
+        <v>440</v>
       </c>
       <c r="D22" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="B23" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C23" t="s">
-        <v>311</v>
+        <v>261</v>
       </c>
       <c r="D23" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C24" t="s">
-        <v>313</v>
+        <v>443</v>
       </c>
       <c r="D24" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B25" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C25" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="D25" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C26" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="D26" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C27" t="s">
-        <v>319</v>
+        <v>394</v>
       </c>
       <c r="D27" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="C28" t="s">
-        <v>344</v>
+        <v>305</v>
       </c>
       <c r="D28" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C29" t="s">
-        <v>446</v>
+        <v>310</v>
       </c>
       <c r="D29" t="s">
-        <v>415</v>
+        <v>418</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" t="s">
+        <v>449</v>
+      </c>
+      <c r="C30" t="s">
+        <v>312</v>
+      </c>
+      <c r="D30" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" t="s">
+        <v>142</v>
+      </c>
+      <c r="B31" t="s">
+        <v>450</v>
+      </c>
+      <c r="C31" t="s">
+        <v>314</v>
+      </c>
+      <c r="D31" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>143</v>
+      </c>
+      <c r="B32" t="s">
+        <v>451</v>
+      </c>
+      <c r="C32" t="s">
+        <v>316</v>
+      </c>
+      <c r="D32" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" t="s">
+        <v>452</v>
+      </c>
+      <c r="C33" t="s">
+        <v>318</v>
+      </c>
+      <c r="D33" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" t="s">
+        <v>453</v>
+      </c>
+      <c r="C34" t="s">
+        <v>343</v>
+      </c>
+      <c r="D34" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" t="s">
+        <v>144</v>
+      </c>
+      <c r="B35" t="s">
+        <v>454</v>
+      </c>
+      <c r="C35" t="s">
+        <v>455</v>
+      </c>
+      <c r="D35" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C36" t="s">
+        <v>457</v>
+      </c>
+      <c r="D36" t="s">
+        <v>414</v>
       </c>
     </row>
   </sheetData>
@@ -5165,12 +5316,12 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B63"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5180,482 +5331,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B5" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B6" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B7" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="B8" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B9" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B11" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="B12" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B13" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="B14" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="B15" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B16" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B17" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="B18" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="B19" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B20" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="B21" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B22" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="B23" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B24" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="B25" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B26" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B27" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B28" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B29" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B30" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="B31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B32" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="B33" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="B35" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B36" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="B37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="B38" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="B39" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="B42" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="B43" t="s">
-        <v>274</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B44" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="B45" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="B46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="B47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="B48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="B52" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="B53" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="B54" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="B55" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B56" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="B60" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="B61" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B62" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="B63" t="s">
-        <v>274</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>534</v>
+      </c>
+      <c r="B64" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -5670,458 +5829,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="C5" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="D5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E5" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F5" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="G5" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H5" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I5" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="J5" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K5" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C6" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="D6" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E6" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F6" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="G6" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H6" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I6" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="J6" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K6" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B7" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="C7" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="D7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E7" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G7" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H7" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I7" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="J7" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K7" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B8" t="s">
+        <v>562</v>
+      </c>
+      <c r="C8" t="s">
+        <v>563</v>
+      </c>
+      <c r="D8" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" t="s">
         <v>550</v>
       </c>
-      <c r="C8" t="s">
-        <v>551</v>
-      </c>
-      <c r="D8" t="s">
-        <v>238</v>
-      </c>
-      <c r="E8" t="s">
-        <v>538</v>
-      </c>
       <c r="F8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G8" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H8" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I8" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="J8" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K8" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B9" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="C9" t="s">
+        <v>566</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" t="s">
+        <v>550</v>
+      </c>
+      <c r="F9" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" t="s">
+        <v>550</v>
+      </c>
+      <c r="H9" t="s">
+        <v>552</v>
+      </c>
+      <c r="I9" t="s">
+        <v>567</v>
+      </c>
+      <c r="J9" t="s">
         <v>554</v>
       </c>
-      <c r="D9" t="s">
-        <v>238</v>
-      </c>
-      <c r="E9" t="s">
-        <v>538</v>
-      </c>
-      <c r="F9" t="s">
-        <v>196</v>
-      </c>
-      <c r="G9" t="s">
-        <v>538</v>
-      </c>
-      <c r="H9" t="s">
-        <v>540</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>555</v>
-      </c>
-      <c r="J9" t="s">
-        <v>542</v>
-      </c>
-      <c r="K9" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B10" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="C10" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="D10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E10" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G10" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H10" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I10" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="J10" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K10" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B11" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C11" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="D11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E11" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G11" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H11" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I11" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="J11" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K11" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C12" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="D12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E12" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G12" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H12" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="J12" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K12" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B13" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C13" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="D13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E13" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F13" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="G13" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H13" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I13" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="J13" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K13" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B14" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C14" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="D14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E14" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F14" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="G14" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="H14" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="J14" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K14" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B15" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="C15" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="D15" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="E15" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="F15" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="G15" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="H15" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="J15" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K15" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B16" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C16" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="D16" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E16" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G16" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="H16" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="I16" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="J16" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="K16" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -6166,22 +6325,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -6196,22 +6355,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
     </row>
   </sheetData>
@@ -6226,44 +6385,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -6278,44 +6437,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -6330,92 +6489,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6425,22 +6584,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
@@ -6455,7 +6614,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6470,87 +6629,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="623">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -381,39 +381,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_13ab43f9_d8nsr.v:100: error: Unknown module type: fet_delay_timingskew_13ab43f9_d8nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_13ab43f9_d8nsr.v:127: error: Unknown module type: fet_delay_timingskew_13ab43f9_d8nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_13ab43f9_d8nsr_nout referenced 1 times.
-        fet_delay_timingskew_13ab43f9_d8nsr_pin referenced 1 times.
-***
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_0bb48130_d1nsr.v:100: error: Unknown module type: fet_delay_timingskew_0bb48130_d1nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_0bb48130_d1nsr.v:127: error: Unknown module type: fet_delay_timingskew_0bb48130_d1nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_0bb48130_d1nsr_nout referenced 1 times.
-        fet_delay_timingskew_0bb48130_d1nsr_pin referenced 1 times.
-***
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_afbafd68_d1nsr.v:100: error: Unknown module type: fet_delay_timingskew_afbafd68_d1nsr_pin
-/celera/projects/Sunnyvale/software/WALTZ/verilog4/delay_timingskew_afbafd68_d1nsr.v:127: error: Unknown module type: fet_delay_timingskew_afbafd68_d1nsr_nout
-3 error(s) during elaboration.
-*** These modules were missing:
-        fet_delay_timingskew_afbafd68_d1nsr_nout referenced 1 times.
-        fet_delay_timingskew_afbafd68_d1nsr_pin referenced 1 times.
-***
 </t>
   </si>
   <si>
@@ -2627,7 +2594,7 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2758,21 +2725,6 @@
     <row r="49" spans="1:1">
       <c r="A49" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2787,7 +2739,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3017,17 +2969,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -3042,37 +2994,37 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -3082,42 +3034,42 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -3127,77 +3079,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:1">
@@ -3207,22 +3159,22 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:1">
@@ -3232,52 +3184,52 @@
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -3287,7 +3239,7 @@
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3302,17 +3254,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -3327,52 +3279,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -3387,81 +3339,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B5" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3469,1268 +3421,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B21" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B28" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B29" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B32" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B41" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B48" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B51" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B52" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B55" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B56" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B57" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B64" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B67" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B68" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B69" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B70" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B77" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B78" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B79" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="B80" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B81" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B82" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B83" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B84" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B85" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B86" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B87" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B88" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B90" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B91" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B92" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B93" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B95" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B96" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B97" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B98" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B99" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B100" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B101" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B102" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B103" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B106" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B107" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B108" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B109" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B110" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B111" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B112" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B113" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B116" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B117" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B118" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B119" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B120" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B121" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="B122" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B123" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B124" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B125" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B126" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B127" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B128" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B129" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B130" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B131" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B132" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B133" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B134" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="B135" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B136" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B137" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B138" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B139" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B140" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B141" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B142" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B143" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B144" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B145" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B146" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B147" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B148" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B149" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B150" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B151" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B152" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B153" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B154" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B155" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B156" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B157" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B158" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B159" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B160" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B161" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B162" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B163" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B164" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B165" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B166" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B167" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B168" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B169" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B170" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B171" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B172" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B173" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B174" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B175" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B176" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B177" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B178" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B179" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B180" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -4745,47 +4697,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4793,15 +4745,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4809,7 +4761,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -4824,7 +4776,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -4839,82 +4791,82 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>399</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="C5" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="C6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D6" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C7" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C8" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4922,13 +4874,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="C9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4936,69 +4888,69 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C10" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="D10" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B11" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="C11" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D11" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B12" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C12" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D12" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C13" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="D13" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B14" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="C14" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D14" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -5006,153 +4958,153 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C15" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="D15" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="C16" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D16" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B17" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C17" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D17" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B18" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C18" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="D18" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C19" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D19" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="C20" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="D20" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C21" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="D21" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B22" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="C22" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D22" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C23" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D23" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B24" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C24" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D24" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="C25" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D25" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5160,13 +5112,13 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C26" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D26" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5174,27 +5126,27 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="C27" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="D27" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C28" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D28" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5202,13 +5154,13 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C29" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D29" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5216,83 +5168,83 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C30" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D30" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B31" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C31" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D31" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B32" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="C32" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D32" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B33" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="C33" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D33" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B34" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C34" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="D34" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B35" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="C35" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="D35" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -5300,13 +5252,13 @@
         <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C36" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D36" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -5321,7 +5273,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5331,490 +5283,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="B5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="B6" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B7" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B8" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="B9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="B10" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B11" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B12" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B13" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B14" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B15" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B16" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B17" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B18" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="B19" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B20" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B21" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B22" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="B23" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B24" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B25" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B26" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B27" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B28" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B29" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B30" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B31" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B33" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B34" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B35" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B36" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="B39" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B43" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B44" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B45" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B46" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="B47" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B48" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="B49" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B50" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="B51" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B52" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="B53" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B54" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B55" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="B56" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B58" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B59" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B60" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B61" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B62" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B63" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B64" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -5829,458 +5781,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>539</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B5" t="s">
+        <v>545</v>
+      </c>
+      <c r="C5" t="s">
+        <v>546</v>
+      </c>
+      <c r="D5" t="s">
+        <v>234</v>
+      </c>
+      <c r="E5" t="s">
+        <v>547</v>
+      </c>
+      <c r="F5" t="s">
         <v>548</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" t="s">
+        <v>547</v>
+      </c>
+      <c r="H5" t="s">
         <v>549</v>
       </c>
-      <c r="D5" t="s">
-        <v>237</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>550</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
         <v>551</v>
       </c>
-      <c r="G5" t="s">
-        <v>550</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>552</v>
-      </c>
-      <c r="I5" t="s">
-        <v>553</v>
-      </c>
-      <c r="J5" t="s">
-        <v>554</v>
-      </c>
-      <c r="K5" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B6" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C6" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E6" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F6" t="s">
+        <v>548</v>
+      </c>
+      <c r="G6" t="s">
+        <v>547</v>
+      </c>
+      <c r="H6" t="s">
+        <v>549</v>
+      </c>
+      <c r="I6" t="s">
+        <v>555</v>
+      </c>
+      <c r="J6" t="s">
         <v>551</v>
       </c>
-      <c r="G6" t="s">
-        <v>550</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="K6" t="s">
         <v>552</v>
-      </c>
-      <c r="I6" t="s">
-        <v>558</v>
-      </c>
-      <c r="J6" t="s">
-        <v>554</v>
-      </c>
-      <c r="K6" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B7" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="C7" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G7" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H7" t="s">
+        <v>549</v>
+      </c>
+      <c r="I7" t="s">
+        <v>558</v>
+      </c>
+      <c r="J7" t="s">
+        <v>551</v>
+      </c>
+      <c r="K7" t="s">
         <v>552</v>
-      </c>
-      <c r="I7" t="s">
-        <v>561</v>
-      </c>
-      <c r="J7" t="s">
-        <v>554</v>
-      </c>
-      <c r="K7" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B8" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C8" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D8" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G8" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H8" t="s">
+        <v>549</v>
+      </c>
+      <c r="I8" t="s">
+        <v>561</v>
+      </c>
+      <c r="J8" t="s">
+        <v>551</v>
+      </c>
+      <c r="K8" t="s">
         <v>552</v>
-      </c>
-      <c r="I8" t="s">
-        <v>564</v>
-      </c>
-      <c r="J8" t="s">
-        <v>554</v>
-      </c>
-      <c r="K8" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B9" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C9" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E9" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G9" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H9" t="s">
+        <v>549</v>
+      </c>
+      <c r="I9" t="s">
+        <v>564</v>
+      </c>
+      <c r="J9" t="s">
+        <v>551</v>
+      </c>
+      <c r="K9" t="s">
         <v>552</v>
-      </c>
-      <c r="I9" t="s">
-        <v>567</v>
-      </c>
-      <c r="J9" t="s">
-        <v>554</v>
-      </c>
-      <c r="K9" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="C10" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="D10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E10" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F10" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G10" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H10" t="s">
+        <v>549</v>
+      </c>
+      <c r="I10" t="s">
+        <v>567</v>
+      </c>
+      <c r="J10" t="s">
+        <v>551</v>
+      </c>
+      <c r="K10" t="s">
         <v>552</v>
-      </c>
-      <c r="I10" t="s">
-        <v>570</v>
-      </c>
-      <c r="J10" t="s">
-        <v>554</v>
-      </c>
-      <c r="K10" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B11" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C11" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="D11" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E11" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G11" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H11" t="s">
+        <v>549</v>
+      </c>
+      <c r="I11" t="s">
+        <v>570</v>
+      </c>
+      <c r="J11" t="s">
+        <v>551</v>
+      </c>
+      <c r="K11" t="s">
         <v>552</v>
-      </c>
-      <c r="I11" t="s">
-        <v>573</v>
-      </c>
-      <c r="J11" t="s">
-        <v>554</v>
-      </c>
-      <c r="K11" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B12" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C12" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G12" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H12" t="s">
+        <v>549</v>
+      </c>
+      <c r="J12" t="s">
+        <v>551</v>
+      </c>
+      <c r="K12" t="s">
         <v>552</v>
-      </c>
-      <c r="J12" t="s">
-        <v>554</v>
-      </c>
-      <c r="K12" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B13" t="s">
+        <v>572</v>
+      </c>
+      <c r="C13" t="s">
+        <v>573</v>
+      </c>
+      <c r="D13" t="s">
+        <v>234</v>
+      </c>
+      <c r="E13" t="s">
+        <v>547</v>
+      </c>
+      <c r="F13" t="s">
+        <v>574</v>
+      </c>
+      <c r="G13" t="s">
+        <v>547</v>
+      </c>
+      <c r="H13" t="s">
+        <v>549</v>
+      </c>
+      <c r="I13" t="s">
         <v>575</v>
       </c>
-      <c r="C13" t="s">
-        <v>576</v>
-      </c>
-      <c r="D13" t="s">
-        <v>237</v>
-      </c>
-      <c r="E13" t="s">
-        <v>550</v>
-      </c>
-      <c r="F13" t="s">
-        <v>577</v>
-      </c>
-      <c r="G13" t="s">
-        <v>550</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
+        <v>551</v>
+      </c>
+      <c r="K13" t="s">
         <v>552</v>
-      </c>
-      <c r="I13" t="s">
-        <v>578</v>
-      </c>
-      <c r="J13" t="s">
-        <v>554</v>
-      </c>
-      <c r="K13" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B14" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C14" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E14" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F14" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G14" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H14" t="s">
+        <v>549</v>
+      </c>
+      <c r="J14" t="s">
+        <v>551</v>
+      </c>
+      <c r="K14" t="s">
         <v>552</v>
-      </c>
-      <c r="J14" t="s">
-        <v>554</v>
-      </c>
-      <c r="K14" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B15" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="C15" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D15" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E15" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F15" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="G15" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H15" t="s">
+        <v>549</v>
+      </c>
+      <c r="J15" t="s">
+        <v>551</v>
+      </c>
+      <c r="K15" t="s">
         <v>552</v>
-      </c>
-      <c r="J15" t="s">
-        <v>554</v>
-      </c>
-      <c r="K15" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="B16" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="C16" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="D16" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E16" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F16" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G16" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H16" t="s">
+        <v>549</v>
+      </c>
+      <c r="I16" t="s">
+        <v>582</v>
+      </c>
+      <c r="J16" t="s">
+        <v>551</v>
+      </c>
+      <c r="K16" t="s">
         <v>552</v>
-      </c>
-      <c r="I16" t="s">
-        <v>585</v>
-      </c>
-      <c r="J16" t="s">
-        <v>554</v>
-      </c>
-      <c r="K16" t="s">
-        <v>555</v>
       </c>
     </row>
   </sheetData>
@@ -6325,22 +6277,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -6355,22 +6307,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>
@@ -6385,44 +6337,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -6437,44 +6389,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>589</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>591</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>593</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>594</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>596</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -6489,92 +6441,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6584,22 +6536,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -6614,7 +6566,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6629,87 +6581,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1520" uniqueCount="1023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="712">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -157,54 +157,6 @@
     <t>(!!! MUST FIX !!! - not allowed)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_496698b1_XU8_be4c5eaa_XDEBUG(ten_496698b1_XU8_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_5e7931f3_XU7_be4c5eaa_XDEBUG(ten_5e7931f3_XU7_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_7bb789c1_XU3_be4c5eaa_XDEBUG(ten_7bb789c1_XU3_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_bdb7126b_XU6_be4c5eaa_XDEBUG(ten_bdb7126b_XU6_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_fc840bff_XU4_be4c5eaa_XDEBUG(ten_fc840bff_XU4_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_38b575fc_XU10_be4c5eaa_XDEBUG(ten_38b575fc_XU10_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_71505146_XU19_be4c5eaa_XDEBUG(ten_71505146_XU19_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_b20889dd_XU21_be4c5eaa_XDEBUG(ten_b20889dd_XU21_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_f614d104_XU20_be4c5eaa_XDEBUG(ten_f614d104_XU20_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG(ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN(ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN(global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN(global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN)</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK</t>
   </si>
   <si>
@@ -220,51 +172,6 @@
     <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
   </si>
   <si>
-    <t>Floating pin XCONTROL.ten_016e5221_XU14_76edd7de_XCONTROL(ten_016e5221_XU14_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_10af5487_XU89_76edd7de_XCONTROL(ten_10af5487_XU89_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_1c924704_XU94_76edd7de_XCONTROL(ten_1c924704_XU94_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_250e1d7b_XU96_76edd7de_XCONTROL(ten_250e1d7b_XU96_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_3a54983a_XU93_76edd7de_XCONTROL(ten_3a54983a_XU93_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_5dbb5861_XU98_76edd7de_XCONTROL(ten_5dbb5861_XU98_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_78907f64_XU97_76edd7de_XCONTROL(ten_78907f64_XU97_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_9e0c6a0f_XU20_76edd7de_XCONTROL(ten_9e0c6a0f_XU20_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_a9541403_XU99_76edd7de_XCONTROL(ten_a9541403_XU99_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_b275df66_XU92_76edd7de_XCONTROL(ten_b275df66_XU92_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_c406e2e9_XU16_76edd7de_XCONTROL(ten_c406e2e9_XU16_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_dc7df0cc_XU18_76edd7de_XCONTROL(ten_dc7df0cc_XU18_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_e1c50519_XU90_76edd7de_XCONTROL(ten_e1c50519_XU90_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_e41e5cb3_XU95_76edd7de_XCONTROL(ten_e41e5cb3_XU95_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
-    <t>Floating pin XCONTROL.ten_efe3dfd4_XU91_76edd7de_XCONTROL(ten_efe3dfd4_XU91_76edd7de_XCONTROL)</t>
-  </si>
-  <si>
     <t>Floating pin XALGORITHM.enableFAULT(121)</t>
   </si>
   <si>
@@ -325,231 +232,15 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW(global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW(ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW(ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XBOTSW.ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW(ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_2a0216d2_XU20_c1b82e6f_XDEBUG(ten_2a0216d2_XU20_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_32f97a89_XU11_c1b82e6f_XDEBUG(ten_32f97a89_XU11_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_34071f1d_XU15_c1b82e6f_XDEBUG(ten_34071f1d_XU15_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_3788e0aa_XU16_c1b82e6f_XDEBUG(ten_3788e0aa_XU16_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_e5798d25_XU18_c1b82e6f_XDEBUG(ten_e5798d25_XU18_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_f83f6ba2_XU10_c1b82e6f_XDEBUG(ten_f83f6ba2_XU10_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_fcfb2c12_XU12_c1b82e6f_XDEBUG(ten_fcfb2c12_XU12_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_af379456_XU5_c1b82e6f_XDEBUG(ten_hijack_af379456_XU5_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG(ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG(ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG(ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.global_cboot_35156756_XU17_f604d85e_XTOPSW(global_cboot_35156756_XU17_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW(global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW(ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW(global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
-    <t>Floating pin XTOPSW.ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW(ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_6044b743_XU7_4c867da6_XDEBUG(ten_6044b743_XU7_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_7e48a0c0_XU2_4c867da6_XDEBUG(ten_7e48a0c0_XU2_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_7e6d3e04_XU1_4c867da6_XDEBUG(ten_7e6d3e04_XU1_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_0b40c959_XU6_4c867da6_XDEBUG(ten_hijack_0b40c959_XU6_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_54e727e4_XU15_4c867da6_XDEBUG(ten_hijack_54e727e4_XU15_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_9929432d_XU17_4c867da6_XDEBUG(ten_hijack_9929432d_XU17_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG(ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG(ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG(ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG(ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_9929432d_XU17_4c867da6_XDEBUG(ten_hijacki_9929432d_XU17_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG(ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG(ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN(ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN)</t>
-  </si>
-  <si>
     <t>Floating pin XMAIN.mode_hiccup(45)</t>
   </si>
   <si>
     <t>Floating pin XMAIN.blank_thermal(46)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_14c9168a_XU7_1cec7299_XDEBUG(ten_14c9168a_XU7_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_6d67c253_XU1_1cec7299_XDEBUG(ten_6d67c253_XU1_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_c69fe1aa_XU8_1cec7299_XDEBUG(ten_c69fe1aa_XU8_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_1d78f0e4_XU13_1cec7299_XDEBUG(ten_1d78f0e4_XU13_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_d748b831_XU15_1cec7299_XDEBUG(ten_d748b831_XU15_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_f4762d45_XU11_1cec7299_XDEBUG(ten_f4762d45_XU11_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_6613b2af_XU3_1cec7299_XDEBUG(ten_hijack_6613b2af_XU3_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_c541f94b_XU16_1cec7299_XDEBUG(ten_hijack_c541f94b_XU16_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG(ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG(ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG(ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_vbuffer_e96a4067_XU8_811a9a05_XMAIN(global_vbuffer_e96a4067_XU8_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN(ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_comparator_70e67769_XU3_811a9a05_XMAIN(global_comparator_70e67769_XU3_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_comparator_ddbf938d_XU22_811a9a05_XMAIN(global_comparator_ddbf938d_XU22_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_resistordivider_37d49b79_XU17_811a9a05_XMAIN(global_resistordivider_37d49b79_XU17_811a9a05_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_162b659f_XU9_f255c70e_XDEBUG(ten_162b659f_XU9_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_83ff2716_XU8_f255c70e_XDEBUG(ten_83ff2716_XU8_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_913fa695_XU7_f255c70e_XDEBUG(ten_913fa695_XU7_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_95483466_XU2_f255c70e_XDEBUG(ten_95483466_XU2_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_d922ca5f_XU6_f255c70e_XDEBUG(ten_d922ca5f_XU6_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_de422ccd_XU11_f255c70e_XDEBUG(ten_hijack_de422ccd_XU11_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG(ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG)</t>
-  </si>
-  <si>
     <t>Floating pin XU10.enable_switch(58)</t>
   </si>
   <si>
@@ -577,63 +268,6 @@
     <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_gm_e44d2b4d_Xgm1_10783060_XMAIN(global_gm_e44d2b4d_Xgm1_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_clamp_b8eb1a18_XU7_10783060_XMAIN(global_clamp_b8eb1a18_XU7_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_vbuffer_866ca25c_XU9_10783060_XMAIN(global_vbuffer_866ca25c_XU9_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_comparator_5c7dff44_XU10_10783060_XMAIN(global_comparator_5c7dff44_XU10_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_voltage2current_4215aede_XU3_10783060_XMAIN(global_voltage2current_4215aede_XU3_10783060_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_0721e5d9_XU56_5c792007_XSEQUENCER(ten_0721e5d9_XU56_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_2958f818_XU61_5c792007_XSEQUENCER(ten_2958f818_XU61_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_29fa69a5_XU60_5c792007_XSEQUENCER(ten_29fa69a5_XU60_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_3bd9bacc_XU59_5c792007_XSEQUENCER(ten_3bd9bacc_XU59_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_445acf01_XU57_5c792007_XSEQUENCER(ten_445acf01_XU57_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_4c7ada73_XU65_5c792007_XSEQUENCER(ten_4c7ada73_XU65_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_4d227e72_XU55_5c792007_XSEQUENCER(ten_4d227e72_XU55_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_6cd23b02_XU66_5c792007_XSEQUENCER(ten_6cd23b02_XU66_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_70525239_XU58_5c792007_XSEQUENCER(ten_70525239_XU58_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_950364d7_XU54_5c792007_XSEQUENCER(ten_950364d7_XU54_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_9d829c39_XU62_5c792007_XSEQUENCER(ten_9d829c39_XU62_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_9ef032e9_XU63_5c792007_XSEQUENCER(ten_9ef032e9_XU63_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
-    <t>Floating pin XSEQUENCER.ten_e8d90cd0_XU64_5c792007_XSEQUENCER(ten_e8d90cd0_XU64_5c792007_XSEQUENCER)</t>
-  </si>
-  <si>
     <t>Floating pin XMAIN.STATEcontrol0(80)</t>
   </si>
   <si>
@@ -646,777 +280,279 @@
     <t>Floating pin XMAIN.STATEcontrol3(83)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_1955111b_XU7_63f6e3c4_XDEBUG(ten_1955111b_XU7_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_742857bf_XU2_63f6e3c4_XDEBUG(ten_742857bf_XU2_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_a6a0ac97_XU3_63f6e3c4_XDEBUG(ten_a6a0ac97_XU3_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_ec5776d4_XU6_63f6e3c4_XDEBUG(ten_ec5776d4_XU6_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_cd882763_XU15_63f6e3c4_XDEBUG(ten_cd882763_XU15_63f6e3c4_XDEBUG)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_ref_553d3e5b_XU4_2345cd7b_XMAIN(ten_ref_553d3e5b_XU4_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN(ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_reference_553d3e5b_XU4_2345cd7b_XMAIN(global_reference_553d3e5b_XU4_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN(global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.global_comparator_75c89176_XU16_2345cd7b_XMAIN(global_comparator_75c89176_XU16_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN(ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_81f80d4d_XU8_88e49508_XDEBUG(ten_81f80d4d_XU8_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_ed87e5db_XU5_88e49508_XDEBUG(ten_ed87e5db_XU5_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_f665b623_XU6_88e49508_XDEBUG(ten_f665b623_XU6_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_528f048c_XU10_88e49508_XDEBUG(ten_528f048c_XU10_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_297df8ef_XU1_88e49508_XDEBUG(ten_hijack_297df8ef_XU1_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijack_dcf795e2_XU14_88e49508_XDEBUG(ten_hijack_dcf795e2_XU14_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_297df8ef_XU1_88e49508_XDEBUG(ten_hijacki_297df8ef_XU1_88e49508_XDEBUG)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG(ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG)</t>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
+  </si>
+  <si>
+    <t>No Connects - Outputs</t>
+  </si>
+  <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>Mixed Mode Conflicts</t>
+  </si>
+  <si>
+    <t>Ring Core IO check report</t>
+  </si>
+  <si>
+    <t>No issues found</t>
+  </si>
+  <si>
+    <t>D to A Tree</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
-    <t>Floating pin XMAIN8.global_dac_0cc08401_XU5_b48f6491_XMAIN8(global_dac_0cc08401_XU5_b48f6491_XMAIN8)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8(global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.halfway(36)</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>ten_496698b1_XU8_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_496698b1_XU8_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_5e7931f3_XU7_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_5e7931f3_XU7_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_7bb789c1_XU3_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7bb789c1_XU3_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_bdb7126b_XU6_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_bdb7126b_XU6_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_fc840bff_XU4_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fc840bff_XU4_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_38b575fc_XU10_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_38b575fc_XU10_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_71505146_XU19_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_71505146_XU19_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_b20889dd_XU21_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_b20889dd_XU21_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_f614d104_XU20_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f614d104_XU20_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG - {"path": "XWALTZ,XceleraCORE,XCLOCK,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_1762d8ee_XU11_be4c5eaa_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "ten_osc_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_oscillator_90c263a6_XOSCEXT_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_016e5221_XU14_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_016e5221_XU14_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_10af5487_XU89_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_10af5487_XU89_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_1c924704_XU94_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_1c924704_XU94_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_250e1d7b_XU96_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_250e1d7b_XU96_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_3a54983a_XU93_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_3a54983a_XU93_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_5dbb5861_XU98_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_5dbb5861_XU98_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_78907f64_XU97_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_78907f64_XU97_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_9e0c6a0f_XU20_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_9e0c6a0f_XU20_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_a9541403_XU99_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_a9541403_XU99_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_b275df66_XU92_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_b275df66_XU92_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_c406e2e9_XU16_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_c406e2e9_XU16_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_dc7df0cc_XU18_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_dc7df0cc_XU18_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_e1c50519_XU90_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e1c50519_XU90_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_e41e5cb3_XU95_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_e41e5cb3_XU95_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_efe3dfd4_XU91_76edd7de_XCONTROL - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "ten_efe3dfd4_XU91_76edd7de_XCONTROL", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW", "instance": "XBOTSW", "symbol": "ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_2a0216d2_XU20_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_2a0216d2_XU20_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_32f97a89_XU11_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_32f97a89_XU11_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_34071f1d_XU15_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_34071f1d_XU15_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_3788e0aa_XU16_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_3788e0aa_XU16_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_e5798d25_XU18_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_e5798d25_XU18_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_f83f6ba2_XU10_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f83f6ba2_XU10_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_fcfb2c12_XU12_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_fcfb2c12_XU12_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_a6d52f4f_XU9_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_af379456_XU5_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG - {"path": "XWALTZ,XceleraCORE,XDRIVER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_cad020c2_XU6_c1b82e6f_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_cboot_35156756_XU17_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_cboot_35156756_XU17_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_slopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_taiislopecomp_f4252e65_XU22_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW", "instance": "XTOPSW", "symbol": "ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_6044b743_XU7_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6044b743_XU7_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_7e48a0c0_XU2_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e48a0c0_XU2_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_7e6d3e04_XU1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_7e6d3e04_XU1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_0b40c959_XU6_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_54e727e4_XU15_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_55e03ae5_XU16_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_7e3d0298_XU27_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_9929432d_XU17_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9929432d_XU17_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_9b5d9ad2_XU29_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c5202207_Xdfthijack1_4c867da6_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "ten_201f84ba_Xthermal1_7fcbe2c9_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_14c9168a_XU7_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_14c9168a_XU7_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_6d67c253_XU1_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6d67c253_XU1_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_c69fe1aa_XU8_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_c69fe1aa_XU8_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_1d78f0e4_XU13_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1d78f0e4_XU13_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_d748b831_XU15_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d748b831_XU15_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_f4762d45_XU11_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f4762d45_XU11_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_6613b2af_XU3_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_c541f94b_XU16_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG", "instance": "XDEBUG", "symbol": "ten_6fd414fa_XUPOWERGOODshortdelay_1cec7299_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_vbuffer_e96a4067_XU8_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_e96a4067_XU8_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "ten_padopendrain_54c5b105_XU4_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_comparator_70e67769_XU3_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_70e67769_XU3_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_comparator_ddbf938d_XU22_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_ddbf938d_XU22_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN - {"path": "XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN", "instance": "XMAIN", "symbol": "global_resistordivider_37d49b79_XU17_811a9a05_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_162b659f_XU9_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_162b659f_XU9_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_83ff2716_XU8_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_83ff2716_XU8_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_913fa695_XU7_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_913fa695_XU7_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_95483466_XU2_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_95483466_XU2_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_d922ca5f_XU6_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_d922ca5f_XU6_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_de422ccd_XU11_f255c70e_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>global_gm_e44d2b4d_Xgm1_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_gm_e44d2b4d_Xgm1_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_clamp_b8eb1a18_XU7_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_clamp_b8eb1a18_XU7_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_vbuffer_866ca25c_XU9_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_vbuffer_866ca25c_XU9_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_comparator_5c7dff44_XU10_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_5c7dff44_XU10_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_voltage2current_4215aede_XU3_10783060_XMAIN - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN", "instance": "XMAIN", "symbol": "global_voltage2current_4215aede_XU3_10783060_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_0721e5d9_XU56_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_0721e5d9_XU56_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_2958f818_XU61_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_2958f818_XU61_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_29fa69a5_XU60_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_29fa69a5_XU60_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_3bd9bacc_XU59_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_3bd9bacc_XU59_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_445acf01_XU57_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_445acf01_XU57_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_4c7ada73_XU65_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4c7ada73_XU65_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_4d227e72_XU55_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_4d227e72_XU55_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_6cd23b02_XU66_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_6cd23b02_XU66_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_70525239_XU58_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_70525239_XU58_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_950364d7_XU54_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_950364d7_XU54_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_9d829c39_XU62_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9d829c39_XU62_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_9ef032e9_XU63_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_9ef032e9_XU63_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_e8d90cd0_XU64_5c792007_XSEQUENCER - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER", "instance": "XSEQUENCER", "symbol": "ten_e8d90cd0_XU64_5c792007_XSEQUENCER", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>ten_1955111b_XU7_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_1955111b_XU7_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_742857bf_XU2_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_742857bf_XU2_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_a6a0ac97_XU3_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_a6a0ac97_XU3_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_ec5776d4_XU6_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ec5776d4_XU6_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_cd882763_XU15_63f6e3c4_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSERVICE,XDEBUG", "instance": "XDEBUG", "symbol": "ten_cd882763_XU15_63f6e3c4_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_ref_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_ref_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_refbg_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv2v5_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_reference_553d3e5b_XU4_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_reference_553d3e5b_XU4_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_vbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taiv1v0f_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_comparator_75c89176_XU16_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "global_comparator_75c89176_XU16_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_taifbvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_tdiokvbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN - {"path": "XWALTZ,XceleraCORE,XSERVICE,XMAIN", "instance": "XMAIN", "symbol": "ten_enablevbias_23bb219c_Xvbias1_2345cd7b_XMAIN", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_81f80d4d_XU8_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_81f80d4d_XU8_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_ed87e5db_XU5_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_ed87e5db_XU5_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_f665b623_XU6_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_f665b623_XU6_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_528f048c_XU10_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_528f048c_XU10_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijack_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijack_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_297df8ef_XU1_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_297df8ef_XU1_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG", "instance": "XDEBUG", "symbol": "ten_hijacki_dcf795e2_XU14_88e49508_XDEBUG", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_dac_0cc08401_XU5_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_dac_0cc08401_XU5_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8", "io": "input", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>Mixed Mode Conflicts</t>
-  </si>
-  <si>
-    <t>Ring Core IO check report</t>
-  </si>
-  <si>
-    <t>No issues found</t>
-  </si>
-  <si>
-    <t>D to A Tree</t>
-  </si>
-  <si>
     <t>Xoscillator1</t>
   </si>
   <si>
@@ -1424,33 +560,6 @@
   </si>
   <si>
     <t>Errors</t>
-  </si>
-  <si>
-    <t>global_clocksync_5d4c1f91_Xclocksync1_e3014061_XMAIN XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>global_fetdriver_bd0adf3c_Xfetdriver1_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_14d08c8e_XU3_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_a0afb596_XU9_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_2d447a5c_XU17_ba40258e_XBOTSW XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>global_fetdriver_8018c87b_Xfetdriver_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
-  </si>
-  <si>
-    <t>ten_measure_currentlimit_98fa5525_XU2_f604d85e_XTOPSW XWALTZ,XceleraCORE,XDRIVER,XTOPSW</t>
-  </si>
-  <si>
-    <t>global_resistordivider_37d49b79_XU17_811a9a05_XMAIN XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
-  </si>
-  <si>
-    <t>global_oscillator_4c0bef8e_Xoscillator1_b48f6491_XMAIN8 XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8</t>
   </si>
   <si>
     <t>Cell Length Exceed Max 50</t>
@@ -1559,10 +668,22 @@
     <t>DFT Efficiency</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
     <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
@@ -1571,7 +692,22 @@
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER</t>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
@@ -1580,37 +716,40 @@
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
   </si>
   <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XPOWERGOOD</t>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION</t>
-  </si>
-  <si>
-    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 2, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSEQUENCER</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
   </si>
   <si>
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE</t>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 44, 'bytes': 44.0, 'noconns': 44, 'efficiency': '87.5%'}</t>
+    <t>{'cells': 32, 'bytes': 32.0, 'noconns': 86, 'efficiency': '66.4%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -2414,210 +1553,138 @@
     <t>dft_hex0x02</t>
   </si>
   <si>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x1A</t>
+  </si>
+  <si>
+    <t>0x1A</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
     <t>DFTtm8d</t>
   </si>
   <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>dft_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>dft_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>dft_hex0x08</t>
+  </si>
+  <si>
+    <t>dft_hex0x1B</t>
+  </si>
+  <si>
+    <t>0x1B</t>
+  </si>
+  <si>
+    <t>dft_hex0x09</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B</t>
+  </si>
+  <si>
+    <t>0x0B</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1C</t>
+  </si>
+  <si>
+    <t>dft_hex0x1D</t>
+  </si>
+  <si>
+    <t>0x1D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D</t>
+  </si>
+  <si>
+    <t>0x0D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E</t>
+  </si>
+  <si>
+    <t>0x0E</t>
+  </si>
+  <si>
+    <t>dft_hex0x0F</t>
+  </si>
+  <si>
+    <t>dft_hex0x1E</t>
+  </si>
+  <si>
+    <t>0x1E</t>
+  </si>
+  <si>
+    <t>dft_hex0x10</t>
+  </si>
+  <si>
+    <t>dft_hex0x11</t>
+  </si>
+  <si>
+    <t>dft_hex0x1F</t>
+  </si>
+  <si>
+    <t>dft_hex0x12</t>
+  </si>
+  <si>
+    <t>dft_hex0x13</t>
+  </si>
+  <si>
+    <t>dft_hex0x14</t>
+  </si>
+  <si>
+    <t>dft_hex0x15</t>
+  </si>
+  <si>
     <t>dft_hex0x16</t>
   </si>
   <si>
     <t>dft_hex0x17</t>
   </si>
   <si>
-    <t>dft_hex0x03</t>
-  </si>
-  <si>
-    <t>dft_hex0x04</t>
-  </si>
-  <si>
     <t>dft_hex0x18</t>
   </si>
   <si>
+    <t>dft_hex0x20</t>
+  </si>
+  <si>
+    <t>0x20</t>
+  </si>
+  <si>
     <t>dft_hex0x19</t>
   </si>
   <si>
     <t>0x19</t>
   </si>
   <si>
-    <t>dft_hex0x05</t>
-  </si>
-  <si>
-    <t>0x05</t>
-  </si>
-  <si>
-    <t>dft_hex0x06</t>
-  </si>
-  <si>
-    <t>0x06</t>
-  </si>
-  <si>
-    <t>dft_hex0x07</t>
-  </si>
-  <si>
-    <t>0x07</t>
-  </si>
-  <si>
-    <t>DFTtm8t</t>
-  </si>
-  <si>
-    <t>dft_hex0x08</t>
-  </si>
-  <si>
-    <t>dft_hex0x1A</t>
-  </si>
-  <si>
-    <t>0x1A</t>
-  </si>
-  <si>
-    <t>dft_hex0x1B</t>
-  </si>
-  <si>
-    <t>0x1B</t>
-  </si>
-  <si>
-    <t>dft_hex0x1C</t>
-  </si>
-  <si>
-    <t>dft_hex0x1D</t>
-  </si>
-  <si>
-    <t>0x1D</t>
-  </si>
-  <si>
-    <t>dft_hex0x09</t>
-  </si>
-  <si>
-    <t>dft_hex0x0A</t>
-  </si>
-  <si>
-    <t>dft_hex0x0B</t>
-  </si>
-  <si>
-    <t>0x0B</t>
-  </si>
-  <si>
-    <t>dft_hex0x1E</t>
-  </si>
-  <si>
-    <t>0x1E</t>
-  </si>
-  <si>
-    <t>dft_hex0x1F</t>
-  </si>
-  <si>
-    <t>dft_hex0x20</t>
-  </si>
-  <si>
-    <t>0x20</t>
-  </si>
-  <si>
-    <t>dft_hex0x21</t>
-  </si>
-  <si>
-    <t>0x21</t>
-  </si>
-  <si>
-    <t>dft_hex0x0C</t>
-  </si>
-  <si>
-    <t>dft_hex0x0D</t>
-  </si>
-  <si>
-    <t>0x0D</t>
-  </si>
-  <si>
-    <t>dft_hex0x22</t>
-  </si>
-  <si>
-    <t>0x22</t>
-  </si>
-  <si>
-    <t>dft_hex0x23</t>
-  </si>
-  <si>
-    <t>0x23</t>
-  </si>
-  <si>
-    <t>dft_hex0x24</t>
-  </si>
-  <si>
-    <t>0x24</t>
-  </si>
-  <si>
-    <t>dft_hex0x0E</t>
-  </si>
-  <si>
-    <t>0x0E</t>
-  </si>
-  <si>
-    <t>dft_hex0x0F</t>
-  </si>
-  <si>
-    <t>dft_hex0x25</t>
-  </si>
-  <si>
-    <t>0x25</t>
-  </si>
-  <si>
-    <t>dft_hex0x26</t>
-  </si>
-  <si>
-    <t>0x26</t>
-  </si>
-  <si>
-    <t>dft_hex0x10</t>
-  </si>
-  <si>
-    <t>dft_hex0x11</t>
-  </si>
-  <si>
-    <t>dft_hex0x27</t>
-  </si>
-  <si>
-    <t>0x27</t>
-  </si>
-  <si>
-    <t>dft_hex0x28</t>
-  </si>
-  <si>
-    <t>0x28</t>
-  </si>
-  <si>
-    <t>dft_hex0x12</t>
-  </si>
-  <si>
-    <t>dft_hex0x13</t>
-  </si>
-  <si>
-    <t>dft_hex0x29</t>
-  </si>
-  <si>
-    <t>0x29</t>
-  </si>
-  <si>
-    <t>dft_hex0x2A</t>
-  </si>
-  <si>
-    <t>0x2A</t>
-  </si>
-  <si>
-    <t>dft_hex0x14</t>
-  </si>
-  <si>
-    <t>dft_hex0x15</t>
-  </si>
-  <si>
-    <t>dft_hex0x2B</t>
-  </si>
-  <si>
-    <t>0x2B</t>
-  </si>
-  <si>
-    <t>dft_hex0x2C</t>
-  </si>
-  <si>
-    <t>0x2C</t>
-  </si>
-  <si>
     <t>Nesto Usage Report</t>
   </si>
   <si>
@@ -2639,16 +1706,16 @@
     <t>193</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>168</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
+    <t>131</t>
   </si>
   <si>
     <t>dbuf</t>
@@ -2681,22 +1748,22 @@
     <t>45</t>
   </si>
   <si>
+    <t>srlatch</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>nor2</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
     <t>dftmodule</t>
   </si>
   <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>srlatch</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>nor2</t>
-  </si>
-  <si>
-    <t>35</t>
+    <t>32</t>
   </si>
   <si>
     <t>dfthijack</t>
@@ -3490,7 +2557,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>452</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3510,7 +2577,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>453</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3525,7 +2592,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>454</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -3540,17 +2607,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>455</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>456</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3560,62 +2627,17 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>457</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>467</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3630,17 +2652,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>468</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>458</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>469</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3655,12 +2677,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>470</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>458</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3675,7 +2697,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3695,127 +2717,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>473</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>474</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>475</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>476</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>477</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>478</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>479</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>480</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>481</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>482</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>483</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>484</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>485</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>486</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>487</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>488</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>489</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>490</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>491</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>492</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>493</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>494</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>495</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>496</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3830,7 +2852,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>497</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3850,17 +2872,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>498</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>499</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>500</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -4080,277 +3102,257 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>501</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>502</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>503</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>502</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
+      <c r="A8" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>505</v>
+      <c r="A11" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>504</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>505</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>506</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>502</v>
+        <v>212</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>507</v>
+      <c r="A18" s="1" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>508</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>502</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>504</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" t="s">
-        <v>509</v>
+      <c r="A23" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" t="s">
-        <v>504</v>
+      <c r="A25" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>507</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>510</v>
+        <v>219</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>504</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>507</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>507</v>
+        <v>216</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
-      <c r="A34" s="1" t="s">
-        <v>511</v>
+      <c r="A33" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" t="s">
-        <v>507</v>
+      <c r="A36" s="1" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>502</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>507</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>512</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>513</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>502</v>
+        <v>225</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>502</v>
+      <c r="A44" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>514</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>504</v>
+      <c r="A47" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>516</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>516</v>
+      <c r="A51" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="1" t="s">
-        <v>517</v>
+      <c r="A53" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>509</v>
+      <c r="A55" s="1" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>502</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" s="1" t="s">
-        <v>26</v>
+      <c r="A58" s="1" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>502</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>502</v>
+      <c r="A62" s="1" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>514</v>
+        <v>206</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -4365,17 +3367,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>518</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>499</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>519</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -4390,52 +3392,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>521</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>522</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>523</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>524</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>525</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>526</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>527</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>528</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>529</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4450,81 +3452,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>530</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>531</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>534</v>
+        <v>247</v>
       </c>
       <c r="B5" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>538</v>
+        <v>251</v>
       </c>
       <c r="B7" t="s">
-        <v>537</v>
+        <v>248</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>539</v>
+        <v>252</v>
       </c>
       <c r="B8" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>540</v>
+        <v>253</v>
       </c>
       <c r="B9" t="s">
-        <v>541</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>542</v>
+        <v>255</v>
       </c>
       <c r="B10" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>544</v>
+        <v>257</v>
       </c>
       <c r="B11" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>545</v>
+        <v>258</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -4532,1268 +3534,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>546</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>547</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>548</v>
+        <v>261</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>549</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>550</v>
+        <v>263</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>551</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>552</v>
+        <v>265</v>
       </c>
       <c r="B20" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>553</v>
+        <v>266</v>
       </c>
       <c r="B21" t="s">
-        <v>537</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>554</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>555</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>556</v>
+        <v>269</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>557</v>
+        <v>270</v>
       </c>
       <c r="B27" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>558</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>559</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s">
-        <v>560</v>
+        <v>273</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>561</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>562</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>563</v>
+        <v>276</v>
       </c>
       <c r="B32" t="s">
-        <v>564</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>565</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s">
-        <v>566</v>
+        <v>279</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>567</v>
+        <v>280</v>
       </c>
       <c r="B34" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>569</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s">
-        <v>570</v>
+        <v>283</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>571</v>
+        <v>284</v>
       </c>
       <c r="B36" t="s">
-        <v>572</v>
+        <v>285</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>573</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>574</v>
+        <v>287</v>
       </c>
       <c r="B38" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>575</v>
+        <v>288</v>
       </c>
       <c r="B39" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>577</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>578</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>579</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>580</v>
+        <v>293</v>
       </c>
       <c r="B43" t="s">
-        <v>581</v>
+        <v>294</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>582</v>
+        <v>295</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>583</v>
+        <v>296</v>
       </c>
       <c r="B46" t="s">
-        <v>584</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>585</v>
+        <v>298</v>
       </c>
       <c r="B47" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>586</v>
+        <v>299</v>
       </c>
       <c r="B48" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>587</v>
+        <v>300</v>
       </c>
       <c r="B49" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>588</v>
+        <v>301</v>
       </c>
       <c r="B50" t="s">
-        <v>535</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>589</v>
+        <v>302</v>
       </c>
       <c r="B51" t="s">
-        <v>590</v>
+        <v>303</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>591</v>
+        <v>304</v>
       </c>
       <c r="B52" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>592</v>
+        <v>305</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>593</v>
+        <v>306</v>
       </c>
       <c r="B55" t="s">
-        <v>594</v>
+        <v>307</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>595</v>
+        <v>308</v>
       </c>
       <c r="B56" t="s">
-        <v>596</v>
+        <v>309</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>597</v>
+        <v>310</v>
       </c>
       <c r="B57" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>598</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>599</v>
+        <v>312</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>600</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>601</v>
+        <v>314</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>602</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>603</v>
+        <v>316</v>
       </c>
       <c r="B64" t="s">
-        <v>604</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>605</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>606</v>
+        <v>319</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>607</v>
+        <v>320</v>
       </c>
       <c r="B67" t="s">
-        <v>608</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>609</v>
+        <v>322</v>
       </c>
       <c r="B68" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>611</v>
+        <v>324</v>
       </c>
       <c r="B69" t="s">
-        <v>608</v>
+        <v>321</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>612</v>
+        <v>325</v>
       </c>
       <c r="B70" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>613</v>
+        <v>326</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>614</v>
+        <v>327</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>615</v>
+        <v>328</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>616</v>
+        <v>329</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>617</v>
+        <v>330</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>618</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>619</v>
+        <v>332</v>
       </c>
       <c r="B78" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>620</v>
+        <v>333</v>
       </c>
       <c r="B79" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>621</v>
+        <v>334</v>
       </c>
       <c r="B80" t="s">
-        <v>622</v>
+        <v>335</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>623</v>
+        <v>336</v>
       </c>
       <c r="B81" t="s">
-        <v>624</v>
+        <v>337</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>625</v>
+        <v>338</v>
       </c>
       <c r="B82" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>626</v>
+        <v>339</v>
       </c>
       <c r="B83" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>627</v>
+        <v>340</v>
       </c>
       <c r="B84" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>628</v>
+        <v>341</v>
       </c>
       <c r="B85" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>629</v>
+        <v>342</v>
       </c>
       <c r="B86" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>630</v>
+        <v>343</v>
       </c>
       <c r="B87" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>631</v>
+        <v>344</v>
       </c>
       <c r="B88" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>632</v>
+        <v>345</v>
       </c>
       <c r="B89" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>633</v>
+        <v>346</v>
       </c>
       <c r="B90" t="s">
-        <v>634</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>635</v>
+        <v>348</v>
       </c>
       <c r="B91" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>636</v>
+        <v>349</v>
       </c>
       <c r="B92" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>637</v>
+        <v>350</v>
       </c>
       <c r="B93" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>638</v>
+        <v>351</v>
       </c>
       <c r="B94" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>639</v>
+        <v>352</v>
       </c>
       <c r="B95" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>640</v>
+        <v>353</v>
       </c>
       <c r="B96" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>641</v>
+        <v>354</v>
       </c>
       <c r="B97" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>642</v>
+        <v>355</v>
       </c>
       <c r="B98" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>643</v>
+        <v>356</v>
       </c>
       <c r="B99" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>644</v>
+        <v>357</v>
       </c>
       <c r="B100" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>645</v>
+        <v>358</v>
       </c>
       <c r="B101" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>647</v>
+        <v>360</v>
       </c>
       <c r="B102" t="s">
-        <v>537</v>
+        <v>250</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>648</v>
+        <v>361</v>
       </c>
       <c r="B103" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>649</v>
+        <v>362</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>650</v>
+        <v>363</v>
       </c>
       <c r="B106" t="s">
-        <v>651</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>652</v>
+        <v>365</v>
       </c>
       <c r="B107" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>654</v>
+        <v>367</v>
       </c>
       <c r="B108" t="s">
-        <v>655</v>
+        <v>368</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>656</v>
+        <v>369</v>
       </c>
       <c r="B109" t="s">
-        <v>657</v>
+        <v>370</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>658</v>
+        <v>371</v>
       </c>
       <c r="B110" t="s">
-        <v>659</v>
+        <v>372</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>660</v>
+        <v>373</v>
       </c>
       <c r="B111" t="s">
-        <v>661</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>662</v>
+        <v>375</v>
       </c>
       <c r="B112" t="s">
-        <v>663</v>
+        <v>376</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>664</v>
+        <v>377</v>
       </c>
       <c r="B113" t="s">
-        <v>590</v>
+        <v>303</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>665</v>
+        <v>378</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>532</v>
+        <v>245</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>533</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>666</v>
+        <v>379</v>
       </c>
       <c r="B116" t="s">
-        <v>581</v>
+        <v>294</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>667</v>
+        <v>380</v>
       </c>
       <c r="B117" t="s">
-        <v>668</v>
+        <v>381</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>669</v>
+        <v>382</v>
       </c>
       <c r="B118" t="s">
-        <v>670</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>671</v>
+        <v>384</v>
       </c>
       <c r="B119" t="s">
-        <v>672</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>673</v>
+        <v>386</v>
       </c>
       <c r="B120" t="s">
-        <v>674</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>675</v>
+        <v>388</v>
       </c>
       <c r="B121" t="s">
-        <v>676</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>677</v>
+        <v>390</v>
       </c>
       <c r="B122" t="s">
-        <v>678</v>
+        <v>391</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>679</v>
+        <v>392</v>
       </c>
       <c r="B123" t="s">
-        <v>674</v>
+        <v>387</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>680</v>
+        <v>393</v>
       </c>
       <c r="B124" t="s">
-        <v>676</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>681</v>
+        <v>394</v>
       </c>
       <c r="B125" t="s">
-        <v>678</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>682</v>
+        <v>395</v>
       </c>
       <c r="B126" t="s">
-        <v>683</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>684</v>
+        <v>397</v>
       </c>
       <c r="B127" t="s">
-        <v>685</v>
+        <v>398</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>686</v>
+        <v>399</v>
       </c>
       <c r="B128" t="s">
-        <v>687</v>
+        <v>400</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>688</v>
+        <v>401</v>
       </c>
       <c r="B129" t="s">
-        <v>689</v>
+        <v>402</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>690</v>
+        <v>403</v>
       </c>
       <c r="B130" t="s">
-        <v>691</v>
+        <v>404</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>642</v>
+        <v>355</v>
       </c>
       <c r="B131" t="s">
-        <v>692</v>
+        <v>405</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>643</v>
+        <v>356</v>
       </c>
       <c r="B132" t="s">
-        <v>693</v>
+        <v>406</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>645</v>
+        <v>358</v>
       </c>
       <c r="B133" t="s">
-        <v>694</v>
+        <v>407</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>644</v>
+        <v>357</v>
       </c>
       <c r="B134" t="s">
-        <v>695</v>
+        <v>408</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>696</v>
+        <v>409</v>
       </c>
       <c r="B135" t="s">
-        <v>581</v>
+        <v>294</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>697</v>
+        <v>410</v>
       </c>
       <c r="B136" t="s">
-        <v>698</v>
+        <v>411</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>699</v>
+        <v>412</v>
       </c>
       <c r="B137" t="s">
-        <v>700</v>
+        <v>413</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>701</v>
+        <v>414</v>
       </c>
       <c r="B138" t="s">
-        <v>702</v>
+        <v>415</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>703</v>
+        <v>416</v>
       </c>
       <c r="B139" t="s">
-        <v>704</v>
+        <v>417</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>705</v>
+        <v>418</v>
       </c>
       <c r="B140" t="s">
-        <v>706</v>
+        <v>419</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>707</v>
+        <v>420</v>
       </c>
       <c r="B141" t="s">
-        <v>674</v>
+        <v>387</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>708</v>
+        <v>421</v>
       </c>
       <c r="B142" t="s">
-        <v>676</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>709</v>
+        <v>422</v>
       </c>
       <c r="B143" t="s">
-        <v>678</v>
+        <v>391</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>710</v>
+        <v>423</v>
       </c>
       <c r="B144" t="s">
-        <v>683</v>
+        <v>396</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>711</v>
+        <v>424</v>
       </c>
       <c r="B145" t="s">
-        <v>685</v>
+        <v>398</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>712</v>
+        <v>425</v>
       </c>
       <c r="B146" t="s">
-        <v>687</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>713</v>
+        <v>426</v>
       </c>
       <c r="B147" t="s">
-        <v>689</v>
+        <v>402</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>714</v>
+        <v>427</v>
       </c>
       <c r="B148" t="s">
-        <v>691</v>
+        <v>404</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>715</v>
+        <v>428</v>
       </c>
       <c r="B149" t="s">
-        <v>716</v>
+        <v>429</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>717</v>
+        <v>430</v>
       </c>
       <c r="B150" t="s">
-        <v>718</v>
+        <v>431</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>719</v>
+        <v>432</v>
       </c>
       <c r="B151" t="s">
-        <v>720</v>
+        <v>433</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>721</v>
+        <v>434</v>
       </c>
       <c r="B152" t="s">
-        <v>722</v>
+        <v>435</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>723</v>
+        <v>436</v>
       </c>
       <c r="B153" t="s">
-        <v>724</v>
+        <v>437</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>725</v>
+        <v>438</v>
       </c>
       <c r="B154" t="s">
-        <v>726</v>
+        <v>439</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>727</v>
+        <v>440</v>
       </c>
       <c r="B155" t="s">
-        <v>728</v>
+        <v>441</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>729</v>
+        <v>442</v>
       </c>
       <c r="B156" t="s">
-        <v>730</v>
+        <v>443</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>731</v>
+        <v>444</v>
       </c>
       <c r="B157" t="s">
-        <v>732</v>
+        <v>445</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>733</v>
+        <v>446</v>
       </c>
       <c r="B158" t="s">
-        <v>734</v>
+        <v>447</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>735</v>
+        <v>448</v>
       </c>
       <c r="B159" t="s">
-        <v>736</v>
+        <v>449</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>737</v>
+        <v>450</v>
       </c>
       <c r="B160" t="s">
-        <v>738</v>
+        <v>451</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>739</v>
+        <v>452</v>
       </c>
       <c r="B161" t="s">
-        <v>740</v>
+        <v>453</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>741</v>
+        <v>454</v>
       </c>
       <c r="B162" t="s">
-        <v>742</v>
+        <v>455</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>743</v>
+        <v>456</v>
       </c>
       <c r="B163" t="s">
-        <v>744</v>
+        <v>457</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>745</v>
+        <v>458</v>
       </c>
       <c r="B164" t="s">
-        <v>746</v>
+        <v>459</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>747</v>
+        <v>460</v>
       </c>
       <c r="B165" t="s">
-        <v>748</v>
+        <v>461</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>749</v>
+        <v>462</v>
       </c>
       <c r="B166" t="s">
-        <v>722</v>
+        <v>435</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>750</v>
+        <v>463</v>
       </c>
       <c r="B167" t="s">
-        <v>704</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>751</v>
+        <v>464</v>
       </c>
       <c r="B168" t="s">
-        <v>706</v>
+        <v>419</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>752</v>
+        <v>465</v>
       </c>
       <c r="B169" t="s">
-        <v>564</v>
+        <v>277</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>753</v>
+        <v>466</v>
       </c>
       <c r="B170" t="s">
-        <v>754</v>
+        <v>467</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>755</v>
+        <v>468</v>
       </c>
       <c r="B171" t="s">
-        <v>756</v>
+        <v>469</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>757</v>
+        <v>470</v>
       </c>
       <c r="B172" t="s">
-        <v>758</v>
+        <v>471</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>759</v>
+        <v>472</v>
       </c>
       <c r="B173" t="s">
-        <v>760</v>
+        <v>473</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>761</v>
+        <v>474</v>
       </c>
       <c r="B174" t="s">
-        <v>543</v>
+        <v>256</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>762</v>
+        <v>475</v>
       </c>
       <c r="B175" t="s">
-        <v>674</v>
+        <v>387</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>763</v>
+        <v>476</v>
       </c>
       <c r="B176" t="s">
-        <v>676</v>
+        <v>389</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>764</v>
+        <v>477</v>
       </c>
       <c r="B177" t="s">
-        <v>716</v>
+        <v>429</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>765</v>
+        <v>478</v>
       </c>
       <c r="B178" t="s">
-        <v>700</v>
+        <v>413</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>766</v>
+        <v>479</v>
       </c>
       <c r="B179" t="s">
-        <v>767</v>
+        <v>480</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>768</v>
+        <v>481</v>
       </c>
       <c r="B180" t="s">
-        <v>704</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -5808,47 +4810,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>769</v>
+        <v>482</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>770</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>771</v>
+        <v>484</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>772</v>
+        <v>485</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>773</v>
+        <v>486</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>774</v>
+        <v>487</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>775</v>
+        <v>488</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>655</v>
+        <v>368</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -5856,15 +4858,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>777</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>778</v>
+        <v>491</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>779</v>
+        <v>492</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -5872,7 +4874,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>780</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -5887,7 +4889,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>781</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -5897,647 +4899,479 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>782</v>
+        <v>495</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>770</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>771</v>
+        <v>484</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>772</v>
+        <v>485</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>783</v>
+        <v>496</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>774</v>
+        <v>487</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>784</v>
+        <v>497</v>
       </c>
       <c r="C5" t="s">
-        <v>704</v>
+        <v>417</v>
       </c>
       <c r="D5" t="s">
-        <v>785</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="B6" t="s">
-        <v>786</v>
+        <v>499</v>
       </c>
       <c r="C6" t="s">
-        <v>706</v>
+        <v>419</v>
       </c>
       <c r="D6" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>205</v>
       </c>
       <c r="B7" t="s">
-        <v>788</v>
+        <v>501</v>
       </c>
       <c r="C7" t="s">
-        <v>689</v>
+        <v>502</v>
       </c>
       <c r="D7" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>209</v>
       </c>
       <c r="B8" t="s">
-        <v>789</v>
+        <v>503</v>
       </c>
       <c r="C8" t="s">
-        <v>691</v>
+        <v>277</v>
       </c>
       <c r="D8" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>790</v>
+        <v>505</v>
       </c>
       <c r="C9" t="s">
-        <v>564</v>
+        <v>467</v>
       </c>
       <c r="D9" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>791</v>
+        <v>506</v>
       </c>
       <c r="C10" t="s">
-        <v>754</v>
+        <v>507</v>
       </c>
       <c r="D10" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>213</v>
       </c>
       <c r="B11" t="s">
-        <v>792</v>
+        <v>508</v>
       </c>
       <c r="C11" t="s">
-        <v>716</v>
+        <v>509</v>
       </c>
       <c r="D11" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>214</v>
       </c>
       <c r="B12" t="s">
-        <v>793</v>
+        <v>510</v>
       </c>
       <c r="C12" t="s">
-        <v>794</v>
+        <v>511</v>
       </c>
       <c r="D12" t="s">
-        <v>787</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>506</v>
+        <v>214</v>
       </c>
       <c r="B13" t="s">
-        <v>795</v>
+        <v>512</v>
       </c>
       <c r="C13" t="s">
-        <v>796</v>
+        <v>469</v>
       </c>
       <c r="D13" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>506</v>
+        <v>214</v>
       </c>
       <c r="B14" t="s">
-        <v>797</v>
+        <v>513</v>
       </c>
       <c r="C14" t="s">
-        <v>798</v>
+        <v>514</v>
       </c>
       <c r="D14" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>506</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>799</v>
+        <v>515</v>
       </c>
       <c r="C15" t="s">
-        <v>800</v>
+        <v>471</v>
       </c>
       <c r="D15" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B16" t="s">
-        <v>802</v>
+        <v>516</v>
       </c>
       <c r="C16" t="s">
-        <v>756</v>
+        <v>473</v>
       </c>
       <c r="D16" t="s">
-        <v>801</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B17" t="s">
-        <v>803</v>
+        <v>517</v>
       </c>
       <c r="C17" t="s">
-        <v>804</v>
+        <v>518</v>
       </c>
       <c r="D17" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B18" t="s">
-        <v>805</v>
+        <v>519</v>
       </c>
       <c r="C18" t="s">
-        <v>806</v>
+        <v>415</v>
       </c>
       <c r="D18" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s">
-        <v>807</v>
+        <v>520</v>
       </c>
       <c r="C19" t="s">
-        <v>700</v>
+        <v>413</v>
       </c>
       <c r="D19" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>506</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>808</v>
+        <v>521</v>
       </c>
       <c r="C20" t="s">
-        <v>809</v>
+        <v>522</v>
       </c>
       <c r="D20" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>221</v>
       </c>
       <c r="B21" t="s">
-        <v>810</v>
+        <v>523</v>
       </c>
       <c r="C21" t="s">
-        <v>758</v>
+        <v>524</v>
       </c>
       <c r="D21" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s">
-        <v>811</v>
+        <v>525</v>
       </c>
       <c r="C22" t="s">
-        <v>760</v>
+        <v>526</v>
       </c>
       <c r="D22" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s">
-        <v>812</v>
+        <v>527</v>
       </c>
       <c r="C23" t="s">
-        <v>813</v>
+        <v>347</v>
       </c>
       <c r="D23" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>222</v>
       </c>
       <c r="B24" t="s">
-        <v>814</v>
+        <v>528</v>
       </c>
       <c r="C24" t="s">
-        <v>815</v>
+        <v>529</v>
       </c>
       <c r="D24" t="s">
-        <v>787</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>224</v>
       </c>
       <c r="B25" t="s">
-        <v>816</v>
+        <v>530</v>
       </c>
       <c r="C25" t="s">
-        <v>767</v>
+        <v>387</v>
       </c>
       <c r="D25" t="s">
-        <v>801</v>
+        <v>504</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>817</v>
+        <v>531</v>
       </c>
       <c r="C26" t="s">
-        <v>818</v>
+        <v>389</v>
       </c>
       <c r="D26" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>819</v>
+        <v>532</v>
       </c>
       <c r="C27" t="s">
-        <v>820</v>
+        <v>480</v>
       </c>
       <c r="D27" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>511</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s">
-        <v>821</v>
+        <v>533</v>
       </c>
       <c r="C28" t="s">
-        <v>702</v>
+        <v>391</v>
       </c>
       <c r="D28" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>511</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>822</v>
+        <v>534</v>
       </c>
       <c r="C29" t="s">
-        <v>823</v>
+        <v>396</v>
       </c>
       <c r="D29" t="s">
-        <v>801</v>
+        <v>504</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>511</v>
+        <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>824</v>
+        <v>535</v>
       </c>
       <c r="C30" t="s">
-        <v>825</v>
+        <v>398</v>
       </c>
       <c r="D30" t="s">
-        <v>785</v>
+        <v>504</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>511</v>
+        <v>228</v>
       </c>
       <c r="B31" t="s">
-        <v>826</v>
+        <v>536</v>
       </c>
       <c r="C31" t="s">
-        <v>827</v>
+        <v>400</v>
       </c>
       <c r="D31" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>511</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s">
-        <v>828</v>
+        <v>537</v>
       </c>
       <c r="C32" t="s">
-        <v>829</v>
+        <v>402</v>
       </c>
       <c r="D32" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>513</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s">
-        <v>830</v>
+        <v>538</v>
       </c>
       <c r="C33" t="s">
-        <v>831</v>
+        <v>404</v>
       </c>
       <c r="D33" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>513</v>
+        <v>230</v>
       </c>
       <c r="B34" t="s">
-        <v>832</v>
+        <v>539</v>
       </c>
       <c r="C34" t="s">
-        <v>634</v>
+        <v>429</v>
       </c>
       <c r="D34" t="s">
-        <v>801</v>
+        <v>498</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>513</v>
+        <v>230</v>
       </c>
       <c r="B35" t="s">
-        <v>833</v>
+        <v>540</v>
       </c>
       <c r="C35" t="s">
-        <v>834</v>
+        <v>541</v>
       </c>
       <c r="D35" t="s">
-        <v>785</v>
+        <v>500</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>513</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>835</v>
+        <v>542</v>
       </c>
       <c r="C36" t="s">
-        <v>836</v>
+        <v>543</v>
       </c>
       <c r="D36" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>515</v>
-      </c>
-      <c r="B37" t="s">
-        <v>837</v>
-      </c>
-      <c r="C37" t="s">
-        <v>674</v>
-      </c>
-      <c r="D37" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>515</v>
-      </c>
-      <c r="B38" t="s">
-        <v>838</v>
-      </c>
-      <c r="C38" t="s">
-        <v>676</v>
-      </c>
-      <c r="D38" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>515</v>
-      </c>
-      <c r="B39" t="s">
-        <v>839</v>
-      </c>
-      <c r="C39" t="s">
-        <v>840</v>
-      </c>
-      <c r="D39" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>515</v>
-      </c>
-      <c r="B40" t="s">
-        <v>841</v>
-      </c>
-      <c r="C40" t="s">
-        <v>842</v>
-      </c>
-      <c r="D40" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>517</v>
-      </c>
-      <c r="B41" t="s">
-        <v>843</v>
-      </c>
-      <c r="C41" t="s">
-        <v>678</v>
-      </c>
-      <c r="D41" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>517</v>
-      </c>
-      <c r="B42" t="s">
-        <v>844</v>
-      </c>
-      <c r="C42" t="s">
-        <v>683</v>
-      </c>
-      <c r="D42" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>517</v>
-      </c>
-      <c r="B43" t="s">
-        <v>845</v>
-      </c>
-      <c r="C43" t="s">
-        <v>846</v>
-      </c>
-      <c r="D43" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>517</v>
-      </c>
-      <c r="B44" t="s">
-        <v>847</v>
-      </c>
-      <c r="C44" t="s">
-        <v>848</v>
-      </c>
-      <c r="D44" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" t="s">
-        <v>849</v>
-      </c>
-      <c r="C45" t="s">
-        <v>685</v>
-      </c>
-      <c r="D45" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>26</v>
-      </c>
-      <c r="B46" t="s">
-        <v>850</v>
-      </c>
-      <c r="C46" t="s">
-        <v>687</v>
-      </c>
-      <c r="D46" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>26</v>
-      </c>
-      <c r="B47" t="s">
-        <v>851</v>
-      </c>
-      <c r="C47" t="s">
-        <v>852</v>
-      </c>
-      <c r="D47" t="s">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>26</v>
-      </c>
-      <c r="B48" t="s">
-        <v>853</v>
-      </c>
-      <c r="C48" t="s">
-        <v>854</v>
-      </c>
-      <c r="D48" t="s">
-        <v>801</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -6552,7 +5386,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>855</v>
+        <v>544</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6562,490 +5396,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>856</v>
+        <v>545</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>857</v>
+        <v>546</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>858</v>
+        <v>547</v>
       </c>
       <c r="B5" t="s">
-        <v>859</v>
+        <v>548</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>860</v>
+        <v>549</v>
       </c>
       <c r="B6" t="s">
-        <v>861</v>
+        <v>550</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>862</v>
+        <v>551</v>
       </c>
       <c r="B7" t="s">
-        <v>863</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>864</v>
+        <v>553</v>
       </c>
       <c r="B8" t="s">
-        <v>865</v>
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>866</v>
+        <v>555</v>
       </c>
       <c r="B9" t="s">
-        <v>867</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>868</v>
+        <v>557</v>
       </c>
       <c r="B10" t="s">
-        <v>780</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>869</v>
+        <v>558</v>
       </c>
       <c r="B11" t="s">
-        <v>780</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>870</v>
+        <v>559</v>
       </c>
       <c r="B12" t="s">
-        <v>871</v>
+        <v>560</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>872</v>
+        <v>561</v>
       </c>
       <c r="B13" t="s">
-        <v>873</v>
+        <v>562</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>874</v>
+        <v>563</v>
       </c>
       <c r="B14" t="s">
-        <v>875</v>
+        <v>564</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>876</v>
+        <v>565</v>
       </c>
       <c r="B15" t="s">
-        <v>877</v>
+        <v>566</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>878</v>
+        <v>567</v>
       </c>
       <c r="B16" t="s">
-        <v>879</v>
+        <v>568</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>880</v>
+        <v>569</v>
       </c>
       <c r="B17" t="s">
-        <v>881</v>
+        <v>570</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>882</v>
+        <v>571</v>
       </c>
       <c r="B18" t="s">
-        <v>883</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>884</v>
+        <v>573</v>
       </c>
       <c r="B19" t="s">
-        <v>883</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>885</v>
+        <v>574</v>
       </c>
       <c r="B20" t="s">
-        <v>886</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>887</v>
+        <v>576</v>
       </c>
       <c r="B21" t="s">
-        <v>886</v>
+        <v>575</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>888</v>
+        <v>577</v>
       </c>
       <c r="B22" t="s">
-        <v>889</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>890</v>
+        <v>579</v>
       </c>
       <c r="B23" t="s">
-        <v>775</v>
+        <v>488</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>891</v>
+        <v>580</v>
       </c>
       <c r="B24" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>892</v>
+        <v>581</v>
       </c>
       <c r="B25" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>893</v>
+        <v>582</v>
       </c>
       <c r="B26" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>894</v>
+        <v>583</v>
       </c>
       <c r="B27" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>895</v>
+        <v>584</v>
       </c>
       <c r="B28" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>896</v>
+        <v>585</v>
       </c>
       <c r="B29" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>897</v>
+        <v>586</v>
       </c>
       <c r="B30" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>898</v>
+        <v>587</v>
       </c>
       <c r="B31" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>899</v>
+        <v>588</v>
       </c>
       <c r="B32" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>900</v>
+        <v>589</v>
       </c>
       <c r="B33" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>901</v>
+        <v>590</v>
       </c>
       <c r="B34" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>902</v>
+        <v>591</v>
       </c>
       <c r="B35" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>903</v>
+        <v>592</v>
       </c>
       <c r="B36" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>904</v>
+        <v>593</v>
       </c>
       <c r="B37" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>905</v>
+        <v>594</v>
       </c>
       <c r="B38" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>906</v>
+        <v>595</v>
       </c>
       <c r="B39" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>907</v>
+        <v>596</v>
       </c>
       <c r="B40" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>908</v>
+        <v>597</v>
       </c>
       <c r="B41" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>909</v>
+        <v>598</v>
       </c>
       <c r="B42" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>910</v>
+        <v>599</v>
       </c>
       <c r="B43" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>911</v>
+        <v>600</v>
       </c>
       <c r="B44" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>912</v>
+        <v>601</v>
       </c>
       <c r="B45" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>913</v>
+        <v>602</v>
       </c>
       <c r="B46" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>914</v>
+        <v>603</v>
       </c>
       <c r="B47" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>915</v>
+        <v>604</v>
       </c>
       <c r="B48" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>916</v>
+        <v>605</v>
       </c>
       <c r="B49" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>917</v>
+        <v>606</v>
       </c>
       <c r="B50" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>918</v>
+        <v>607</v>
       </c>
       <c r="B51" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>919</v>
+        <v>608</v>
       </c>
       <c r="B52" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>920</v>
+        <v>609</v>
       </c>
       <c r="B53" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>921</v>
+        <v>610</v>
       </c>
       <c r="B54" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>922</v>
+        <v>611</v>
       </c>
       <c r="B55" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>923</v>
+        <v>612</v>
       </c>
       <c r="B56" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>924</v>
+        <v>613</v>
       </c>
       <c r="B57" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>925</v>
+        <v>614</v>
       </c>
       <c r="B58" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>926</v>
+        <v>615</v>
       </c>
       <c r="B59" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>927</v>
+        <v>616</v>
       </c>
       <c r="B60" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>928</v>
+        <v>617</v>
       </c>
       <c r="B61" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>929</v>
+        <v>618</v>
       </c>
       <c r="B62" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>930</v>
+        <v>619</v>
       </c>
       <c r="B63" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>931</v>
+        <v>620</v>
       </c>
       <c r="B64" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -7060,458 +5894,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>932</v>
+        <v>621</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>933</v>
+        <v>622</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>934</v>
+        <v>623</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>935</v>
+        <v>624</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>936</v>
+        <v>625</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>937</v>
+        <v>626</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>938</v>
+        <v>627</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>939</v>
+        <v>628</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>940</v>
+        <v>629</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>941</v>
+        <v>630</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>942</v>
+        <v>631</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>943</v>
+        <v>632</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>944</v>
+        <v>633</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>646</v>
+        <v>359</v>
       </c>
       <c r="B5" t="s">
-        <v>945</v>
+        <v>634</v>
       </c>
       <c r="C5" t="s">
-        <v>946</v>
+        <v>635</v>
       </c>
       <c r="D5" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E5" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F5" t="s">
-        <v>948</v>
+        <v>637</v>
       </c>
       <c r="G5" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H5" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I5" t="s">
-        <v>950</v>
+        <v>639</v>
       </c>
       <c r="J5" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K5" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>576</v>
+        <v>289</v>
       </c>
       <c r="B6" t="s">
-        <v>953</v>
+        <v>642</v>
       </c>
       <c r="C6" t="s">
-        <v>954</v>
+        <v>643</v>
       </c>
       <c r="D6" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E6" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F6" t="s">
-        <v>948</v>
+        <v>637</v>
       </c>
       <c r="G6" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H6" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I6" t="s">
-        <v>955</v>
+        <v>644</v>
       </c>
       <c r="J6" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K6" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>653</v>
+        <v>366</v>
       </c>
       <c r="B7" t="s">
-        <v>956</v>
+        <v>645</v>
       </c>
       <c r="C7" t="s">
-        <v>957</v>
+        <v>646</v>
       </c>
       <c r="D7" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E7" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F7" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
       <c r="G7" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H7" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I7" t="s">
-        <v>958</v>
+        <v>647</v>
       </c>
       <c r="J7" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K7" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>776</v>
+        <v>489</v>
       </c>
       <c r="B8" t="s">
-        <v>959</v>
+        <v>648</v>
       </c>
       <c r="C8" t="s">
-        <v>960</v>
+        <v>649</v>
       </c>
       <c r="D8" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E8" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F8" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
       <c r="G8" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H8" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I8" t="s">
-        <v>961</v>
+        <v>650</v>
       </c>
       <c r="J8" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K8" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>655</v>
+        <v>368</v>
       </c>
       <c r="B9" t="s">
-        <v>962</v>
+        <v>651</v>
       </c>
       <c r="C9" t="s">
-        <v>963</v>
+        <v>652</v>
       </c>
       <c r="D9" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E9" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F9" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
       <c r="G9" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H9" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I9" t="s">
-        <v>964</v>
+        <v>653</v>
       </c>
       <c r="J9" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K9" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
       <c r="B10" t="s">
-        <v>965</v>
+        <v>654</v>
       </c>
       <c r="C10" t="s">
-        <v>966</v>
+        <v>655</v>
       </c>
       <c r="D10" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E10" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F10" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
       <c r="G10" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H10" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I10" t="s">
-        <v>967</v>
+        <v>656</v>
       </c>
       <c r="J10" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K10" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>775</v>
+        <v>488</v>
       </c>
       <c r="B11" t="s">
-        <v>968</v>
+        <v>657</v>
       </c>
       <c r="C11" t="s">
-        <v>969</v>
+        <v>658</v>
       </c>
       <c r="D11" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E11" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F11" t="s">
-        <v>568</v>
+        <v>281</v>
       </c>
       <c r="G11" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H11" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I11" t="s">
-        <v>970</v>
+        <v>659</v>
       </c>
       <c r="J11" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K11" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>590</v>
+        <v>303</v>
       </c>
       <c r="B12" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="C12" t="s">
-        <v>971</v>
+        <v>660</v>
       </c>
       <c r="D12" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E12" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F12" t="s">
-        <v>608</v>
+        <v>321</v>
       </c>
       <c r="G12" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H12" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="J12" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K12" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>889</v>
+        <v>578</v>
       </c>
       <c r="B13" t="s">
-        <v>972</v>
+        <v>661</v>
       </c>
       <c r="C13" t="s">
-        <v>973</v>
+        <v>662</v>
       </c>
       <c r="D13" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E13" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F13" t="s">
-        <v>974</v>
+        <v>663</v>
       </c>
       <c r="G13" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H13" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I13" t="s">
-        <v>975</v>
+        <v>664</v>
       </c>
       <c r="J13" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K13" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>663</v>
+        <v>376</v>
       </c>
       <c r="B14" t="s">
-        <v>976</v>
+        <v>665</v>
       </c>
       <c r="C14" t="s">
-        <v>977</v>
+        <v>666</v>
       </c>
       <c r="D14" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E14" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F14" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="G14" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="H14" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="J14" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K14" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>886</v>
+        <v>575</v>
       </c>
       <c r="B15" t="s">
-        <v>978</v>
+        <v>667</v>
       </c>
       <c r="C15" t="s">
-        <v>979</v>
+        <v>668</v>
       </c>
       <c r="D15" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="E15" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="F15" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="G15" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="H15" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="J15" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K15" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>596</v>
+        <v>309</v>
       </c>
       <c r="B16" t="s">
-        <v>980</v>
+        <v>669</v>
       </c>
       <c r="C16" t="s">
-        <v>981</v>
+        <v>670</v>
       </c>
       <c r="D16" t="s">
-        <v>610</v>
+        <v>323</v>
       </c>
       <c r="E16" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="F16" t="s">
-        <v>608</v>
+        <v>321</v>
       </c>
       <c r="G16" t="s">
-        <v>947</v>
+        <v>636</v>
       </c>
       <c r="H16" t="s">
-        <v>949</v>
+        <v>638</v>
       </c>
       <c r="I16" t="s">
-        <v>982</v>
+        <v>671</v>
       </c>
       <c r="J16" t="s">
-        <v>951</v>
+        <v>640</v>
       </c>
       <c r="K16" t="s">
-        <v>952</v>
+        <v>641</v>
       </c>
     </row>
   </sheetData>
@@ -7526,22 +6360,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>983</v>
+        <v>672</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>984</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>985</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>986</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -7581,22 +6415,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>987</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>984</v>
+        <v>673</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>985</v>
+        <v>674</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>986</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -7611,44 +6445,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>988</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>770</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>936</v>
+        <v>625</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>935</v>
+        <v>624</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>773</v>
+        <v>486</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>989</v>
+        <v>678</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>990</v>
+        <v>679</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>991</v>
+        <v>680</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>992</v>
+        <v>681</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>944</v>
+        <v>633</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>993</v>
+        <v>682</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>994</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -7663,44 +6497,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>995</v>
+        <v>684</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>770</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>936</v>
+        <v>625</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>935</v>
+        <v>624</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>773</v>
+        <v>486</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>989</v>
+        <v>678</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>990</v>
+        <v>679</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>991</v>
+        <v>680</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>992</v>
+        <v>681</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>944</v>
+        <v>633</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>993</v>
+        <v>682</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>994</v>
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -7715,92 +6549,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>996</v>
+        <v>685</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>997</v>
+        <v>686</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>100</v>
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>998</v>
+        <v>687</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>998</v>
+        <v>687</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>998</v>
+        <v>687</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>120</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>999</v>
+        <v>688</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>999</v>
+        <v>688</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>999</v>
+        <v>688</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>1000</v>
+        <v>689</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>1000</v>
+        <v>689</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>1000</v>
+        <v>689</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>1000</v>
+        <v>689</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>142</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>1001</v>
+        <v>690</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>1002</v>
+        <v>691</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -7810,22 +6644,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>1003</v>
+        <v>692</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>1004</v>
+        <v>693</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>1004</v>
+        <v>693</v>
       </c>
     </row>
   </sheetData>
@@ -7840,7 +6674,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>1005</v>
+        <v>694</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7855,87 +6689,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>1006</v>
+        <v>695</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>1007</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>1008</v>
+        <v>697</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>1009</v>
+        <v>698</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1010</v>
+        <v>699</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>1011</v>
+        <v>700</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>1012</v>
+        <v>701</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>1013</v>
+        <v>702</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>1014</v>
+        <v>703</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>1015</v>
+        <v>704</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>1016</v>
+        <v>705</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>1017</v>
+        <v>706</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>1018</v>
+        <v>707</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>1019</v>
+        <v>708</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>1020</v>
+        <v>709</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>1021</v>
+        <v>710</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>1022</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
@@ -8000,7 +6834,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A244"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -8044,1053 +6878,298 @@
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>42</v>
+      <c r="A12" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>5</v>
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>64</v>
+      <c r="A38" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>67</v>
+      <c r="A41" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>71</v>
+      <c r="A45" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>74</v>
+      <c r="A48" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="1" t="s">
-        <v>11</v>
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>80</v>
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>86</v>
+      <c r="A64" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>90</v>
+      <c r="A68" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="71" spans="1:1">
-      <c r="A71" s="1" t="s">
-        <v>92</v>
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="120" spans="1:1">
-      <c r="A120" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="127" spans="1:1">
-      <c r="A127" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="140" spans="1:1">
-      <c r="A140" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="147" spans="1:1">
-      <c r="A147" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="157" spans="1:1">
-      <c r="A157" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="167" spans="1:1">
-      <c r="A167" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="174" spans="1:1">
-      <c r="A174" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="193" spans="1:1">
-      <c r="A193" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="200" spans="1:1">
-      <c r="A200" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1">
-      <c r="A201" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1">
-      <c r="A210" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="212" spans="1:1">
-      <c r="A212" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1">
-      <c r="A217" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1">
-      <c r="A220" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1">
-      <c r="A221" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="222" spans="1:1">
-      <c r="A222" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1">
-      <c r="A223" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1">
-      <c r="A224" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="226" spans="1:1">
-      <c r="A226" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="230" spans="1:1">
-      <c r="A230" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1">
-      <c r="A237" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1">
-      <c r="A240" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="244" spans="1:1">
-      <c r="A244" t="s">
-        <v>241</v>
+      <c r="A80" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -9105,47 +7184,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>249</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -9160,47 +7239,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>250</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>254</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>256</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>257</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -9210,12 +7289,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A243"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>258</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -9225,1082 +7304,327 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>259</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>260</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>261</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>262</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>264</v>
+      <c r="A9" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>265</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>266</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>267</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>268</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>269</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>270</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>271</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>272</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>273</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>274</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>276</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>5</v>
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>277</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>279</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>280</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>281</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>282</v>
+        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>284</v>
+      <c r="A35" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>285</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>287</v>
+      <c r="A38" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>288</v>
+        <v>133</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>289</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>291</v>
+      <c r="A42" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>292</v>
+        <v>135</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>294</v>
+      <c r="A45" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>295</v>
+        <v>136</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>296</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="1" t="s">
-        <v>11</v>
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>297</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>298</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>299</v>
+        <v>142</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>300</v>
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>301</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>302</v>
+        <v>145</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>303</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>304</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>306</v>
+      <c r="A61" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>307</v>
+        <v>148</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>308</v>
+        <v>149</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>310</v>
+      <c r="A65" s="1" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>311</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>92</v>
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>312</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>313</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>314</v>
+        <v>155</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>315</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>316</v>
+        <v>157</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>317</v>
+        <v>158</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>318</v>
+        <v>159</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" s="1" t="s">
-        <v>100</v>
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="103" spans="1:1">
-      <c r="A103" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="104" spans="1:1">
-      <c r="A104" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="105" spans="1:1">
-      <c r="A105" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="106" spans="1:1">
-      <c r="A106" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="107" spans="1:1">
-      <c r="A107" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="108" spans="1:1">
-      <c r="A108" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="109" spans="1:1">
-      <c r="A109" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="110" spans="1:1">
-      <c r="A110" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="111" spans="1:1">
-      <c r="A111" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="112" spans="1:1">
-      <c r="A112" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="113" spans="1:1">
-      <c r="A113" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="114" spans="1:1">
-      <c r="A114" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="115" spans="1:1">
-      <c r="A115" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="116" spans="1:1">
-      <c r="A116" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="117" spans="1:1">
-      <c r="A117" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="118" spans="1:1">
-      <c r="A118" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="119" spans="1:1">
-      <c r="A119" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="121" spans="1:1">
-      <c r="A121" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="122" spans="1:1">
-      <c r="A122" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="124" spans="1:1">
-      <c r="A124" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="125" spans="1:1">
-      <c r="A125" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="126" spans="1:1">
-      <c r="A126" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="128" spans="1:1">
-      <c r="A128" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="129" spans="1:1">
-      <c r="A129" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="130" spans="1:1">
-      <c r="A130" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="131" spans="1:1">
-      <c r="A131" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="132" spans="1:1">
-      <c r="A132" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="133" spans="1:1">
-      <c r="A133" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="134" spans="1:1">
-      <c r="A134" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="135" spans="1:1">
-      <c r="A135" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="136" spans="1:1">
-      <c r="A136" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="137" spans="1:1">
-      <c r="A137" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="138" spans="1:1">
-      <c r="A138" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="139" spans="1:1">
-      <c r="A139" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="141" spans="1:1">
-      <c r="A141" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="142" spans="1:1">
-      <c r="A142" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="143" spans="1:1">
-      <c r="A143" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="144" spans="1:1">
-      <c r="A144" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="145" spans="1:1">
-      <c r="A145" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="146" spans="1:1">
-      <c r="A146" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="148" spans="1:1">
-      <c r="A148" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="149" spans="1:1">
-      <c r="A149" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="150" spans="1:1">
-      <c r="A150" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="151" spans="1:1">
-      <c r="A151" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="152" spans="1:1">
-      <c r="A152" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="153" spans="1:1">
-      <c r="A153" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="154" spans="1:1">
-      <c r="A154" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="155" spans="1:1">
-      <c r="A155" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="156" spans="1:1">
-      <c r="A156" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="158" spans="1:1">
-      <c r="A158" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="159" spans="1:1">
-      <c r="A159" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="160" spans="1:1">
-      <c r="A160" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="161" spans="1:1">
-      <c r="A161" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="162" spans="1:1">
-      <c r="A162" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="163" spans="1:1">
-      <c r="A163" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="164" spans="1:1">
-      <c r="A164" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="165" spans="1:1">
-      <c r="A165" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="166" spans="1:1">
-      <c r="A166" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="168" spans="1:1">
-      <c r="A168" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="169" spans="1:1">
-      <c r="A169" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="170" spans="1:1">
-      <c r="A170" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="171" spans="1:1">
-      <c r="A171" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="172" spans="1:1">
-      <c r="A172" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="173" spans="1:1">
-      <c r="A173" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="175" spans="1:1">
-      <c r="A175" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="176" spans="1:1">
-      <c r="A176" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="177" spans="1:1">
-      <c r="A177" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="178" spans="1:1">
-      <c r="A178" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="179" spans="1:1">
-      <c r="A179" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="180" spans="1:1">
-      <c r="A180" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="181" spans="1:1">
-      <c r="A181" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="182" spans="1:1">
-      <c r="A182" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="183" spans="1:1">
-      <c r="A183" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="184" spans="1:1">
-      <c r="A184" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="185" spans="1:1">
-      <c r="A185" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="186" spans="1:1">
-      <c r="A186" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="187" spans="1:1">
-      <c r="A187" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="188" spans="1:1">
-      <c r="A188" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="189" spans="1:1">
-      <c r="A189" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="190" spans="1:1">
-      <c r="A190" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="191" spans="1:1">
-      <c r="A191" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="192" spans="1:1">
-      <c r="A192" s="1" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="194" spans="1:1">
-      <c r="A194" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="195" spans="1:1">
-      <c r="A195" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="196" spans="1:1">
-      <c r="A196" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="197" spans="1:1">
-      <c r="A197" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="198" spans="1:1">
-      <c r="A198" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="199" spans="1:1">
-      <c r="A199" s="1" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="201" spans="1:1">
-      <c r="A201" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="202" spans="1:1">
-      <c r="A202" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="203" spans="1:1">
-      <c r="A203" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="204" spans="1:1">
-      <c r="A204" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="205" spans="1:1">
-      <c r="A205" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="206" spans="1:1">
-      <c r="A206" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="207" spans="1:1">
-      <c r="A207" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="208" spans="1:1">
-      <c r="A208" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="209" spans="1:1">
-      <c r="A209" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="210" spans="1:1">
-      <c r="A210" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="211" spans="1:1">
-      <c r="A211" s="1" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="213" spans="1:1">
-      <c r="A213" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="214" spans="1:1">
-      <c r="A214" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="215" spans="1:1">
-      <c r="A215" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="216" spans="1:1">
-      <c r="A216" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="217" spans="1:1">
-      <c r="A217" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="218" spans="1:1">
-      <c r="A218" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="219" spans="1:1">
-      <c r="A219" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="220" spans="1:1">
-      <c r="A220" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="221" spans="1:1">
-      <c r="A221" s="1" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="223" spans="1:1">
-      <c r="A223" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="224" spans="1:1">
-      <c r="A224" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="225" spans="1:1">
-      <c r="A225" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="227" spans="1:1">
-      <c r="A227" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="228" spans="1:1">
-      <c r="A228" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="229" spans="1:1">
-      <c r="A229" s="1" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="231" spans="1:1">
-      <c r="A231" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="232" spans="1:1">
-      <c r="A232" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="233" spans="1:1">
-      <c r="A233" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="234" spans="1:1">
-      <c r="A234" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="235" spans="1:1">
-      <c r="A235" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="236" spans="1:1">
-      <c r="A236" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="237" spans="1:1">
-      <c r="A237" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="238" spans="1:1">
-      <c r="A238" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="239" spans="1:1">
-      <c r="A239" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="240" spans="1:1">
-      <c r="A240" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="241" spans="1:1">
-      <c r="A241" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="242" spans="1:1">
-      <c r="A242" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="243" spans="1:1">
-      <c r="A243" t="s">
-        <v>451</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -30,31 +30,32 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
-    <sheet name="PAD REPORT" sheetId="27" r:id="rId27"/>
-    <sheet name="REGISTER ADDRESS REPORT" sheetId="28" r:id="rId28"/>
-    <sheet name="REGISTER DETAIL ADDRESS REPORT" sheetId="29" r:id="rId29"/>
-    <sheet name="FACTORY ADDRESS REPORT" sheetId="30" r:id="rId30"/>
-    <sheet name="ACCURACY ADDRESS REPORT" sheetId="31" r:id="rId31"/>
-    <sheet name="DFT PROBE ADDRESS REPORT" sheetId="32" r:id="rId32"/>
-    <sheet name="DFT HIJACK ADDRESS REPORT" sheetId="33" r:id="rId33"/>
-    <sheet name="DFT DBUF ADDRESS REPORT" sheetId="34" r:id="rId34"/>
-    <sheet name="TMA SUMMARY REPORT (DFTs)" sheetId="35" r:id="rId35"/>
-    <sheet name="DFT CELL GLOBAL ADDRESS REPORT" sheetId="36" r:id="rId36"/>
-    <sheet name="DFT CELL DBUF ADDRESS REPORT" sheetId="37" r:id="rId37"/>
-    <sheet name="DFT CELL ADDRESS REPORT (Rich)" sheetId="38" r:id="rId38"/>
-    <sheet name="DFT dftprobe Checker" sheetId="39" r:id="rId39"/>
-    <sheet name="DFT dfthijack Checker" sheetId="40" r:id="rId40"/>
-    <sheet name="Pad Checker" sheetId="41" r:id="rId41"/>
+    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
+    <sheet name="PAD REPORT" sheetId="28" r:id="rId28"/>
+    <sheet name="REGISTER ADDRESS REPORT" sheetId="29" r:id="rId29"/>
+    <sheet name="REGISTER DETAIL ADDRESS REPORT" sheetId="30" r:id="rId30"/>
+    <sheet name="FACTORY ADDRESS REPORT" sheetId="31" r:id="rId31"/>
+    <sheet name="ACCURACY ADDRESS REPORT" sheetId="32" r:id="rId32"/>
+    <sheet name="DFT PROBE ADDRESS REPORT" sheetId="33" r:id="rId33"/>
+    <sheet name="DFT HIJACK ADDRESS REPORT" sheetId="34" r:id="rId34"/>
+    <sheet name="DFT DBUF ADDRESS REPORT" sheetId="35" r:id="rId35"/>
+    <sheet name="TMA SUMMARY REPORT (DFTs)" sheetId="36" r:id="rId36"/>
+    <sheet name="DFT CELL GLOBAL ADDRESS REPORT" sheetId="37" r:id="rId37"/>
+    <sheet name="DFT CELL DBUF ADDRESS REPORT" sheetId="38" r:id="rId38"/>
+    <sheet name="DFT CELL ADDRESS REPORT (Rich)" sheetId="39" r:id="rId39"/>
+    <sheet name="DFT dftprobe Checker" sheetId="40" r:id="rId40"/>
+    <sheet name="DFT dfthijack Checker" sheetId="41" r:id="rId41"/>
+    <sheet name="Pad Checker" sheetId="42" r:id="rId42"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="604">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -146,10 +147,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -161,7 +162,142 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ</t>
+  </si>
+  <si>
+    <t>Floating pin XceleraCORE.PORB97836(PORB97836)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -174,6 +310,135 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>PORB97836 - {"path": "XWALTZ,XceleraCORE", "instance": "XceleraCORE", "symbol": "PORB97836", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -294,67 +559,13 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
-  </si>
-  <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
     <t>DRM Efficiency Summary</t>
   </si>
   <si>
     <t>Summary</t>
   </si>
   <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
   </si>
   <si>
     <t>DFT Efficiency</t>
@@ -363,9 +574,6 @@
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
-  </si>
-  <si>
     <t>Project Summary</t>
   </si>
   <si>
@@ -1113,27 +1321,51 @@
     <t>measure_reset_command</t>
   </si>
   <si>
+    <t>DRM Summary</t>
+  </si>
+  <si>
+    <t>Addresses</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Instance</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
     <t>Register Summary</t>
   </si>
   <si>
     <t>DFT Summary</t>
   </si>
   <si>
-    <t>Addresses</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Instance</t>
-  </si>
-  <si>
     <t>TMA</t>
   </si>
   <si>
-    <t>type</t>
-  </si>
-  <si>
     <t>Nesto Usage Report</t>
   </si>
   <si>
@@ -1155,30 +1387,27 @@
     <t>193</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>122</t>
+    <t>114</t>
   </si>
   <si>
     <t>nor3</t>
   </si>
   <si>
-    <t>61</t>
-  </si>
-  <si>
     <t>delayfixed</t>
   </si>
   <si>
@@ -1221,10 +1450,10 @@
     <t>16</t>
   </si>
   <si>
-    <t>drmmodule</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>tie</t>
@@ -1242,15 +1471,9 @@
     <t>9</t>
   </si>
   <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
     <t>resistor</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>oneshot</t>
   </si>
   <si>
@@ -1299,6 +1522,9 @@
     <t>capacitorfixed</t>
   </si>
   <si>
+    <t>PEBBLEtiehi</t>
+  </si>
+  <si>
     <t>voltage2current</t>
   </si>
   <si>
@@ -1470,9 +1696,6 @@
     <t>ESDcore6 SYNC -&gt; GESD</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>FB</t>
   </si>
   <si>
@@ -1518,30 +1741,6 @@
     <t>ESDdiodeB2B PGND -&gt; GESD</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>DFTSDA</t>
-  </si>
-  <si>
-    <t>i2c_data_inout</t>
-  </si>
-  <si>
-    <t>ESDcore6 DFTSDA -&gt; GESD</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>DFTSCL</t>
-  </si>
-  <si>
-    <t>i2c_input_clock</t>
-  </si>
-  <si>
-    <t>ESDcore6 DFTSCL -&gt; GESD</t>
-  </si>
-  <si>
     <t>REGISTER ADDRESS REPORT</t>
   </si>
   <si>
@@ -1560,9 +1759,6 @@
     <t>FACTORY ADDRESS REPORT</t>
   </si>
   <si>
-    <t>TMB</t>
-  </si>
-  <si>
     <t>Bank</t>
   </si>
   <si>
@@ -1581,348 +1777,9 @@
     <t>rdl_data</t>
   </si>
   <si>
-    <t>Adjust_Minimum_off_time</t>
-  </si>
-  <si>
-    <t>CLOCKofftime</t>
-  </si>
-  <si>
-    <t>3:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,drm_hex0x02</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Adjust_Minimum_off_time', 'name': 'CLOCKofftime', 'enums': [{'desc': '0.0ns', 'name': 'Threshold_0.0ns'}, {'desc': '8.0ns', 'name': 'Threshold_8.0ns'}, {'desc': '16.0ns', 'name': 'Threshold_16.0ns'}, {'desc': '24.0ns', 'name': 'Threshold_24.0ns'}, {'desc': '32.0ns', 'name': 'Threshold_32.0ns'}, {'desc': '40.0ns', 'name': 'Threshold_40.0ns'}, {'desc': '48.0ns', 'name': 'Threshold_48.0ns'}, {'desc': '56.0ns', 'name': 'Threshold_56.0ns'}, {'desc': '64.0ns', 'name': 'Threshold_64.0ns'}, {'desc': '72.0ns', 'name': 'Threshold_72.0ns'}, {'desc': '80.0ns', 'name': 'Threshold_80.0ns'}, {'desc': '88.0ns', 'name': 'Threshold_88.0ns'}, {'desc': '96.0ns', 'name': 'Threshold_96.0ns'}, {'desc': '104.0ns', 'name': 'Threshold_104.0ns'}, {'desc': '112.0ns', 'name': 'Threshold_112.0ns'}, {'desc': '120.0ns', 'name': 'Threshold_120.0ns'}], 'function': 'range', 'range_lsb': 8.0, 'readwrite': 'readwrite', 'range_start': 0.0, 'range_units': 'ns'}]}</t>
-  </si>
-  <si>
-    <t>Algorithm5p9_STATE_control</t>
-  </si>
-  <si>
-    <t>Algorithm5p9_statecontrol</t>
-  </si>
-  <si>
-    <t>4:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,drm_hex0x03</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Algorithm5p9_STATE_control', 'name': 'Algorithm5p9_statecontrol', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>CONTROL_configuration</t>
-  </si>
-  <si>
-    <t>CONTROLconfiguration</t>
-  </si>
-  <si>
-    <t>2:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCONTROL,drm_hex0x04</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Operating_Mode', 'name': 'Operating_Mode', 'enums': [{'desc': 'Discontinous', 'name': 'Discontinous'}, {'desc': 'Continous', 'name': 'Continous'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'Blank_bottom', 'name': 'Blank_bottom', 'enums': [{'desc': 'Maximum_on_time_fault', 'name': 'Maximum_on_time_fault'}, {'desc': 'Blank_maximum_on_time', 'name': 'Blank_maximum_on_time'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'Blank_refresh', 'name': 'Blank_refresh', 'enums': [{'desc': 'Refresh_with_ok_driver', 'name': 'Refresh_with_ok_driver'}, {'desc': 'Blank_refresh', 'name': 'Blank_refresh'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>BBM_Status_Enabled</t>
-  </si>
-  <si>
-    <t>BBMstatus</t>
-  </si>
-  <si>
-    <t>0x05</t>
-  </si>
-  <si>
-    <t>1:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBBM,drm_hex0x05</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Bottom_status', 'name': 'Bottom_status', 'enums': [{'desc': 'Enable', 'name': 'Enable'}, {'desc': 'Disable', 'name': 'Disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'Top_status', 'name': 'Top_status', 'enums': [{'desc': 'Enable', 'name': 'Enable'}, {'desc': 'Disable', 'name': 'Disable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>TOP_Switch_on_delay</t>
-  </si>
-  <si>
-    <t>TOPSWITCHstatusDELAY</t>
-  </si>
-  <si>
-    <t>6:2</t>
-  </si>
-  <si>
-    <t>{'nesto': 'timingskew_d7d32aa0', 'fields': [{'desc': 'TOPSWITCHstatusDELAY', 'name': 'TOPSWITCHstatusDELAY', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>BOT_Switch_on_delay</t>
-  </si>
-  <si>
-    <t>BOTTOMSWITCHstatusDELAY</t>
-  </si>
-  <si>
-    <t>{'nesto': 'timingskew_b5de11eb', 'fields': [{'desc': 'BOTTOMSWITCHstatusDELAY', 'name': 'BOTTOMSWITCHstatusDELAY', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Highside_Current_Limit_Trim</t>
-  </si>
-  <si>
-    <t>TOPSWITCHaccuracy</t>
-  </si>
-  <si>
-    <t>0x07</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XTOPSW,drm_hex0x07</t>
-  </si>
-  <si>
-    <t>{'nesto': 'currentlimitfet_e27944c0', 'fields': [{'desc': 'TOPSWITCHaccuracy', 'name': 'TOPSWITCHaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Disable_slope_current</t>
-  </si>
-  <si>
-    <t>DISABLEslope</t>
-  </si>
-  <si>
-    <t>5:5</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'SLOPE_curent', 'name': 'SLOPE_curent', 'enums': [{'desc': 'enable', 'name': 'enable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>FAULTMANAGER_configuration</t>
-  </si>
-  <si>
-    <t>FAULTMANAGERconfiguration</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,drm_hex0x09</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'HICCUPmode', 'name': 'HICCUPmode', 'enums': [{'desc': 'Disable', 'name': 'Disable'}, {'desc': 'Enable', 'name': 'Enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'BLANKthermal', 'name': 'BLANKthermal', 'enums': [{'desc': 'Disable', 'name': 'Disable'}, {'desc': 'Enable', 'name': 'Enable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>REGUALTION_Configure_DEBUG_controls</t>
-  </si>
-  <si>
-    <t>REGULATIONtestmode</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XDEBUG,drm_hex0x0A</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'VC_override', 'name': 'VC_override', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'VSS_override', 'name': 'VSS_override', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'VSS_status', 'name': 'VSS_status', 'enums': [{'desc': 'Low', 'name': 'Low'}, {'desc': 'High', 'name': 'High'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Compensation_Resistor</t>
-  </si>
-  <si>
-    <t>RZCOMP</t>
-  </si>
-  <si>
-    <t>0x0B</t>
-  </si>
-  <si>
-    <t>XWALTZ,XREGULATION,XMAIN,XCOMPENSATION,drm_hex0x0B</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Compensation_Resistor', 'name': 'RZCOMP', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Compensation_Gain_resistance</t>
-  </si>
-  <si>
-    <t>GAINCOMP</t>
-  </si>
-  <si>
-    <t>4:3</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Compensation_Gain_resistance', 'name': 'GAINCOMP', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Compensation_Capacitor</t>
-  </si>
-  <si>
-    <t>CZCOMP</t>
-  </si>
-  <si>
-    <t>7:5</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Compensation_Capacitor', 'name': 'CZCOMP', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Regulation_output_ripple_in_DCM_mode</t>
-  </si>
-  <si>
-    <t>DCM_Output_Rripple</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN,drm_hex0x0C</t>
-  </si>
-  <si>
-    <t>{'nesto': 'comparatornoctlpins_1b4420c5', 'fields': [{'desc': 'DCM_Output_Rripple', 'name': 'DCM_Output_Rripple', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>SEQUENCER1waltz_Rev1_STATE_control</t>
-  </si>
-  <si>
-    <t>SEQUENCER1waltz_Rev1_statecontrol</t>
-  </si>
-  <si>
-    <t>0x0D</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,drm_hex0x0D</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'SEQUENCER1waltz_Rev1_STATE_control', 'name': 'SEQUENCER1waltz_Rev1_statecontrol', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Curvature_Correction_Accuracy</t>
-  </si>
-  <si>
-    <t>REFCCacc</t>
-  </si>
-  <si>
-    <t>0x0E</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN,drm_hex0x0E</t>
-  </si>
-  <si>
-    <t>{'nesto': 'reference_4fa591be', 'fields': [{'desc': 'REFCCacc', 'name': 'REFCCacc', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Softstart_configuration</t>
-  </si>
-  <si>
-    <t>SOFTSTARTconfiguration</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,drm_hex0x0F</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Softstart_time', 'name': 'Softstart_time', 'enums': [{'desc': '4ms', 'name': '4ms'}, {'desc': '1ms', 'name': '1ms'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'Halfway', 'name': 'Halfway', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
     <t>ACCURACY ADDRESS REPORT</t>
   </si>
   <si>
-    <t>CLOCK_accuracy_at_400KHz_50K</t>
-  </si>
-  <si>
-    <t>CLOCKaccuracy</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN,drm_hex0x01</t>
-  </si>
-  <si>
-    <t>{'nesto': 'oscillator_d9a22b83', 'fields': [{'desc': 'CLOCKaccuracy', 'name': 'CLOCKaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Lowside_Negative_Current_Accuracy</t>
-  </si>
-  <si>
-    <t>botswinegacc</t>
-  </si>
-  <si>
-    <t>0x06</t>
-  </si>
-  <si>
-    <t>7:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW,drm_hex0x06</t>
-  </si>
-  <si>
-    <t>{'nesto': 'currentlimitfet_282c42a8', 'fields': [{'desc': 'botswinegacc', 'name': 'botswinegacc', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>BottomSW_Zcross</t>
-  </si>
-  <si>
-    <t>botswzcrossacc</t>
-  </si>
-  <si>
-    <t>{'nesto': 'currentlimitfet_bdeab8a2', 'fields': [{'desc': 'botswzcrossacc', 'name': 'botswzcrossacc', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Lowside_Zero_Cross_Accuracy</t>
-  </si>
-  <si>
-    <t>botswipeakacc</t>
-  </si>
-  <si>
-    <t>{'nesto': 'currentlimitfet_2899e616', 'fields': [{'desc': 'botswipeakacc', 'name': 'botswipeakacc', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Trim_Slope_Comp_Amplitude</t>
-  </si>
-  <si>
-    <t>SLOPECOMPENSATIONaccuracy</t>
-  </si>
-  <si>
-    <t>{'nesto': 'slopecomp_00a4cb3c', 'fields': [{'desc': 'SLOPECOMPENSATIONaccuracy', 'name': 'SLOPECOMPENSATIONaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Thermal_shutdowen</t>
-  </si>
-  <si>
-    <t>THERMALaccuracy</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN,drm_hex0x08</t>
-  </si>
-  <si>
-    <t>{'nesto': 'thermal_b84c0fbd', 'fields': [{'desc': 'THERMALaccuracy', 'name': 'THERMALaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Voltage_Control_Node_Clamp_Accuracy_to_3V</t>
-  </si>
-  <si>
-    <t>VCclampACCURACY</t>
-  </si>
-  <si>
-    <t>{'nesto': 'clamp_57e24cde', 'fields': [{'desc': 'VCclampACCURACY', 'name': 'VCclampACCURACY', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>FB_Reference_buffer_Accuracy</t>
-  </si>
-  <si>
-    <t>REFbufferACCURACY</t>
-  </si>
-  <si>
-    <t>6:0</t>
-  </si>
-  <si>
-    <t>{'nesto': 'vbuffer_602daa59', 'fields': [{'desc': 'REFbufferACCURACY', 'name': 'REFbufferACCURACY', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>GMaccuracy</t>
-  </si>
-  <si>
-    <t>{'nesto': 'gm_6be6af5d', 'fields': [{'desc': 'GMaccuracy', 'name': 'GMaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>5:0</t>
-  </si>
-  <si>
-    <t>VCC_5V_Accuracy</t>
-  </si>
-  <si>
-    <t>VCCaccuracy</t>
-  </si>
-  <si>
-    <t>{'nesto': 'vbias_06fccf36', 'fields': [{'desc': 'VCCaccuracy', 'name': 'VCCaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
     <t>DFT PROBE ADDRESS REPORT</t>
   </si>
   <si>
@@ -1944,7 +1801,7 @@
     <t>TMA SUMMARY REPORT (DFTs)</t>
   </si>
   <si>
-    <t>Slave Address 0x54</t>
+    <t>Slave Address 0</t>
   </si>
   <si>
     <t>DFT CELL GLOBAL ADDRESS REPORT</t>
@@ -2384,7 +2241,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2404,7 +2261,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2419,7 +2276,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2434,17 +2291,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2459,12 +2316,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2479,17 +2336,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2504,12 +2361,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2524,7 +2381,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2544,127 +2401,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2674,162 +2531,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2844,17 +2556,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3079,7 +2791,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3099,17 +2811,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -3124,52 +2836,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3184,81 +2896,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>187</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>190</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>191</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3266,1268 +2978,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>133</v>
+        <v>202</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>136</v>
+        <v>205</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>206</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>208</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>211</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>216</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>223</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>225</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>228</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>160</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>161</v>
+        <v>230</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>231</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>164</v>
+        <v>233</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>235</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>236</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>227</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>238</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>239</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>240</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>173</v>
+        <v>242</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>174</v>
+        <v>243</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="B55" t="s">
-        <v>176</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>246</v>
       </c>
       <c r="B56" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>180</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>181</v>
+        <v>250</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>182</v>
+        <v>251</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>183</v>
+        <v>252</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>184</v>
+        <v>253</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>185</v>
+        <v>254</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>255</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>187</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>188</v>
+        <v>257</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>189</v>
+        <v>258</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>191</v>
+        <v>260</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>193</v>
+        <v>262</v>
       </c>
       <c r="B69" t="s">
-        <v>190</v>
+        <v>259</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>263</v>
       </c>
       <c r="B70" t="s">
-        <v>192</v>
+        <v>261</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>195</v>
+        <v>264</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>265</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>197</v>
+        <v>266</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>198</v>
+        <v>267</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>199</v>
+        <v>268</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>269</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>270</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>271</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>272</v>
       </c>
       <c r="B80" t="s">
-        <v>204</v>
+        <v>273</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>275</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>276</v>
       </c>
       <c r="B82" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="B83" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="B84" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>210</v>
+        <v>279</v>
       </c>
       <c r="B85" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>211</v>
+        <v>280</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>212</v>
+        <v>281</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>213</v>
+        <v>282</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>283</v>
       </c>
       <c r="B89" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>215</v>
+        <v>284</v>
       </c>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>285</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>217</v>
+        <v>286</v>
       </c>
       <c r="B91" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>218</v>
+        <v>287</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>219</v>
+        <v>288</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>220</v>
+        <v>289</v>
       </c>
       <c r="B94" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>221</v>
+        <v>290</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>224</v>
+        <v>293</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="B99" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="B101" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>229</v>
+        <v>298</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="B103" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>300</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>301</v>
       </c>
       <c r="B106" t="s">
-        <v>233</v>
+        <v>302</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>234</v>
+        <v>303</v>
       </c>
       <c r="B107" t="s">
-        <v>235</v>
+        <v>304</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>236</v>
+        <v>305</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>306</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>238</v>
+        <v>307</v>
       </c>
       <c r="B109" t="s">
-        <v>239</v>
+        <v>308</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>240</v>
+        <v>309</v>
       </c>
       <c r="B110" t="s">
-        <v>241</v>
+        <v>310</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>242</v>
+        <v>311</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>312</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>313</v>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>314</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>246</v>
+        <v>315</v>
       </c>
       <c r="B113" t="s">
-        <v>172</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>247</v>
+        <v>316</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>115</v>
+        <v>184</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="B116" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>318</v>
       </c>
       <c r="B117" t="s">
-        <v>250</v>
+        <v>319</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>251</v>
+        <v>320</v>
       </c>
       <c r="B118" t="s">
-        <v>252</v>
+        <v>321</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>253</v>
+        <v>322</v>
       </c>
       <c r="B119" t="s">
-        <v>254</v>
+        <v>323</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>255</v>
+        <v>324</v>
       </c>
       <c r="B120" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>257</v>
+        <v>326</v>
       </c>
       <c r="B121" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>259</v>
+        <v>328</v>
       </c>
       <c r="B122" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>261</v>
+        <v>330</v>
       </c>
       <c r="B123" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>262</v>
+        <v>331</v>
       </c>
       <c r="B124" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>263</v>
+        <v>332</v>
       </c>
       <c r="B125" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>264</v>
+        <v>333</v>
       </c>
       <c r="B126" t="s">
-        <v>265</v>
+        <v>334</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>266</v>
+        <v>335</v>
       </c>
       <c r="B127" t="s">
-        <v>267</v>
+        <v>336</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>268</v>
+        <v>337</v>
       </c>
       <c r="B128" t="s">
-        <v>269</v>
+        <v>338</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>270</v>
+        <v>339</v>
       </c>
       <c r="B129" t="s">
-        <v>271</v>
+        <v>340</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>272</v>
+        <v>341</v>
       </c>
       <c r="B130" t="s">
-        <v>273</v>
+        <v>342</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>224</v>
+        <v>293</v>
       </c>
       <c r="B131" t="s">
-        <v>274</v>
+        <v>343</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>225</v>
+        <v>294</v>
       </c>
       <c r="B132" t="s">
-        <v>275</v>
+        <v>344</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>227</v>
+        <v>296</v>
       </c>
       <c r="B133" t="s">
-        <v>276</v>
+        <v>345</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>226</v>
+        <v>295</v>
       </c>
       <c r="B134" t="s">
-        <v>277</v>
+        <v>346</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>278</v>
+        <v>347</v>
       </c>
       <c r="B135" t="s">
-        <v>163</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>279</v>
+        <v>348</v>
       </c>
       <c r="B136" t="s">
-        <v>280</v>
+        <v>349</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>281</v>
+        <v>350</v>
       </c>
       <c r="B137" t="s">
-        <v>282</v>
+        <v>351</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>283</v>
+        <v>352</v>
       </c>
       <c r="B138" t="s">
-        <v>284</v>
+        <v>353</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
       <c r="B139" t="s">
-        <v>286</v>
+        <v>355</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>287</v>
+        <v>356</v>
       </c>
       <c r="B140" t="s">
-        <v>288</v>
+        <v>357</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>289</v>
+        <v>358</v>
       </c>
       <c r="B141" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>290</v>
+        <v>359</v>
       </c>
       <c r="B142" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>291</v>
+        <v>360</v>
       </c>
       <c r="B143" t="s">
-        <v>260</v>
+        <v>329</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>292</v>
+        <v>361</v>
       </c>
       <c r="B144" t="s">
-        <v>265</v>
+        <v>334</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>293</v>
+        <v>362</v>
       </c>
       <c r="B145" t="s">
-        <v>267</v>
+        <v>336</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>294</v>
+        <v>363</v>
       </c>
       <c r="B146" t="s">
-        <v>269</v>
+        <v>338</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>295</v>
+        <v>364</v>
       </c>
       <c r="B147" t="s">
-        <v>271</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>296</v>
+        <v>365</v>
       </c>
       <c r="B148" t="s">
-        <v>273</v>
+        <v>342</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>297</v>
+        <v>366</v>
       </c>
       <c r="B149" t="s">
-        <v>298</v>
+        <v>367</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>299</v>
+        <v>368</v>
       </c>
       <c r="B150" t="s">
-        <v>300</v>
+        <v>369</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>301</v>
+        <v>370</v>
       </c>
       <c r="B151" t="s">
-        <v>302</v>
+        <v>371</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>303</v>
+        <v>372</v>
       </c>
       <c r="B152" t="s">
-        <v>304</v>
+        <v>373</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>305</v>
+        <v>374</v>
       </c>
       <c r="B153" t="s">
-        <v>306</v>
+        <v>375</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>307</v>
+        <v>376</v>
       </c>
       <c r="B154" t="s">
-        <v>308</v>
+        <v>377</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>309</v>
+        <v>378</v>
       </c>
       <c r="B155" t="s">
-        <v>310</v>
+        <v>379</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>311</v>
+        <v>380</v>
       </c>
       <c r="B156" t="s">
-        <v>312</v>
+        <v>381</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>313</v>
+        <v>382</v>
       </c>
       <c r="B157" t="s">
-        <v>314</v>
+        <v>383</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>315</v>
+        <v>384</v>
       </c>
       <c r="B158" t="s">
-        <v>316</v>
+        <v>385</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>317</v>
+        <v>386</v>
       </c>
       <c r="B159" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>319</v>
+        <v>388</v>
       </c>
       <c r="B160" t="s">
-        <v>320</v>
+        <v>389</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>321</v>
+        <v>390</v>
       </c>
       <c r="B161" t="s">
-        <v>322</v>
+        <v>391</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>323</v>
+        <v>392</v>
       </c>
       <c r="B162" t="s">
-        <v>324</v>
+        <v>393</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>325</v>
+        <v>394</v>
       </c>
       <c r="B163" t="s">
-        <v>326</v>
+        <v>395</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>327</v>
+        <v>396</v>
       </c>
       <c r="B164" t="s">
-        <v>328</v>
+        <v>397</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>329</v>
+        <v>398</v>
       </c>
       <c r="B165" t="s">
-        <v>330</v>
+        <v>399</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>331</v>
+        <v>400</v>
       </c>
       <c r="B166" t="s">
-        <v>304</v>
+        <v>373</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>332</v>
+        <v>401</v>
       </c>
       <c r="B167" t="s">
-        <v>286</v>
+        <v>355</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>333</v>
+        <v>402</v>
       </c>
       <c r="B168" t="s">
-        <v>288</v>
+        <v>357</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>334</v>
+        <v>403</v>
       </c>
       <c r="B169" t="s">
-        <v>146</v>
+        <v>215</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>335</v>
+        <v>404</v>
       </c>
       <c r="B170" t="s">
-        <v>336</v>
+        <v>405</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>337</v>
+        <v>406</v>
       </c>
       <c r="B171" t="s">
-        <v>338</v>
+        <v>407</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>339</v>
+        <v>408</v>
       </c>
       <c r="B172" t="s">
-        <v>340</v>
+        <v>409</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>341</v>
+        <v>410</v>
       </c>
       <c r="B173" t="s">
-        <v>342</v>
+        <v>411</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>343</v>
+        <v>412</v>
       </c>
       <c r="B174" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>344</v>
+        <v>413</v>
       </c>
       <c r="B175" t="s">
-        <v>256</v>
+        <v>325</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>345</v>
+        <v>414</v>
       </c>
       <c r="B176" t="s">
-        <v>258</v>
+        <v>327</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>346</v>
+        <v>415</v>
       </c>
       <c r="B177" t="s">
-        <v>298</v>
+        <v>367</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>347</v>
+        <v>416</v>
       </c>
       <c r="B178" t="s">
-        <v>282</v>
+        <v>351</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>348</v>
+        <v>417</v>
       </c>
       <c r="B179" t="s">
-        <v>349</v>
+        <v>418</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>350</v>
+        <v>419</v>
       </c>
       <c r="B180" t="s">
-        <v>286</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -4537,12 +4249,76 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4552,31 +4328,12 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>357</v>
+        <v>432</v>
       </c>
     </row>
   </sheetData>
@@ -4586,473 +4343,31 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>359</v>
+        <v>422</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>361</v>
-      </c>
-      <c r="B5" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>363</v>
-      </c>
-      <c r="B6" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>365</v>
-      </c>
-      <c r="B7" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>367</v>
-      </c>
-      <c r="B8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>369</v>
-      </c>
-      <c r="B9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>371</v>
-      </c>
-      <c r="B10" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>373</v>
-      </c>
-      <c r="B11" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>375</v>
-      </c>
-      <c r="B12" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>377</v>
-      </c>
-      <c r="B13" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>379</v>
-      </c>
-      <c r="B14" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>381</v>
-      </c>
-      <c r="B15" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>383</v>
-      </c>
-      <c r="B16" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>385</v>
-      </c>
-      <c r="B17" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>387</v>
-      </c>
-      <c r="B18" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>389</v>
-      </c>
-      <c r="B19" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>391</v>
-      </c>
-      <c r="B20" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>392</v>
-      </c>
-      <c r="B21" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>394</v>
-      </c>
-      <c r="B22" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" t="s">
-        <v>395</v>
-      </c>
-      <c r="B23" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>397</v>
-      </c>
-      <c r="B24" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" t="s">
-        <v>398</v>
-      </c>
-      <c r="B25" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" t="s">
-        <v>399</v>
-      </c>
-      <c r="B26" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>400</v>
-      </c>
-      <c r="B27" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>401</v>
-      </c>
-      <c r="B28" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>402</v>
-      </c>
-      <c r="B29" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>403</v>
-      </c>
-      <c r="B30" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>404</v>
-      </c>
-      <c r="B31" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>405</v>
-      </c>
-      <c r="B32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>406</v>
-      </c>
-      <c r="B33" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>407</v>
-      </c>
-      <c r="B34" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>408</v>
-      </c>
-      <c r="B35" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>409</v>
-      </c>
-      <c r="B36" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>410</v>
-      </c>
-      <c r="B37" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>411</v>
-      </c>
-      <c r="B38" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>412</v>
-      </c>
-      <c r="B39" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>413</v>
-      </c>
-      <c r="B40" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>414</v>
-      </c>
-      <c r="B41" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>415</v>
-      </c>
-      <c r="B42" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>416</v>
-      </c>
-      <c r="B43" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>417</v>
-      </c>
-      <c r="B44" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>418</v>
-      </c>
-      <c r="B45" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>419</v>
-      </c>
-      <c r="B46" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>420</v>
-      </c>
-      <c r="B47" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>421</v>
-      </c>
-      <c r="B48" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>422</v>
-      </c>
-      <c r="B49" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
         <v>423</v>
       </c>
-      <c r="B50" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>424</v>
-      </c>
-      <c r="B51" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
+      <c r="C4" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="B52" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>426</v>
-      </c>
-      <c r="B53" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>427</v>
-      </c>
-      <c r="B54" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>428</v>
-      </c>
-      <c r="B55" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>429</v>
-      </c>
-      <c r="B56" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>430</v>
-      </c>
-      <c r="B57" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>431</v>
-      </c>
-      <c r="B58" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>432</v>
-      </c>
-      <c r="B59" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>433</v>
-      </c>
-      <c r="B60" t="s">
-        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -5062,533 +4377,473 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
         <v>436</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>438</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="B5" t="s">
         <v>439</v>
       </c>
-      <c r="E4" s="1" t="s">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>440</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B6" t="s">
         <v>441</v>
       </c>
-      <c r="G4" s="1" t="s">
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>442</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="B7" t="s">
         <v>443</v>
       </c>
-      <c r="I4" s="1" t="s">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
         <v>444</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="B8" t="s">
         <v>445</v>
       </c>
-      <c r="K4" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>228</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B9" t="s">
         <v>447</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>448</v>
       </c>
-      <c r="D5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B10" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
         <v>449</v>
       </c>
-      <c r="F5" t="s">
+      <c r="B11" t="s">
         <v>450</v>
       </c>
-      <c r="G5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
         <v>451</v>
       </c>
-      <c r="I5" t="s">
+      <c r="B12" t="s">
         <v>452</v>
       </c>
-      <c r="J5" t="s">
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>453</v>
       </c>
-      <c r="K5" t="s">
+      <c r="B13" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>455</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B14" t="s">
         <v>456</v>
       </c>
-      <c r="D6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" t="s">
-        <v>449</v>
-      </c>
-      <c r="F6" t="s">
-        <v>450</v>
-      </c>
-      <c r="G6" t="s">
-        <v>449</v>
-      </c>
-      <c r="H6" t="s">
-        <v>451</v>
-      </c>
-      <c r="I6" t="s">
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>457</v>
       </c>
-      <c r="J6" t="s">
-        <v>453</v>
-      </c>
-      <c r="K6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B15" t="s">
         <v>458</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>459</v>
       </c>
-      <c r="D7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" t="s">
-        <v>449</v>
-      </c>
-      <c r="F7" t="s">
-        <v>150</v>
-      </c>
-      <c r="G7" t="s">
-        <v>449</v>
-      </c>
-      <c r="H7" t="s">
-        <v>451</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="B16" t="s">
         <v>460</v>
       </c>
-      <c r="J7" t="s">
-        <v>453</v>
-      </c>
-      <c r="K7" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>396</v>
-      </c>
-      <c r="B8" t="s">
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>461</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B17" t="s">
         <v>462</v>
       </c>
-      <c r="D8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" t="s">
-        <v>449</v>
-      </c>
-      <c r="F8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" t="s">
-        <v>449</v>
-      </c>
-      <c r="H8" t="s">
-        <v>451</v>
-      </c>
-      <c r="I8" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>463</v>
       </c>
-      <c r="J8" t="s">
-        <v>453</v>
-      </c>
-      <c r="K8" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="B18" t="s">
         <v>464</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>465</v>
       </c>
-      <c r="D9" t="s">
-        <v>192</v>
-      </c>
-      <c r="E9" t="s">
-        <v>449</v>
-      </c>
-      <c r="F9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G9" t="s">
-        <v>449</v>
-      </c>
-      <c r="H9" t="s">
-        <v>451</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="B19" t="s">
         <v>466</v>
       </c>
-      <c r="J9" t="s">
-        <v>453</v>
-      </c>
-      <c r="K9" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B10" t="s">
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>467</v>
       </c>
-      <c r="C10" t="s">
+      <c r="B20" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
         <v>468</v>
       </c>
-      <c r="D10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E10" t="s">
-        <v>449</v>
-      </c>
-      <c r="F10" t="s">
-        <v>150</v>
-      </c>
-      <c r="G10" t="s">
-        <v>449</v>
-      </c>
-      <c r="H10" t="s">
-        <v>451</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="B21" t="s">
         <v>469</v>
       </c>
-      <c r="J10" t="s">
-        <v>453</v>
-      </c>
-      <c r="K10" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
         <v>470</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B22" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>471</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B23" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
         <v>472</v>
       </c>
-      <c r="D11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" t="s">
-        <v>449</v>
-      </c>
-      <c r="F11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G11" t="s">
-        <v>449</v>
-      </c>
-      <c r="H11" t="s">
-        <v>451</v>
-      </c>
-      <c r="I11" t="s">
+      <c r="B24" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
         <v>473</v>
       </c>
-      <c r="J11" t="s">
-        <v>453</v>
-      </c>
-      <c r="K11" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>172</v>
-      </c>
-      <c r="B12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B25" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>474</v>
       </c>
-      <c r="D12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E12" t="s">
-        <v>449</v>
-      </c>
-      <c r="F12" t="s">
-        <v>190</v>
-      </c>
-      <c r="G12" t="s">
-        <v>449</v>
-      </c>
-      <c r="H12" t="s">
-        <v>451</v>
-      </c>
-      <c r="J12" t="s">
-        <v>453</v>
-      </c>
-      <c r="K12" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>393</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="B26" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
         <v>475</v>
       </c>
-      <c r="C13" t="s">
+      <c r="B27" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
         <v>476</v>
       </c>
-      <c r="D13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E13" t="s">
-        <v>449</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="B28" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
         <v>477</v>
       </c>
-      <c r="G13" t="s">
-        <v>449</v>
-      </c>
-      <c r="H13" t="s">
-        <v>451</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="B29" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
         <v>478</v>
       </c>
-      <c r="J13" t="s">
-        <v>453</v>
-      </c>
-      <c r="K13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>245</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="B30" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
         <v>479</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B31" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
         <v>480</v>
       </c>
-      <c r="D14" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" t="s">
-        <v>449</v>
-      </c>
-      <c r="F14" t="s">
-        <v>453</v>
-      </c>
-      <c r="G14" t="s">
-        <v>453</v>
-      </c>
-      <c r="H14" t="s">
-        <v>451</v>
-      </c>
-      <c r="J14" t="s">
-        <v>453</v>
-      </c>
-      <c r="K14" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>390</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="B32" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
         <v>481</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B33" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
         <v>482</v>
       </c>
-      <c r="D15" t="s">
-        <v>453</v>
-      </c>
-      <c r="E15" t="s">
-        <v>453</v>
-      </c>
-      <c r="F15" t="s">
-        <v>453</v>
-      </c>
-      <c r="G15" t="s">
-        <v>453</v>
-      </c>
-      <c r="H15" t="s">
-        <v>451</v>
-      </c>
-      <c r="J15" t="s">
-        <v>453</v>
-      </c>
-      <c r="K15" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>178</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="B34" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
         <v>483</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B35" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
         <v>484</v>
       </c>
-      <c r="D16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" t="s">
-        <v>449</v>
-      </c>
-      <c r="F16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G16" t="s">
-        <v>449</v>
-      </c>
-      <c r="H16" t="s">
-        <v>451</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="B36" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
         <v>485</v>
       </c>
-      <c r="J16" t="s">
-        <v>453</v>
-      </c>
-      <c r="K16" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
+      <c r="B37" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
         <v>486</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B38" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
         <v>487</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B39" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
         <v>488</v>
       </c>
-      <c r="D17" t="s">
-        <v>192</v>
-      </c>
-      <c r="E17" t="s">
-        <v>449</v>
-      </c>
-      <c r="F17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G17" t="s">
-        <v>449</v>
-      </c>
-      <c r="H17" t="s">
-        <v>451</v>
-      </c>
-      <c r="I17" t="s">
+      <c r="B40" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
         <v>489</v>
       </c>
-      <c r="J17" t="s">
-        <v>453</v>
-      </c>
-      <c r="K17" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
+      <c r="B41" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
         <v>490</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B42" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
         <v>491</v>
       </c>
-      <c r="C18" t="s">
+      <c r="B43" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
         <v>492</v>
       </c>
-      <c r="D18" t="s">
-        <v>192</v>
-      </c>
-      <c r="E18" t="s">
-        <v>449</v>
-      </c>
-      <c r="F18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G18" t="s">
-        <v>449</v>
-      </c>
-      <c r="H18" t="s">
-        <v>451</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="B44" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
         <v>493</v>
       </c>
-      <c r="J18" t="s">
-        <v>453</v>
-      </c>
-      <c r="K18" t="s">
-        <v>454</v>
+      <c r="B45" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>494</v>
+      </c>
+      <c r="B46" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>495</v>
+      </c>
+      <c r="B47" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>496</v>
+      </c>
+      <c r="B48" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>497</v>
+      </c>
+      <c r="B49" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>498</v>
+      </c>
+      <c r="B50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>499</v>
+      </c>
+      <c r="B51" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>500</v>
+      </c>
+      <c r="B52" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>501</v>
+      </c>
+      <c r="B53" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>502</v>
+      </c>
+      <c r="B54" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>503</v>
+      </c>
+      <c r="B55" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>504</v>
+      </c>
+      <c r="B56" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>505</v>
+      </c>
+      <c r="B57" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>506</v>
+      </c>
+      <c r="B58" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>507</v>
+      </c>
+      <c r="B59" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>508</v>
+      </c>
+      <c r="B60" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -5598,27 +4853,463 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>511</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>497</v>
+        <v>297</v>
+      </c>
+      <c r="B5" t="s">
+        <v>522</v>
+      </c>
+      <c r="C5" t="s">
+        <v>523</v>
+      </c>
+      <c r="D5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" t="s">
+        <v>524</v>
+      </c>
+      <c r="F5" t="s">
+        <v>525</v>
+      </c>
+      <c r="G5" t="s">
+        <v>524</v>
+      </c>
+      <c r="H5" t="s">
+        <v>526</v>
+      </c>
+      <c r="I5" t="s">
+        <v>527</v>
+      </c>
+      <c r="J5" t="s">
+        <v>528</v>
+      </c>
+      <c r="K5" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>530</v>
+      </c>
+      <c r="C6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" t="s">
+        <v>524</v>
+      </c>
+      <c r="F6" t="s">
+        <v>525</v>
+      </c>
+      <c r="G6" t="s">
+        <v>524</v>
+      </c>
+      <c r="H6" t="s">
+        <v>526</v>
+      </c>
+      <c r="I6" t="s">
+        <v>532</v>
+      </c>
+      <c r="J6" t="s">
+        <v>528</v>
+      </c>
+      <c r="K6" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>304</v>
+      </c>
+      <c r="B7" t="s">
+        <v>533</v>
+      </c>
+      <c r="C7" t="s">
+        <v>534</v>
+      </c>
+      <c r="D7" t="s">
+        <v>261</v>
+      </c>
+      <c r="E7" t="s">
+        <v>524</v>
+      </c>
+      <c r="F7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" t="s">
+        <v>524</v>
+      </c>
+      <c r="H7" t="s">
+        <v>526</v>
+      </c>
+      <c r="I7" t="s">
+        <v>535</v>
+      </c>
+      <c r="J7" t="s">
+        <v>528</v>
+      </c>
+      <c r="K7" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>427</v>
+      </c>
+      <c r="B8" t="s">
+        <v>536</v>
+      </c>
+      <c r="C8" t="s">
+        <v>537</v>
+      </c>
+      <c r="D8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E8" t="s">
+        <v>524</v>
+      </c>
+      <c r="F8" t="s">
+        <v>219</v>
+      </c>
+      <c r="G8" t="s">
+        <v>524</v>
+      </c>
+      <c r="H8" t="s">
+        <v>526</v>
+      </c>
+      <c r="I8" t="s">
+        <v>538</v>
+      </c>
+      <c r="J8" t="s">
+        <v>528</v>
+      </c>
+      <c r="K8" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>306</v>
+      </c>
+      <c r="B9" t="s">
+        <v>539</v>
+      </c>
+      <c r="C9" t="s">
+        <v>540</v>
+      </c>
+      <c r="D9" t="s">
+        <v>261</v>
+      </c>
+      <c r="E9" t="s">
+        <v>524</v>
+      </c>
+      <c r="F9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G9" t="s">
+        <v>524</v>
+      </c>
+      <c r="H9" t="s">
+        <v>526</v>
+      </c>
+      <c r="I9" t="s">
+        <v>541</v>
+      </c>
+      <c r="J9" t="s">
+        <v>528</v>
+      </c>
+      <c r="K9" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>219</v>
+      </c>
+      <c r="B10" t="s">
+        <v>542</v>
+      </c>
+      <c r="C10" t="s">
+        <v>543</v>
+      </c>
+      <c r="D10" t="s">
+        <v>261</v>
+      </c>
+      <c r="E10" t="s">
+        <v>524</v>
+      </c>
+      <c r="F10" t="s">
+        <v>219</v>
+      </c>
+      <c r="G10" t="s">
+        <v>524</v>
+      </c>
+      <c r="H10" t="s">
+        <v>526</v>
+      </c>
+      <c r="I10" t="s">
+        <v>544</v>
+      </c>
+      <c r="J10" t="s">
+        <v>528</v>
+      </c>
+      <c r="K10" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>426</v>
+      </c>
+      <c r="B11" t="s">
+        <v>545</v>
+      </c>
+      <c r="C11" t="s">
+        <v>546</v>
+      </c>
+      <c r="D11" t="s">
+        <v>261</v>
+      </c>
+      <c r="E11" t="s">
+        <v>524</v>
+      </c>
+      <c r="F11" t="s">
+        <v>219</v>
+      </c>
+      <c r="G11" t="s">
+        <v>524</v>
+      </c>
+      <c r="H11" t="s">
+        <v>526</v>
+      </c>
+      <c r="I11" t="s">
+        <v>547</v>
+      </c>
+      <c r="J11" t="s">
+        <v>528</v>
+      </c>
+      <c r="K11" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>241</v>
+      </c>
+      <c r="B12" t="s">
+        <v>524</v>
+      </c>
+      <c r="C12" t="s">
+        <v>548</v>
+      </c>
+      <c r="D12" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" t="s">
+        <v>524</v>
+      </c>
+      <c r="F12" t="s">
+        <v>259</v>
+      </c>
+      <c r="G12" t="s">
+        <v>524</v>
+      </c>
+      <c r="H12" t="s">
+        <v>526</v>
+      </c>
+      <c r="J12" t="s">
+        <v>528</v>
+      </c>
+      <c r="K12" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>469</v>
+      </c>
+      <c r="B13" t="s">
+        <v>549</v>
+      </c>
+      <c r="C13" t="s">
+        <v>550</v>
+      </c>
+      <c r="D13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E13" t="s">
+        <v>524</v>
+      </c>
+      <c r="F13" t="s">
+        <v>551</v>
+      </c>
+      <c r="G13" t="s">
+        <v>524</v>
+      </c>
+      <c r="H13" t="s">
+        <v>526</v>
+      </c>
+      <c r="I13" t="s">
+        <v>552</v>
+      </c>
+      <c r="J13" t="s">
+        <v>528</v>
+      </c>
+      <c r="K13" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" t="s">
+        <v>553</v>
+      </c>
+      <c r="C14" t="s">
+        <v>554</v>
+      </c>
+      <c r="D14" t="s">
+        <v>261</v>
+      </c>
+      <c r="E14" t="s">
+        <v>524</v>
+      </c>
+      <c r="F14" t="s">
+        <v>528</v>
+      </c>
+      <c r="G14" t="s">
+        <v>528</v>
+      </c>
+      <c r="H14" t="s">
+        <v>526</v>
+      </c>
+      <c r="J14" t="s">
+        <v>528</v>
+      </c>
+      <c r="K14" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>466</v>
+      </c>
+      <c r="B15" t="s">
+        <v>555</v>
+      </c>
+      <c r="C15" t="s">
+        <v>556</v>
+      </c>
+      <c r="D15" t="s">
+        <v>528</v>
+      </c>
+      <c r="E15" t="s">
+        <v>528</v>
+      </c>
+      <c r="F15" t="s">
+        <v>528</v>
+      </c>
+      <c r="G15" t="s">
+        <v>528</v>
+      </c>
+      <c r="H15" t="s">
+        <v>526</v>
+      </c>
+      <c r="J15" t="s">
+        <v>528</v>
+      </c>
+      <c r="K15" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>247</v>
+      </c>
+      <c r="B16" t="s">
+        <v>557</v>
+      </c>
+      <c r="C16" t="s">
+        <v>558</v>
+      </c>
+      <c r="D16" t="s">
+        <v>261</v>
+      </c>
+      <c r="E16" t="s">
+        <v>524</v>
+      </c>
+      <c r="F16" t="s">
+        <v>259</v>
+      </c>
+      <c r="G16" t="s">
+        <v>524</v>
+      </c>
+      <c r="H16" t="s">
+        <v>526</v>
+      </c>
+      <c r="I16" t="s">
+        <v>559</v>
+      </c>
+      <c r="J16" t="s">
+        <v>528</v>
+      </c>
+      <c r="K16" t="s">
+        <v>529</v>
       </c>
     </row>
   </sheetData>
@@ -5633,22 +5324,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>498</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>495</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>496</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>497</v>
+        <v>563</v>
       </c>
     </row>
   </sheetData>
@@ -5683,571 +5374,27 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>507</v>
-      </c>
-      <c r="B5" t="s">
-        <v>508</v>
-      </c>
-      <c r="C5" t="s">
-        <v>288</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>396</v>
-      </c>
-      <c r="F5" t="s">
-        <v>509</v>
-      </c>
-      <c r="G5" t="s">
-        <v>340</v>
-      </c>
-      <c r="I5" t="s">
-        <v>510</v>
-      </c>
-      <c r="J5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>512</v>
-      </c>
-      <c r="B6" t="s">
-        <v>513</v>
-      </c>
-      <c r="C6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" t="s">
-        <v>514</v>
-      </c>
-      <c r="G6" t="s">
-        <v>256</v>
-      </c>
-      <c r="I6" t="s">
-        <v>515</v>
-      </c>
-      <c r="J6" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>517</v>
-      </c>
-      <c r="B7" t="s">
-        <v>518</v>
-      </c>
-      <c r="C7" t="s">
-        <v>336</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>235</v>
-      </c>
-      <c r="F7" t="s">
-        <v>519</v>
-      </c>
-      <c r="G7" t="s">
-        <v>146</v>
-      </c>
-      <c r="I7" t="s">
-        <v>520</v>
-      </c>
-      <c r="J7" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>522</v>
-      </c>
-      <c r="B8" t="s">
-        <v>523</v>
-      </c>
-      <c r="C8" t="s">
-        <v>524</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" t="s">
-        <v>525</v>
-      </c>
-      <c r="G8" t="s">
-        <v>146</v>
-      </c>
-      <c r="I8" t="s">
-        <v>526</v>
-      </c>
-      <c r="J8" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>528</v>
-      </c>
-      <c r="B9" t="s">
-        <v>529</v>
-      </c>
-      <c r="C9" t="s">
-        <v>524</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>237</v>
-      </c>
-      <c r="F9" t="s">
-        <v>530</v>
-      </c>
-      <c r="G9" t="s">
-        <v>298</v>
-      </c>
-      <c r="I9" t="s">
-        <v>526</v>
-      </c>
-      <c r="J9" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>532</v>
-      </c>
-      <c r="B10" t="s">
-        <v>533</v>
-      </c>
-      <c r="C10" t="s">
-        <v>524</v>
-      </c>
-      <c r="D10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" t="s">
-        <v>514</v>
-      </c>
-      <c r="G10" t="s">
-        <v>298</v>
-      </c>
-      <c r="I10" t="s">
-        <v>526</v>
-      </c>
-      <c r="J10" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>535</v>
-      </c>
-      <c r="B11" t="s">
-        <v>536</v>
-      </c>
-      <c r="C11" t="s">
-        <v>537</v>
-      </c>
-      <c r="D11" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" t="s">
-        <v>237</v>
-      </c>
-      <c r="F11" t="s">
-        <v>514</v>
-      </c>
-      <c r="G11" t="s">
-        <v>256</v>
-      </c>
-      <c r="I11" t="s">
-        <v>538</v>
-      </c>
-      <c r="J11" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>540</v>
-      </c>
-      <c r="B12" t="s">
-        <v>541</v>
-      </c>
-      <c r="C12" t="s">
-        <v>537</v>
-      </c>
-      <c r="D12" t="s">
-        <v>228</v>
-      </c>
-      <c r="E12" t="s">
-        <v>228</v>
-      </c>
-      <c r="F12" t="s">
-        <v>542</v>
-      </c>
-      <c r="G12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" t="s">
-        <v>538</v>
-      </c>
-      <c r="J12" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>544</v>
-      </c>
-      <c r="B13" t="s">
-        <v>545</v>
-      </c>
-      <c r="C13" t="s">
-        <v>340</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F13" t="s">
-        <v>525</v>
-      </c>
-      <c r="G13" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" t="s">
-        <v>546</v>
-      </c>
-      <c r="J13" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>548</v>
-      </c>
-      <c r="B14" t="s">
-        <v>549</v>
-      </c>
-      <c r="C14" t="s">
-        <v>342</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" t="s">
-        <v>519</v>
-      </c>
-      <c r="G14" t="s">
-        <v>125</v>
-      </c>
-      <c r="I14" t="s">
-        <v>550</v>
-      </c>
-      <c r="J14" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>552</v>
-      </c>
-      <c r="B15" t="s">
-        <v>553</v>
-      </c>
-      <c r="C15" t="s">
-        <v>554</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>235</v>
-      </c>
-      <c r="F15" t="s">
-        <v>519</v>
-      </c>
-      <c r="G15" t="s">
-        <v>146</v>
-      </c>
-      <c r="I15" t="s">
-        <v>555</v>
-      </c>
-      <c r="J15" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>557</v>
-      </c>
-      <c r="B16" t="s">
-        <v>558</v>
-      </c>
-      <c r="C16" t="s">
-        <v>554</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>158</v>
-      </c>
-      <c r="F16" t="s">
-        <v>559</v>
-      </c>
-      <c r="G16" t="s">
-        <v>286</v>
-      </c>
-      <c r="I16" t="s">
-        <v>555</v>
-      </c>
-      <c r="J16" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>561</v>
-      </c>
-      <c r="B17" t="s">
-        <v>562</v>
-      </c>
-      <c r="C17" t="s">
-        <v>554</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>235</v>
-      </c>
-      <c r="F17" t="s">
         <v>563</v>
-      </c>
-      <c r="G17" t="s">
-        <v>125</v>
-      </c>
-      <c r="I17" t="s">
-        <v>555</v>
-      </c>
-      <c r="J17" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>565</v>
-      </c>
-      <c r="B18" t="s">
-        <v>566</v>
-      </c>
-      <c r="C18" t="s">
-        <v>284</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>158</v>
-      </c>
-      <c r="F18" t="s">
-        <v>525</v>
-      </c>
-      <c r="G18" t="s">
-        <v>286</v>
-      </c>
-      <c r="I18" t="s">
-        <v>567</v>
-      </c>
-      <c r="J18" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>569</v>
-      </c>
-      <c r="B19" t="s">
-        <v>570</v>
-      </c>
-      <c r="C19" t="s">
-        <v>571</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>396</v>
-      </c>
-      <c r="F19" t="s">
-        <v>509</v>
-      </c>
-      <c r="G19" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" t="s">
-        <v>572</v>
-      </c>
-      <c r="J19" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>574</v>
-      </c>
-      <c r="B20" t="s">
-        <v>575</v>
-      </c>
-      <c r="C20" t="s">
-        <v>576</v>
-      </c>
-      <c r="D20" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F20" t="s">
-        <v>514</v>
-      </c>
-      <c r="G20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I20" t="s">
-        <v>577</v>
-      </c>
-      <c r="J20" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>574</v>
-      </c>
-      <c r="B21" t="s">
-        <v>575</v>
-      </c>
-      <c r="C21" t="s">
-        <v>576</v>
-      </c>
-      <c r="D21" t="s">
-        <v>235</v>
-      </c>
-      <c r="E21" t="s">
-        <v>237</v>
-      </c>
-      <c r="F21" t="s">
-        <v>514</v>
-      </c>
-      <c r="G21" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" t="s">
-        <v>577</v>
-      </c>
-      <c r="J21" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>579</v>
-      </c>
-      <c r="B22" t="s">
-        <v>580</v>
-      </c>
-      <c r="C22" t="s">
-        <v>216</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" t="s">
-        <v>525</v>
-      </c>
-      <c r="G22" t="s">
-        <v>125</v>
-      </c>
-      <c r="I22" t="s">
-        <v>581</v>
-      </c>
-      <c r="J22" t="s">
-        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -6257,629 +5404,49 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>583</v>
+        <v>565</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>353</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>438</v>
+        <v>513</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>437</v>
+        <v>512</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>500</v>
+        <v>424</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>501</v>
+        <v>566</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>502</v>
+        <v>567</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>503</v>
+        <v>568</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>446</v>
+        <v>521</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>505</v>
+        <v>570</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>584</v>
-      </c>
-      <c r="B5" t="s">
-        <v>585</v>
-      </c>
-      <c r="C5" t="s">
-        <v>286</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F5" t="s">
-        <v>514</v>
-      </c>
-      <c r="G5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I5" t="s">
-        <v>586</v>
-      </c>
-      <c r="J5" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>584</v>
-      </c>
-      <c r="B6" t="s">
-        <v>585</v>
-      </c>
-      <c r="C6" t="s">
-        <v>286</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F6" t="s">
-        <v>563</v>
-      </c>
-      <c r="G6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" t="s">
-        <v>586</v>
-      </c>
-      <c r="J6" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>584</v>
-      </c>
-      <c r="B7" t="s">
-        <v>585</v>
-      </c>
-      <c r="C7" t="s">
-        <v>286</v>
-      </c>
-      <c r="D7" t="s">
-        <v>228</v>
-      </c>
-      <c r="E7" t="s">
-        <v>237</v>
-      </c>
-      <c r="F7" t="s">
-        <v>514</v>
-      </c>
-      <c r="G7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" t="s">
-        <v>586</v>
-      </c>
-      <c r="J7" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>584</v>
-      </c>
-      <c r="B8" t="s">
-        <v>585</v>
-      </c>
-      <c r="C8" t="s">
-        <v>286</v>
-      </c>
-      <c r="D8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E8" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" t="s">
-        <v>563</v>
-      </c>
-      <c r="G8" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" t="s">
-        <v>586</v>
-      </c>
-      <c r="J8" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>588</v>
-      </c>
-      <c r="B9" t="s">
-        <v>589</v>
-      </c>
-      <c r="C9" t="s">
-        <v>590</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>172</v>
-      </c>
-      <c r="F9" t="s">
-        <v>591</v>
-      </c>
-      <c r="G9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I9" t="s">
-        <v>592</v>
-      </c>
-      <c r="J9" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>594</v>
-      </c>
-      <c r="B10" t="s">
-        <v>595</v>
-      </c>
-      <c r="C10" t="s">
-        <v>590</v>
-      </c>
-      <c r="D10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" t="s">
-        <v>172</v>
-      </c>
-      <c r="F10" t="s">
-        <v>591</v>
-      </c>
-      <c r="G10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I10" t="s">
-        <v>592</v>
-      </c>
-      <c r="J10" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>597</v>
-      </c>
-      <c r="B11" t="s">
-        <v>598</v>
-      </c>
-      <c r="C11" t="s">
-        <v>590</v>
-      </c>
-      <c r="D11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E11" t="s">
-        <v>172</v>
-      </c>
-      <c r="F11" t="s">
-        <v>591</v>
-      </c>
-      <c r="G11" t="s">
-        <v>125</v>
-      </c>
-      <c r="I11" t="s">
-        <v>592</v>
-      </c>
-      <c r="J11" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>535</v>
-      </c>
-      <c r="B12" t="s">
-        <v>536</v>
-      </c>
-      <c r="C12" t="s">
-        <v>537</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>172</v>
-      </c>
-      <c r="F12" t="s">
-        <v>591</v>
-      </c>
-      <c r="G12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" t="s">
-        <v>538</v>
-      </c>
-      <c r="J12" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>600</v>
-      </c>
-      <c r="B13" t="s">
-        <v>601</v>
-      </c>
-      <c r="C13" t="s">
-        <v>537</v>
-      </c>
-      <c r="D13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E13" t="s">
-        <v>396</v>
-      </c>
-      <c r="F13" t="s">
-        <v>509</v>
-      </c>
-      <c r="G13" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" t="s">
-        <v>538</v>
-      </c>
-      <c r="J13" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>603</v>
-      </c>
-      <c r="B14" t="s">
-        <v>604</v>
-      </c>
-      <c r="C14" t="s">
-        <v>338</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" t="s">
-        <v>519</v>
-      </c>
-      <c r="G14" t="s">
-        <v>125</v>
-      </c>
-      <c r="I14" t="s">
-        <v>605</v>
-      </c>
-      <c r="J14" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>607</v>
-      </c>
-      <c r="B15" t="s">
-        <v>608</v>
-      </c>
-      <c r="C15" t="s">
-        <v>284</v>
-      </c>
-      <c r="D15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" t="s">
-        <v>172</v>
-      </c>
-      <c r="F15" t="s">
-        <v>591</v>
-      </c>
-      <c r="G15" t="s">
-        <v>125</v>
-      </c>
-      <c r="I15" t="s">
-        <v>567</v>
-      </c>
-      <c r="J15" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>610</v>
-      </c>
-      <c r="B16" t="s">
-        <v>611</v>
-      </c>
-      <c r="C16" t="s">
-        <v>284</v>
-      </c>
-      <c r="D16" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" t="s">
-        <v>470</v>
-      </c>
-      <c r="F16" t="s">
-        <v>612</v>
-      </c>
-      <c r="G16" t="s">
-        <v>125</v>
-      </c>
-      <c r="I16" t="s">
-        <v>567</v>
-      </c>
-      <c r="J16" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>610</v>
-      </c>
-      <c r="B17" t="s">
-        <v>611</v>
-      </c>
-      <c r="C17" t="s">
-        <v>284</v>
-      </c>
-      <c r="D17" t="s">
-        <v>235</v>
-      </c>
-      <c r="E17" t="s">
-        <v>470</v>
-      </c>
-      <c r="F17" t="s">
-        <v>612</v>
-      </c>
-      <c r="G17" t="s">
-        <v>125</v>
-      </c>
-      <c r="I17" t="s">
-        <v>567</v>
-      </c>
-      <c r="J17" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>614</v>
-      </c>
-      <c r="B18" t="s">
-        <v>615</v>
-      </c>
-      <c r="C18" t="s">
-        <v>284</v>
-      </c>
-      <c r="D18" t="s">
-        <v>396</v>
-      </c>
-      <c r="E18" t="s">
-        <v>470</v>
-      </c>
-      <c r="F18" t="s">
-        <v>612</v>
-      </c>
-      <c r="G18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I18" t="s">
-        <v>567</v>
-      </c>
-      <c r="J18" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>614</v>
-      </c>
-      <c r="B19" t="s">
-        <v>615</v>
-      </c>
-      <c r="C19" t="s">
-        <v>284</v>
-      </c>
-      <c r="D19" t="s">
-        <v>237</v>
-      </c>
-      <c r="E19" t="s">
-        <v>470</v>
-      </c>
-      <c r="F19" t="s">
-        <v>612</v>
-      </c>
-      <c r="G19" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" t="s">
-        <v>567</v>
-      </c>
-      <c r="J19" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>574</v>
-      </c>
-      <c r="B20" t="s">
-        <v>575</v>
-      </c>
-      <c r="C20" t="s">
-        <v>576</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" t="s">
-        <v>617</v>
-      </c>
-      <c r="G20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I20" t="s">
-        <v>577</v>
-      </c>
-      <c r="J20" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>574</v>
-      </c>
-      <c r="B21" t="s">
-        <v>575</v>
-      </c>
-      <c r="C21" t="s">
-        <v>576</v>
-      </c>
-      <c r="D21" t="s">
-        <v>228</v>
-      </c>
-      <c r="E21" t="s">
-        <v>470</v>
-      </c>
-      <c r="F21" t="s">
-        <v>612</v>
-      </c>
-      <c r="G21" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" t="s">
-        <v>577</v>
-      </c>
-      <c r="J21" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>618</v>
-      </c>
-      <c r="B22" t="s">
-        <v>619</v>
-      </c>
-      <c r="C22" t="s">
-        <v>576</v>
-      </c>
-      <c r="D22" t="s">
-        <v>396</v>
-      </c>
-      <c r="E22" t="s">
-        <v>172</v>
-      </c>
-      <c r="F22" t="s">
-        <v>591</v>
-      </c>
-      <c r="G22" t="s">
-        <v>125</v>
-      </c>
-      <c r="I22" t="s">
-        <v>577</v>
-      </c>
-      <c r="J22" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>618</v>
-      </c>
-      <c r="B23" t="s">
-        <v>619</v>
-      </c>
-      <c r="C23" t="s">
-        <v>576</v>
-      </c>
-      <c r="D23" t="s">
-        <v>237</v>
-      </c>
-      <c r="E23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F23" t="s">
-        <v>591</v>
-      </c>
-      <c r="G23" t="s">
-        <v>125</v>
-      </c>
-      <c r="I23" t="s">
-        <v>577</v>
-      </c>
-      <c r="J23" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>618</v>
-      </c>
-      <c r="B24" t="s">
-        <v>619</v>
-      </c>
-      <c r="C24" t="s">
-        <v>576</v>
-      </c>
-      <c r="D24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24" t="s">
-        <v>172</v>
-      </c>
-      <c r="F24" t="s">
-        <v>591</v>
-      </c>
-      <c r="G24" t="s">
-        <v>125</v>
-      </c>
-      <c r="I24" t="s">
-        <v>577</v>
-      </c>
-      <c r="J24" t="s">
-        <v>620</v>
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -6889,27 +5456,49 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>624</v>
+        <v>513</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>566</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>571</v>
       </c>
     </row>
   </sheetData>
@@ -6924,22 +5513,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>625</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>622</v>
+        <v>574</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>623</v>
+        <v>575</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>624</v>
+        <v>576</v>
       </c>
     </row>
   </sheetData>
@@ -6949,12 +5538,27 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>577</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>576</v>
       </c>
     </row>
   </sheetData>
@@ -6964,32 +5568,12 @@
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>628</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -6999,12 +5583,32 @@
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>629</v>
+        <v>579</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -7019,7 +5623,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>630</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>
@@ -7029,27 +5633,12 @@
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>628</v>
+        <v>582</v>
       </c>
     </row>
   </sheetData>
@@ -7059,17 +5648,27 @@
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>632</v>
+        <v>583</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -7114,12 +5713,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>633</v>
+        <v>584</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>228</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -7129,12 +5728,32 @@
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>297</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>634</v>
+        <v>586</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7149,87 +5768,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>635</v>
+        <v>587</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>636</v>
+        <v>588</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>637</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>638</v>
+        <v>590</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>639</v>
+        <v>591</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>640</v>
+        <v>592</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>641</v>
+        <v>593</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>642</v>
+        <v>594</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>643</v>
+        <v>595</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>644</v>
+        <v>596</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>645</v>
+        <v>597</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>646</v>
+        <v>598</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>647</v>
+        <v>599</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>648</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>649</v>
+        <v>601</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>650</v>
+        <v>602</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>651</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>
@@ -7264,7 +5883,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -7280,6 +5899,276 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -7294,7 +6183,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7304,7 +6193,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -7319,7 +6208,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7334,17 +6223,282 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -7549,7 +7549,7 @@
         <v>592</v>
       </c>
       <c r="G9" t="s">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="I9" t="s">
         <v>588</v>
@@ -7578,7 +7578,7 @@
         <v>577</v>
       </c>
       <c r="G10" t="s">
-        <v>319</v>
+        <v>281</v>
       </c>
       <c r="I10" t="s">
         <v>588</v>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -30,31 +30,24 @@
     <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
     <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
     <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
-    <sheet name="PAD REPORT" sheetId="27" r:id="rId27"/>
-    <sheet name="REGISTER ADDRESS REPORT" sheetId="28" r:id="rId28"/>
-    <sheet name="REGISTER DETAIL ADDRESS REPORT" sheetId="29" r:id="rId29"/>
-    <sheet name="FACTORY ADDRESS REPORT" sheetId="30" r:id="rId30"/>
-    <sheet name="ACCURACY ADDRESS REPORT" sheetId="31" r:id="rId31"/>
-    <sheet name="DFT PROBE ADDRESS REPORT" sheetId="32" r:id="rId32"/>
-    <sheet name="DFT HIJACK ADDRESS REPORT" sheetId="33" r:id="rId33"/>
-    <sheet name="DFT DBUF ADDRESS REPORT" sheetId="34" r:id="rId34"/>
-    <sheet name="TMA SUMMARY REPORT (DFTs)" sheetId="35" r:id="rId35"/>
-    <sheet name="DFT CELL GLOBAL ADDRESS REPORT" sheetId="36" r:id="rId36"/>
-    <sheet name="DFT CELL DBUF ADDRESS REPORT" sheetId="37" r:id="rId37"/>
-    <sheet name="DFT CELL ADDRESS REPORT (Rich)" sheetId="38" r:id="rId38"/>
-    <sheet name="DFT dftprobe Checker" sheetId="39" r:id="rId39"/>
-    <sheet name="DFT dfthijack Checker" sheetId="40" r:id="rId40"/>
-    <sheet name="Pad Checker" sheetId="41" r:id="rId41"/>
+    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
+    <sheet name="PAD REPORT" sheetId="28" r:id="rId28"/>
+    <sheet name="REGISTER ADDRESS REPORT" sheetId="29" r:id="rId29"/>
+    <sheet name="REGISTER DETAIL ADDRESS REPORT" sheetId="30" r:id="rId30"/>
+    <sheet name="FACTORY ADDRESS REPORT" sheetId="31" r:id="rId31"/>
+    <sheet name="ACCURACY ADDRESS REPORT" sheetId="32" r:id="rId32"/>
+    <sheet name="DFT dfthijack Checker" sheetId="33" r:id="rId33"/>
+    <sheet name="Pad Checker" sheetId="34" r:id="rId34"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="698">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -146,10 +139,10 @@
     <t>Shorted Inputs</t>
   </si>
   <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_1 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(REGULATIONtestmode_d791a7c9_1)</t>
-  </si>
-  <si>
-    <t>Shorted input REGULATIONtestmode_d791a7c9_2 XU20.i0 --&gt; XU21.i(REGULATIONtestmode_d791a7c9_2)</t>
+    <t>Shorted input 59 XU19.Tstate --&gt; XU20.Tstate --&gt; XU14.enable_switchb(59)</t>
+  </si>
+  <si>
+    <t>Shorted input 60 XU20.i0 --&gt; XU21.i(60)</t>
   </si>
   <si>
     <t>Shorted Outputs</t>
@@ -161,19 +154,388 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_0(44)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_1(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_2(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.CLOCKofftime_3(47)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.enableFAULT(121)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol0(117)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol1(118)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol2(119)</t>
+  </si>
+  <si>
+    <t>Floating pin XALGORITHM.STATEcontrol3(120)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.fcm(59)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_bottom(60)</t>
+  </si>
+  <si>
+    <t>Floating pin XCONTROL.blank_refresh(61)</t>
+  </si>
+  <si>
+    <t>Floating pin XU21.i0(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU22.i0(49)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
+  </si>
+  <si>
+    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XU11.enable_switchb(102)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.mode_hiccup(45)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.blank_thermal(46)</t>
+  </si>
+  <si>
+    <t>Floating pin XU10.enable_switch(58)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(35)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(34)</t>
+  </si>
+  <si>
+    <t>Floating pin XU2.adjust_resistor(33)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(50)</t>
+  </si>
+  <si>
+    <t>Floating pin XU4.adjust_resistor(49)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(70)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(69)</t>
+  </si>
+  <si>
+    <t>Floating pin XCZCOMP.capacitoradjust(68)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol0(80)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol1(81)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol2(82)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN.STATEcontrol3(83)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.halfway(36)</t>
+  </si>
+  <si>
+    <t>Floating pin XMAIN8.softstart_1ms(35)</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>No Connects - Inputs</t>
+  </si>
+  <si>
+    <t>44 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>47 - {"path": "XWALTZ,XceleraCORE,XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CLOCKofftime_3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>121 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "enableFAULT", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>117 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>118 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>119 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>120 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL,XALGORITHM", "instance": "XALGORITHM", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>59 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "fcm", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>60 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_bottom", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>61 - {"path": "XWALTZ,XceleraCORE,XCONTROL,XCONTROL", "instance": "XCONTROL", "symbol": "blank_refresh", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU21", "instance": "XU21", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>45 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "mode_hiccup", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>46 - {"path": "XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN", "instance": "XMAIN", "symbol": "blank_thermal", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>58 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XDEBUG,XU10", "instance": "XU10", "symbol": "enable_switch", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>34 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>33 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU2", "instance": "XU2", "symbol": "adjust_resistor", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>50 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>49 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XU4", "instance": "XU4", "symbol": "adjust_resistor", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>70 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>69 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>68 - {"path": "XWALTZ,XceleraCORE,XREGULATION,XMAIN,XCOMPENSATION,XCZCOMP", "instance": "XCZCOMP", "symbol": "capacitoradjust", "io": "input", "bus": "[2:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>80 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol0", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>81 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol1", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>82 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol2", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>83 - {"path": "XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,XMAIN", "instance": "XMAIN", "symbol": "STATEcontrol3", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>36 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "halfway", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
+  </si>
+  <si>
+    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
+  </si>
+  <si>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
+  </si>
+  <si>
+    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -294,76 +656,94 @@
     <t>DRM Efficiency</t>
   </si>
   <si>
+    <t>DRM Efficiency Summary</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+  </si>
+  <si>
+    <t>DFT Efficiency</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm16L', 'bits': 16, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 4, 'efficiency': '50.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm16', 'bits': 16, 'noconns': 4, 'efficiency': '75.0%'}</t>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
   </si>
   <si>
-    <t>{'name': 'drm24L', 'bits': 24, 'noconns': 0, 'efficiency': '100.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm24', 'bits': 24, 'noconns': 6, 'efficiency': '75.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 7, 'efficiency': '12.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm8L', 'bits': 8, 'noconns': 5, 'efficiency': '37.5%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
-  </si>
-  <si>
-    <t>{'name': 'drm8', 'bits': 8, 'noconns': 0, 'efficiency': '100.0%'}</t>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 3, 'efficiency': '62.5%'}</t>
+  </si>
+  <si>
+    <t>{'name': 'DFTtm8', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm48', 'bits': 48, 'noconns': 10, 'efficiency': '79.2%'}</t>
+    <t>XWALTZ,XceleraCORE,XSERVICE,XDEBUG</t>
   </si>
   <si>
     <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN</t>
   </si>
   <si>
-    <t>{'name': 'drm56', 'bits': 56, 'noconns': 9, 'efficiency': '83.9%'}</t>
-  </si>
-  <si>
-    <t>DRM Efficiency Summary</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>{'cells': 15, 'bytes': 32.0, 'noconns': 67, 'efficiency': '73.8%'}</t>
-  </si>
-  <si>
-    <t>DFT Efficiency</t>
+    <t>{'name': 'DFTtm8t', 'bits': 8, 'noconns': 6, 'efficiency': '25.0%'}</t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG</t>
   </si>
   <si>
     <t>DFM Efficiency Summary</t>
   </si>
   <si>
-    <t>{'cells': 0, 'bytes': 0, 'noconns': 0, 'efficiency': '100%'}</t>
+    <t>{'cells': 25, 'bytes': 25.0, 'noconns': 62, 'efficiency': '69.0%'}</t>
   </si>
   <si>
     <t>Project Summary</t>
@@ -372,16 +752,16 @@
     <t>Package Stats</t>
   </si>
   <si>
-    <t>needed: 0</t>
+    <t>needed: 2</t>
   </si>
   <si>
     <t>spares: 0</t>
   </si>
   <si>
-    <t>algorithm: 0 - No compression needed</t>
-  </si>
-  <si>
-    <t>piggyback: []</t>
+    <t>algorithm: 6 - Piggybacks</t>
+  </si>
+  <si>
+    <t>piggyback: ['DFTSCL', 'DFTSDA']</t>
   </si>
   <si>
     <t>user_pads: 12</t>
@@ -411,18 +791,18 @@
     <t>add_dft</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>add_dbufdft</t>
+  </si>
+  <si>
     <t>N</t>
   </si>
   <si>
-    <t>add_dbufdft</t>
-  </si>
-  <si>
     <t>dft_ignore_bricks</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>dft_measure</t>
   </si>
   <si>
@@ -1116,25 +1496,154 @@
     <t>measure_reset_command</t>
   </si>
   <si>
+    <t>DRM Summary</t>
+  </si>
+  <si>
+    <t>Addresses</t>
+  </si>
+  <si>
+    <t>Path</t>
+  </si>
+  <si>
+    <t>Instance</t>
+  </si>
+  <si>
+    <t>TMB</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>DRM to Memory Check</t>
+  </si>
+  <si>
+    <t>TOTAL dec</t>
+  </si>
+  <si>
+    <t>Allowed &lt;= 61</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
     <t>Register Summary</t>
   </si>
   <si>
     <t>DFT Summary</t>
   </si>
   <si>
-    <t>Addresses</t>
-  </si>
-  <si>
-    <t>Path</t>
-  </si>
-  <si>
-    <t>Instance</t>
-  </si>
-  <si>
     <t>TMA</t>
   </si>
   <si>
-    <t>type</t>
+    <t>dft_hex0x01</t>
+  </si>
+  <si>
+    <t>DFTtm8</t>
+  </si>
+  <si>
+    <t>dft_hex0x02</t>
+  </si>
+  <si>
+    <t>DFTtm8t</t>
+  </si>
+  <si>
+    <t>dft_hex0x03</t>
+  </si>
+  <si>
+    <t>DFTtm8d</t>
+  </si>
+  <si>
+    <t>dft_hex0x04</t>
+  </si>
+  <si>
+    <t>dft_hex0x05</t>
+  </si>
+  <si>
+    <t>0x05</t>
+  </si>
+  <si>
+    <t>dft_hex0x06</t>
+  </si>
+  <si>
+    <t>0x06</t>
+  </si>
+  <si>
+    <t>dft_hex0x07</t>
+  </si>
+  <si>
+    <t>0x07</t>
+  </si>
+  <si>
+    <t>dft_hex0x08</t>
+  </si>
+  <si>
+    <t>dft_hex0x09</t>
+  </si>
+  <si>
+    <t>dft_hex0x0A</t>
+  </si>
+  <si>
+    <t>dft_hex0x0B</t>
+  </si>
+  <si>
+    <t>0x0B</t>
+  </si>
+  <si>
+    <t>dft_hex0x0C</t>
+  </si>
+  <si>
+    <t>dft_hex0x0D</t>
+  </si>
+  <si>
+    <t>0x0D</t>
+  </si>
+  <si>
+    <t>dft_hex0x0E</t>
+  </si>
+  <si>
+    <t>0x0E</t>
+  </si>
+  <si>
+    <t>dft_hex0x0F</t>
+  </si>
+  <si>
+    <t>dft_hex0x10</t>
+  </si>
+  <si>
+    <t>dft_hex0x11</t>
+  </si>
+  <si>
+    <t>dft_hex0x12</t>
+  </si>
+  <si>
+    <t>dft_hex0x13</t>
+  </si>
+  <si>
+    <t>dft_hex0x14</t>
+  </si>
+  <si>
+    <t>dft_hex0x15</t>
+  </si>
+  <si>
+    <t>dft_hex0x16</t>
+  </si>
+  <si>
+    <t>dft_hex0x17</t>
+  </si>
+  <si>
+    <t>dft_hex0x18</t>
+  </si>
+  <si>
+    <t>dft_hex0x19</t>
+  </si>
+  <si>
+    <t>0x19</t>
   </si>
   <si>
     <t>Nesto Usage Report</t>
@@ -1158,28 +1667,28 @@
     <t>193</t>
   </si>
   <si>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>148</t>
+  </si>
+  <si>
+    <t>dbuf</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>148</t>
-  </si>
-  <si>
-    <t>dbuf</t>
-  </si>
-  <si>
-    <t>122</t>
+    <t>107</t>
   </si>
   <si>
     <t>nor3</t>
   </si>
   <si>
-    <t>61</t>
+    <t>dftprobeModel0</t>
   </si>
   <si>
     <t>delayfixed</t>
@@ -1212,75 +1721,75 @@
     <t>35</t>
   </si>
   <si>
+    <t>dftmodule</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>dfthijack</t>
+  </si>
+  <si>
+    <t>dff</t>
+  </si>
+  <si>
+    <t>tie</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>brick</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>dftprobeModel2</t>
+  </si>
+  <si>
+    <t>PEBBLEtielo</t>
+  </si>
+  <si>
+    <t>resistor</t>
+  </si>
+  <si>
+    <t>oneshot</t>
+  </si>
+  <si>
+    <t>fetdn</t>
+  </si>
+  <si>
+    <t>currentlimitfet</t>
+  </si>
+  <si>
+    <t>comparatornoctlpins</t>
+  </si>
+  <si>
+    <t>ESDminiClamp6</t>
+  </si>
+  <si>
+    <t>timingskew</t>
+  </si>
+  <si>
+    <t>switchpulldown</t>
+  </si>
+  <si>
+    <t>resistordivider</t>
+  </si>
+  <si>
+    <t>delayclock</t>
+  </si>
+  <si>
+    <t>amux2</t>
+  </si>
+  <si>
     <t>wrapper</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>dff</t>
-  </si>
-  <si>
-    <t>drmmodule</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>tie</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>brick</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>resistor</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>oneshot</t>
-  </si>
-  <si>
-    <t>fetdn</t>
-  </si>
-  <si>
-    <t>currentlimitfet</t>
-  </si>
-  <si>
-    <t>comparatornoctlpins</t>
-  </si>
-  <si>
-    <t>ESDminiClamp6</t>
-  </si>
-  <si>
-    <t>timingskew</t>
-  </si>
-  <si>
-    <t>switchpulldown</t>
-  </si>
-  <si>
-    <t>resistordivider</t>
-  </si>
-  <si>
-    <t>delayclock</t>
-  </si>
-  <si>
-    <t>amux2</t>
-  </si>
-  <si>
     <t>vbuffer</t>
   </si>
   <si>
@@ -1299,6 +1808,9 @@
     <t>capacitorfixed</t>
   </si>
   <si>
+    <t>PEBBLEtiehi</t>
+  </si>
+  <si>
     <t>voltage2current</t>
   </si>
   <si>
@@ -1470,9 +1982,6 @@
     <t>ESDcore6 SYNC -&gt; GESD</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>FB</t>
   </si>
   <si>
@@ -1518,30 +2027,6 @@
     <t>ESDdiodeB2B PGND -&gt; GESD</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>DFTSDA</t>
-  </si>
-  <si>
-    <t>i2c_data_inout</t>
-  </si>
-  <si>
-    <t>ESDcore6 DFTSDA -&gt; GESD</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>DFTSCL</t>
-  </si>
-  <si>
-    <t>i2c_input_clock</t>
-  </si>
-  <si>
-    <t>ESDcore6 DFTSCL -&gt; GESD</t>
-  </si>
-  <si>
     <t>REGISTER ADDRESS REPORT</t>
   </si>
   <si>
@@ -1560,9 +2045,6 @@
     <t>FACTORY ADDRESS REPORT</t>
   </si>
   <si>
-    <t>TMB</t>
-  </si>
-  <si>
     <t>Bank</t>
   </si>
   <si>
@@ -1581,385 +2063,34 @@
     <t>rdl_data</t>
   </si>
   <si>
-    <t>Adjust_Minimum_off_time</t>
-  </si>
-  <si>
-    <t>CLOCKofftime</t>
-  </si>
-  <si>
-    <t>3:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,drm_hex0x02</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Adjust_Minimum_off_time', 'name': 'CLOCKofftime', 'enums': [{'desc': '0.0ns', 'name': 'Threshold_0.0ns'}, {'desc': '8.0ns', 'name': 'Threshold_8.0ns'}, {'desc': '16.0ns', 'name': 'Threshold_16.0ns'}, {'desc': '24.0ns', 'name': 'Threshold_24.0ns'}, {'desc': '32.0ns', 'name': 'Threshold_32.0ns'}, {'desc': '40.0ns', 'name': 'Threshold_40.0ns'}, {'desc': '48.0ns', 'name': 'Threshold_48.0ns'}, {'desc': '56.0ns', 'name': 'Threshold_56.0ns'}, {'desc': '64.0ns', 'name': 'Threshold_64.0ns'}, {'desc': '72.0ns', 'name': 'Threshold_72.0ns'}, {'desc': '80.0ns', 'name': 'Threshold_80.0ns'}, {'desc': '88.0ns', 'name': 'Threshold_88.0ns'}, {'desc': '96.0ns', 'name': 'Threshold_96.0ns'}, {'desc': '104.0ns', 'name': 'Threshold_104.0ns'}, {'desc': '112.0ns', 'name': 'Threshold_112.0ns'}, {'desc': '120.0ns', 'name': 'Threshold_120.0ns'}], 'function': 'range', 'range_lsb': 8.0, 'readwrite': 'readwrite', 'range_start': 0.0, 'range_units': 'ns'}]}</t>
-  </si>
-  <si>
-    <t>Algorithm5p9_STATE_control</t>
-  </si>
-  <si>
-    <t>Algorithm5p9_statecontrol</t>
-  </si>
-  <si>
-    <t>4:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCONTROL,XCONTROL,drm_hex0x03</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Algorithm5p9_STATE_control', 'name': 'Algorithm5p9_statecontrol', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>CONTROL_configuration</t>
-  </si>
-  <si>
-    <t>CONTROLconfiguration</t>
-  </si>
-  <si>
-    <t>2:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCONTROL,drm_hex0x04</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Operating_Mode', 'name': 'Operating_Mode', 'enums': [{'desc': 'Discontinous', 'name': 'Discontinous'}, {'desc': 'Continous', 'name': 'Continous'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'Blank_bottom', 'name': 'Blank_bottom', 'enums': [{'desc': 'Maximum_on_time_fault', 'name': 'Maximum_on_time_fault'}, {'desc': 'Blank_maximum_on_time', 'name': 'Blank_maximum_on_time'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'Blank_refresh', 'name': 'Blank_refresh', 'enums': [{'desc': 'Refresh_with_ok_driver', 'name': 'Refresh_with_ok_driver'}, {'desc': 'Blank_refresh', 'name': 'Blank_refresh'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>BBM_Status_Enabled</t>
-  </si>
-  <si>
-    <t>BBMstatus</t>
-  </si>
-  <si>
-    <t>0x05</t>
-  </si>
-  <si>
-    <t>1:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBBM,drm_hex0x05</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Bottom_status', 'name': 'Bottom_status', 'enums': [{'desc': 'Enable', 'name': 'Enable'}, {'desc': 'Disable', 'name': 'Disable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'Top_status', 'name': 'Top_status', 'enums': [{'desc': 'Enable', 'name': 'Enable'}, {'desc': 'Disable', 'name': 'Disable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>TOP_Switch_on_delay</t>
-  </si>
-  <si>
-    <t>TOPSWITCHstatusDELAY</t>
-  </si>
-  <si>
-    <t>6:2</t>
-  </si>
-  <si>
-    <t>{'nesto': 'timingskew_d7d32aa0', 'fields': [{'desc': 'TOPSWITCHstatusDELAY', 'name': 'TOPSWITCHstatusDELAY', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>BOT_Switch_on_delay</t>
-  </si>
-  <si>
-    <t>BOTTOMSWITCHstatusDELAY</t>
-  </si>
-  <si>
-    <t>{'nesto': 'timingskew_b5de11eb', 'fields': [{'desc': 'BOTTOMSWITCHstatusDELAY', 'name': 'BOTTOMSWITCHstatusDELAY', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Highside_Current_Limit_Trim</t>
-  </si>
-  <si>
-    <t>TOPSWITCHaccuracy</t>
-  </si>
-  <si>
-    <t>0x07</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XTOPSW,drm_hex0x07</t>
-  </si>
-  <si>
-    <t>{'nesto': 'currentlimitfet_e27944c0', 'fields': [{'desc': 'TOPSWITCHaccuracy', 'name': 'TOPSWITCHaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Disable_slope_current</t>
-  </si>
-  <si>
-    <t>DISABLEslope</t>
-  </si>
-  <si>
-    <t>5:5</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'SLOPE_curent', 'name': 'SLOPE_curent', 'enums': [{'desc': 'enable', 'name': 'enable'}, {'desc': 'disable', 'name': 'disable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>FAULTMANAGER_configuration</t>
-  </si>
-  <si>
-    <t>FAULTMANAGERconfiguration</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,drm_hex0x09</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'HICCUPmode', 'name': 'HICCUPmode', 'enums': [{'desc': 'Disable', 'name': 'Disable'}, {'desc': 'Enable', 'name': 'Enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'BLANKthermal', 'name': 'BLANKthermal', 'enums': [{'desc': 'Disable', 'name': 'Disable'}, {'desc': 'Enable', 'name': 'Enable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>REGUALTION_Configure_DEBUG_controls</t>
-  </si>
-  <si>
-    <t>REGULATIONtestmode</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XDEBUG,drm_hex0x0A</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'VC_override', 'name': 'VC_override', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'VSS_override', 'name': 'VSS_override', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'VSS_status', 'name': 'VSS_status', 'enums': [{'desc': 'Low', 'name': 'Low'}, {'desc': 'High', 'name': 'High'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Compensation_Resistor</t>
-  </si>
-  <si>
-    <t>RZCOMP</t>
-  </si>
-  <si>
-    <t>0x0B</t>
-  </si>
-  <si>
-    <t>XWALTZ,XREGULATION,XMAIN,XCOMPENSATION,drm_hex0x0B</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Compensation_Resistor', 'name': 'RZCOMP', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Compensation_Gain_resistance</t>
-  </si>
-  <si>
-    <t>GAINCOMP</t>
-  </si>
-  <si>
-    <t>4:3</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Compensation_Gain_resistance', 'name': 'GAINCOMP', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Compensation_Capacitor</t>
-  </si>
-  <si>
-    <t>CZCOMP</t>
-  </si>
-  <si>
-    <t>7:5</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Compensation_Capacitor', 'name': 'CZCOMP', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
-    <t>Regulation_output_ripple_in_DCM_mode</t>
-  </si>
-  <si>
-    <t>DCM_Output_Rripple</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XREGULATION,XMAIN,drm_hex0x0C</t>
-  </si>
-  <si>
-    <t>{'nesto': 'comparatornoctlpins_1b4420c5', 'fields': [{'desc': 'DCM_Output_Rripple', 'name': 'DCM_Output_Rripple', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>SEQUENCER1waltz_Rev1_STATE_control</t>
-  </si>
-  <si>
-    <t>SEQUENCER1waltz_Rev1_statecontrol</t>
-  </si>
-  <si>
-    <t>0x0D</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSEQUENCER,XSEQUENCER,drm_hex0x0D</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'SEQUENCER1waltz_Rev1_STATE_control', 'name': 'SEQUENCER1waltz_Rev1_statecontrol', 'enums': [{'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}, {'desc': '', 'name': ''}], 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Curvature_Correction_Accuracy</t>
-  </si>
-  <si>
-    <t>REFCCacc</t>
-  </si>
-  <si>
-    <t>0x0E</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSERVICE,XMAIN,drm_hex0x0E</t>
-  </si>
-  <si>
-    <t>{'nesto': 'reference_4fa591be', 'fields': [{'desc': 'REFCCacc', 'name': 'REFCCacc', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Softstart_configuration</t>
-  </si>
-  <si>
-    <t>SOFTSTARTconfiguration</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XSOFTSTART,drm_hex0x0F</t>
-  </si>
-  <si>
-    <t>{'nesto': '', 'fields': [{'desc': 'Softstart_time', 'name': 'Softstart_time', 'enums': [{'desc': '4ms', 'name': '4ms'}, {'desc': '1ms', 'name': '1ms'}], 'function': 'function', 'readwrite': 'readwrite'}, {'desc': 'Halfway', 'name': 'Halfway', 'enums': [{'desc': 'disable', 'name': 'disable'}, {'desc': 'enable', 'name': 'enable'}], 'function': 'function', 'readwrite': 'readwrite'}]}</t>
-  </si>
-  <si>
     <t>ACCURACY ADDRESS REPORT</t>
   </si>
   <si>
-    <t>CLOCK_accuracy_at_400KHz_50K</t>
-  </si>
-  <si>
-    <t>CLOCKaccuracy</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XCLOCK,XMAIN,drm_hex0x01</t>
-  </si>
-  <si>
-    <t>{'nesto': 'oscillator_d9a22b83', 'fields': [{'desc': 'CLOCKaccuracy', 'name': 'CLOCKaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Lowside_Negative_Current_Accuracy</t>
-  </si>
-  <si>
-    <t>botswinegacc</t>
-  </si>
-  <si>
-    <t>0x06</t>
-  </si>
-  <si>
-    <t>7:0</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW,drm_hex0x06</t>
-  </si>
-  <si>
-    <t>{'nesto': 'currentlimitfet_282c42a8', 'fields': [{'desc': 'botswinegacc', 'name': 'botswinegacc', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>BottomSW_Zcross</t>
-  </si>
-  <si>
-    <t>botswzcrossacc</t>
-  </si>
-  <si>
-    <t>{'nesto': 'currentlimitfet_bdeab8a2', 'fields': [{'desc': 'botswzcrossacc', 'name': 'botswzcrossacc', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Lowside_Zero_Cross_Accuracy</t>
-  </si>
-  <si>
-    <t>botswipeakacc</t>
-  </si>
-  <si>
-    <t>{'nesto': 'currentlimitfet_2899e616', 'fields': [{'desc': 'botswipeakacc', 'name': 'botswipeakacc', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Trim_Slope_Comp_Amplitude</t>
-  </si>
-  <si>
-    <t>SLOPECOMPENSATIONaccuracy</t>
-  </si>
-  <si>
-    <t>{'nesto': 'slopecomp_00a4cb3c', 'fields': [{'desc': 'SLOPECOMPENSATIONaccuracy', 'name': 'SLOPECOMPENSATIONaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Thermal_shutdowen</t>
-  </si>
-  <si>
-    <t>THERMALaccuracy</t>
-  </si>
-  <si>
-    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XMAIN,drm_hex0x08</t>
-  </si>
-  <si>
-    <t>{'nesto': 'thermal_b84c0fbd', 'fields': [{'desc': 'THERMALaccuracy', 'name': 'THERMALaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>Voltage_Control_Node_Clamp_Accuracy_to_3V</t>
-  </si>
-  <si>
-    <t>VCclampACCURACY</t>
-  </si>
-  <si>
-    <t>{'nesto': 'clamp_57e24cde', 'fields': [{'desc': 'VCclampACCURACY', 'name': 'VCclampACCURACY', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>FB_Reference_buffer_Accuracy</t>
-  </si>
-  <si>
-    <t>REFbufferACCURACY</t>
-  </si>
-  <si>
-    <t>6:0</t>
-  </si>
-  <si>
-    <t>{'nesto': 'vbuffer_602daa59', 'fields': [{'desc': 'REFbufferACCURACY', 'name': 'REFbufferACCURACY', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>GMaccuracy</t>
-  </si>
-  <si>
-    <t>{'nesto': 'gm_6be6af5d', 'fields': [{'desc': 'GMaccuracy', 'name': 'GMaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>5:0</t>
-  </si>
-  <si>
-    <t>VCC_5V_Accuracy</t>
-  </si>
-  <si>
-    <t>VCCaccuracy</t>
-  </si>
-  <si>
-    <t>{'nesto': 'vbias_06fccf36', 'fields': [{'desc': 'VCCaccuracy', 'name': 'VCCaccuracy', 'function': 'code', 'readwrite': 'readonly'}]}</t>
-  </si>
-  <si>
-    <t>DFT PROBE ADDRESS REPORT</t>
-  </si>
-  <si>
-    <t>Pad Number</t>
-  </si>
-  <si>
-    <t>PADs</t>
-  </si>
-  <si>
-    <t>{}</t>
-  </si>
-  <si>
-    <t>DFT HIJACK ADDRESS REPORT</t>
-  </si>
-  <si>
-    <t>DFT DBUF ADDRESS REPORT</t>
-  </si>
-  <si>
-    <t>TMA SUMMARY REPORT (DFTs)</t>
-  </si>
-  <si>
-    <t>Slave Address 0x54</t>
-  </si>
-  <si>
-    <t>DFT CELL GLOBAL ADDRESS REPORT</t>
-  </si>
-  <si>
-    <t>DFT CELL DBUF ADDRESS REPORT</t>
-  </si>
-  <si>
-    <t>DFT CELL ADDRESS REPORT (Rich)</t>
-  </si>
-  <si>
-    <t>DFT dftprobe Checker</t>
-  </si>
-  <si>
     <t>DFT dfthijack Checker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XWALTZ,XceleraCORE,XCLOCK,XDEBUG 6V connects to </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XWALTZ,XceleraCORE,XDRIVER,XDEBUG 6V connects to </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG 6V connects to </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XFAULTMANAGER,XDEBUG 6V connects to XU23.a0 (6V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG 6V connects to </t>
+  </si>
+  <si>
+    <t>XWALTZ,XceleraCORE,XPOWERGOOD,XDEBUG 6V connects to XU18.a0 (6V)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XWALTZ,XceleraCORE,XREGULATION,XDEBUG 6V connects to </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XWALTZ,XceleraCORE,XSOFTSTART,XDEBUG 6V connects to </t>
   </si>
   <si>
     <t>Pad Checker</t>
@@ -2384,7 +2515,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2404,7 +2535,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2419,7 +2550,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -2434,17 +2565,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2459,12 +2590,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2479,17 +2610,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2504,12 +2635,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -2524,7 +2655,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2544,127 +2675,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>59</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>64</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>65</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>68</v>
+        <v>191</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>69</v>
+        <v>192</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>72</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>73</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>76</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2674,162 +2805,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>90</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2844,17 +2830,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -3074,17 +3060,222 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="1" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -3099,17 +3290,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3124,52 +3315,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>103</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>110</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3184,81 +3375,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>117</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>247</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>249</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>124</v>
+        <v>253</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3266,1268 +3457,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>128</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>129</v>
+        <v>258</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>130</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>131</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>133</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>134</v>
+        <v>263</v>
       </c>
       <c r="B20" t="s">
-        <v>120</v>
+        <v>248</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>264</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>136</v>
+        <v>265</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>266</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>138</v>
+        <v>267</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>141</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s">
-        <v>142</v>
+        <v>271</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>274</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>276</v>
       </c>
       <c r="B33" t="s">
-        <v>148</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>149</v>
+        <v>278</v>
       </c>
       <c r="B34" t="s">
-        <v>150</v>
+        <v>279</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>280</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>281</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>153</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
-        <v>154</v>
+        <v>283</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>155</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>156</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>157</v>
+        <v>286</v>
       </c>
       <c r="B39" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>159</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>160</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>161</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>162</v>
+        <v>291</v>
       </c>
       <c r="B43" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>164</v>
+        <v>293</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>165</v>
+        <v>294</v>
       </c>
       <c r="B46" t="s">
-        <v>166</v>
+        <v>295</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>296</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>297</v>
       </c>
       <c r="B48" t="s">
-        <v>158</v>
+        <v>287</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>298</v>
       </c>
       <c r="B49" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>170</v>
+        <v>299</v>
       </c>
       <c r="B50" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>171</v>
+        <v>300</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>301</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>173</v>
+        <v>302</v>
       </c>
       <c r="B52" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>174</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>175</v>
+        <v>304</v>
       </c>
       <c r="B55" t="s">
-        <v>176</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>306</v>
       </c>
       <c r="B56" t="s">
-        <v>178</v>
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>179</v>
+        <v>308</v>
       </c>
       <c r="B57" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>180</v>
+        <v>309</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>181</v>
+        <v>310</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>182</v>
+        <v>311</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>183</v>
+        <v>312</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>184</v>
+        <v>313</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="B64" t="s">
-        <v>186</v>
+        <v>315</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>187</v>
+        <v>316</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>188</v>
+        <v>317</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>189</v>
+        <v>318</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>191</v>
+        <v>320</v>
       </c>
       <c r="B68" t="s">
-        <v>192</v>
+        <v>321</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>193</v>
+        <v>322</v>
       </c>
       <c r="B69" t="s">
-        <v>190</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>323</v>
       </c>
       <c r="B70" t="s">
-        <v>192</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>195</v>
+        <v>324</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>325</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>198</v>
+        <v>327</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>199</v>
+        <v>328</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>329</v>
       </c>
       <c r="B77" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>330</v>
       </c>
       <c r="B78" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>332</v>
       </c>
       <c r="B80" t="s">
-        <v>204</v>
+        <v>333</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>205</v>
+        <v>334</v>
       </c>
       <c r="B81" t="s">
-        <v>206</v>
+        <v>335</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>336</v>
       </c>
       <c r="B82" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>337</v>
       </c>
       <c r="B83" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="B84" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>210</v>
+        <v>339</v>
       </c>
       <c r="B85" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>211</v>
+        <v>340</v>
       </c>
       <c r="B86" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>212</v>
+        <v>341</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>213</v>
+        <v>342</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="B89" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>215</v>
+        <v>344</v>
       </c>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>345</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>217</v>
+        <v>346</v>
       </c>
       <c r="B91" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>218</v>
+        <v>347</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>219</v>
+        <v>348</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>220</v>
+        <v>349</v>
       </c>
       <c r="B94" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>221</v>
+        <v>350</v>
       </c>
       <c r="B95" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>222</v>
+        <v>351</v>
       </c>
       <c r="B96" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>223</v>
+        <v>352</v>
       </c>
       <c r="B97" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="B98" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>225</v>
+        <v>354</v>
       </c>
       <c r="B99" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>226</v>
+        <v>355</v>
       </c>
       <c r="B100" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>227</v>
+        <v>356</v>
       </c>
       <c r="B101" t="s">
-        <v>228</v>
+        <v>357</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>229</v>
+        <v>358</v>
       </c>
       <c r="B102" t="s">
-        <v>117</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>230</v>
+        <v>359</v>
       </c>
       <c r="B103" t="s">
-        <v>150</v>
+        <v>279</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>231</v>
+        <v>360</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>361</v>
       </c>
       <c r="B106" t="s">
-        <v>233</v>
+        <v>362</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>234</v>
+        <v>363</v>
       </c>
       <c r="B107" t="s">
-        <v>235</v>
+        <v>364</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>236</v>
+        <v>365</v>
       </c>
       <c r="B108" t="s">
-        <v>237</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>238</v>
+        <v>367</v>
       </c>
       <c r="B109" t="s">
-        <v>239</v>
+        <v>368</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>240</v>
+        <v>369</v>
       </c>
       <c r="B110" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>242</v>
+        <v>371</v>
       </c>
       <c r="B111" t="s">
-        <v>243</v>
+        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>244</v>
+        <v>373</v>
       </c>
       <c r="B112" t="s">
-        <v>245</v>
+        <v>374</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>246</v>
+        <v>375</v>
       </c>
       <c r="B113" t="s">
-        <v>247</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>248</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>249</v>
+        <v>378</v>
       </c>
       <c r="B116" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>250</v>
+        <v>379</v>
       </c>
       <c r="B117" t="s">
-        <v>251</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>252</v>
+        <v>381</v>
       </c>
       <c r="B118" t="s">
-        <v>253</v>
+        <v>382</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>254</v>
+        <v>383</v>
       </c>
       <c r="B119" t="s">
-        <v>255</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>256</v>
+        <v>385</v>
       </c>
       <c r="B120" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>258</v>
+        <v>387</v>
       </c>
       <c r="B121" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>260</v>
+        <v>389</v>
       </c>
       <c r="B122" t="s">
-        <v>261</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>262</v>
+        <v>391</v>
       </c>
       <c r="B123" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>263</v>
+        <v>392</v>
       </c>
       <c r="B124" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>264</v>
+        <v>393</v>
       </c>
       <c r="B125" t="s">
-        <v>261</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>265</v>
+        <v>394</v>
       </c>
       <c r="B126" t="s">
-        <v>266</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>267</v>
+        <v>396</v>
       </c>
       <c r="B127" t="s">
-        <v>268</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>269</v>
+        <v>398</v>
       </c>
       <c r="B128" t="s">
-        <v>270</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>271</v>
+        <v>400</v>
       </c>
       <c r="B129" t="s">
-        <v>272</v>
+        <v>401</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>273</v>
+        <v>402</v>
       </c>
       <c r="B130" t="s">
-        <v>274</v>
+        <v>403</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>224</v>
+        <v>353</v>
       </c>
       <c r="B131" t="s">
-        <v>275</v>
+        <v>404</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>225</v>
+        <v>354</v>
       </c>
       <c r="B132" t="s">
-        <v>276</v>
+        <v>405</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>227</v>
+        <v>356</v>
       </c>
       <c r="B133" t="s">
-        <v>277</v>
+        <v>406</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>226</v>
+        <v>355</v>
       </c>
       <c r="B134" t="s">
-        <v>278</v>
+        <v>407</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>279</v>
+        <v>408</v>
       </c>
       <c r="B135" t="s">
-        <v>163</v>
+        <v>292</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>280</v>
+        <v>409</v>
       </c>
       <c r="B136" t="s">
-        <v>281</v>
+        <v>410</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>282</v>
+        <v>411</v>
       </c>
       <c r="B137" t="s">
-        <v>283</v>
+        <v>412</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>284</v>
+        <v>413</v>
       </c>
       <c r="B138" t="s">
-        <v>285</v>
+        <v>414</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>286</v>
+        <v>415</v>
       </c>
       <c r="B139" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>288</v>
+        <v>417</v>
       </c>
       <c r="B140" t="s">
-        <v>289</v>
+        <v>418</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>290</v>
+        <v>419</v>
       </c>
       <c r="B141" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>291</v>
+        <v>420</v>
       </c>
       <c r="B142" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>292</v>
+        <v>421</v>
       </c>
       <c r="B143" t="s">
-        <v>261</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>293</v>
+        <v>422</v>
       </c>
       <c r="B144" t="s">
-        <v>266</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>294</v>
+        <v>423</v>
       </c>
       <c r="B145" t="s">
-        <v>268</v>
+        <v>397</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>295</v>
+        <v>424</v>
       </c>
       <c r="B146" t="s">
-        <v>270</v>
+        <v>399</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>296</v>
+        <v>425</v>
       </c>
       <c r="B147" t="s">
-        <v>272</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>297</v>
+        <v>426</v>
       </c>
       <c r="B148" t="s">
-        <v>274</v>
+        <v>403</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>298</v>
+        <v>427</v>
       </c>
       <c r="B149" t="s">
-        <v>299</v>
+        <v>428</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>300</v>
+        <v>429</v>
       </c>
       <c r="B150" t="s">
-        <v>301</v>
+        <v>430</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>302</v>
+        <v>431</v>
       </c>
       <c r="B151" t="s">
-        <v>303</v>
+        <v>432</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>304</v>
+        <v>433</v>
       </c>
       <c r="B152" t="s">
-        <v>305</v>
+        <v>434</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>306</v>
+        <v>435</v>
       </c>
       <c r="B153" t="s">
-        <v>307</v>
+        <v>436</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>308</v>
+        <v>437</v>
       </c>
       <c r="B154" t="s">
-        <v>309</v>
+        <v>438</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>310</v>
+        <v>439</v>
       </c>
       <c r="B155" t="s">
-        <v>311</v>
+        <v>440</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>312</v>
+        <v>441</v>
       </c>
       <c r="B156" t="s">
-        <v>313</v>
+        <v>442</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>314</v>
+        <v>443</v>
       </c>
       <c r="B157" t="s">
-        <v>315</v>
+        <v>444</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>316</v>
+        <v>445</v>
       </c>
       <c r="B158" t="s">
-        <v>317</v>
+        <v>446</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>318</v>
+        <v>447</v>
       </c>
       <c r="B159" t="s">
-        <v>319</v>
+        <v>448</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>320</v>
+        <v>449</v>
       </c>
       <c r="B160" t="s">
-        <v>321</v>
+        <v>450</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>322</v>
+        <v>451</v>
       </c>
       <c r="B161" t="s">
-        <v>323</v>
+        <v>452</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>324</v>
+        <v>453</v>
       </c>
       <c r="B162" t="s">
-        <v>325</v>
+        <v>454</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>326</v>
+        <v>455</v>
       </c>
       <c r="B163" t="s">
-        <v>327</v>
+        <v>456</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>328</v>
+        <v>457</v>
       </c>
       <c r="B164" t="s">
-        <v>329</v>
+        <v>458</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>330</v>
+        <v>459</v>
       </c>
       <c r="B165" t="s">
-        <v>331</v>
+        <v>460</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>332</v>
+        <v>461</v>
       </c>
       <c r="B166" t="s">
-        <v>305</v>
+        <v>434</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>333</v>
+        <v>462</v>
       </c>
       <c r="B167" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>334</v>
+        <v>463</v>
       </c>
       <c r="B168" t="s">
-        <v>289</v>
+        <v>418</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>335</v>
+        <v>464</v>
       </c>
       <c r="B169" t="s">
-        <v>146</v>
+        <v>275</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>336</v>
+        <v>465</v>
       </c>
       <c r="B170" t="s">
-        <v>337</v>
+        <v>466</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>338</v>
+        <v>467</v>
       </c>
       <c r="B171" t="s">
-        <v>339</v>
+        <v>468</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>340</v>
+        <v>469</v>
       </c>
       <c r="B172" t="s">
-        <v>341</v>
+        <v>470</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>342</v>
+        <v>471</v>
       </c>
       <c r="B173" t="s">
-        <v>343</v>
+        <v>472</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>344</v>
+        <v>473</v>
       </c>
       <c r="B174" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>345</v>
+        <v>474</v>
       </c>
       <c r="B175" t="s">
-        <v>257</v>
+        <v>386</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>346</v>
+        <v>475</v>
       </c>
       <c r="B176" t="s">
-        <v>259</v>
+        <v>388</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>347</v>
+        <v>476</v>
       </c>
       <c r="B177" t="s">
-        <v>299</v>
+        <v>428</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>348</v>
+        <v>477</v>
       </c>
       <c r="B178" t="s">
-        <v>283</v>
+        <v>412</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>349</v>
+        <v>478</v>
       </c>
       <c r="B179" t="s">
-        <v>350</v>
+        <v>479</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>351</v>
+        <v>480</v>
       </c>
       <c r="B180" t="s">
-        <v>287</v>
+        <v>416</v>
       </c>
     </row>
   </sheetData>
@@ -4537,12 +4728,76 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>352</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="1" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -4552,31 +4807,12 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>358</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
@@ -4586,473 +4822,381 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>360</v>
+        <v>483</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>484</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>362</v>
+        <v>205</v>
       </c>
       <c r="B5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>496</v>
+      </c>
+      <c r="C5" t="s">
+        <v>416</v>
+      </c>
+      <c r="D5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>364</v>
+        <v>205</v>
       </c>
       <c r="B6" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>498</v>
+      </c>
+      <c r="C6" t="s">
+        <v>418</v>
+      </c>
+      <c r="D6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>366</v>
+        <v>208</v>
       </c>
       <c r="B7" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>500</v>
+      </c>
+      <c r="C7" t="s">
+        <v>275</v>
+      </c>
+      <c r="D7" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>368</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>502</v>
+      </c>
+      <c r="C8" t="s">
+        <v>466</v>
+      </c>
+      <c r="D8" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>370</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>503</v>
+      </c>
+      <c r="C9" t="s">
+        <v>504</v>
+      </c>
+      <c r="D9" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>372</v>
+        <v>212</v>
       </c>
       <c r="B10" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>505</v>
+      </c>
+      <c r="C10" t="s">
+        <v>506</v>
+      </c>
+      <c r="D10" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>374</v>
+        <v>213</v>
       </c>
       <c r="B11" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>507</v>
+      </c>
+      <c r="C11" t="s">
+        <v>508</v>
+      </c>
+      <c r="D11" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>376</v>
+        <v>213</v>
       </c>
       <c r="B12" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>509</v>
+      </c>
+      <c r="C12" t="s">
+        <v>468</v>
+      </c>
+      <c r="D12" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>378</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>510</v>
+      </c>
+      <c r="C13" t="s">
+        <v>470</v>
+      </c>
+      <c r="D13" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>216</v>
       </c>
       <c r="B14" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>511</v>
+      </c>
+      <c r="C14" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>382</v>
+        <v>216</v>
       </c>
       <c r="B15" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>512</v>
+      </c>
+      <c r="C15" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>384</v>
+        <v>216</v>
       </c>
       <c r="B16" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>514</v>
+      </c>
+      <c r="C16" t="s">
+        <v>414</v>
+      </c>
+      <c r="D16" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" t="s">
+        <v>515</v>
+      </c>
+      <c r="C17" t="s">
+        <v>516</v>
+      </c>
+      <c r="D17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>220</v>
+      </c>
+      <c r="B18" t="s">
+        <v>517</v>
+      </c>
+      <c r="C18" t="s">
+        <v>518</v>
+      </c>
+      <c r="D18" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>220</v>
+      </c>
+      <c r="B19" t="s">
+        <v>519</v>
+      </c>
+      <c r="C19" t="s">
+        <v>345</v>
+      </c>
+      <c r="D19" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>221</v>
+      </c>
+      <c r="B20" t="s">
+        <v>520</v>
+      </c>
+      <c r="C20" t="s">
         <v>386</v>
       </c>
-      <c r="B17" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>387</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="D20" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C21" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>389</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="D21" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>224</v>
+      </c>
+      <c r="B22" t="s">
+        <v>522</v>
+      </c>
+      <c r="C22" t="s">
         <v>390</v>
       </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>391</v>
-      </c>
-      <c r="B20" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>392</v>
-      </c>
-      <c r="B21" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" t="s">
-        <v>394</v>
-      </c>
-      <c r="B22" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+      <c r="D22" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B23" t="s">
+        <v>523</v>
+      </c>
+      <c r="C23" t="s">
         <v>395</v>
       </c>
-      <c r="B23" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+      <c r="D23" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" t="s">
+        <v>25</v>
+      </c>
+      <c r="B24" t="s">
+        <v>524</v>
+      </c>
+      <c r="C24" t="s">
         <v>397</v>
       </c>
-      <c r="B24" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
+      <c r="D24" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>398</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
+        <v>525</v>
+      </c>
+      <c r="C25" t="s">
+        <v>399</v>
+      </c>
+      <c r="D25" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>399</v>
+        <v>226</v>
       </c>
       <c r="B26" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
+        <v>526</v>
+      </c>
+      <c r="C26" t="s">
+        <v>401</v>
+      </c>
+      <c r="D26" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>400</v>
+        <v>226</v>
       </c>
       <c r="B27" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+        <v>527</v>
+      </c>
+      <c r="C27" t="s">
+        <v>403</v>
+      </c>
+      <c r="D27" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>401</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>528</v>
+      </c>
+      <c r="C28" t="s">
+        <v>428</v>
+      </c>
+      <c r="D28" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>402</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>403</v>
-      </c>
-      <c r="B30" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>404</v>
-      </c>
-      <c r="B31" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>405</v>
-      </c>
-      <c r="B32" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>406</v>
-      </c>
-      <c r="B33" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>407</v>
-      </c>
-      <c r="B34" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>408</v>
-      </c>
-      <c r="B35" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>409</v>
-      </c>
-      <c r="B36" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>410</v>
-      </c>
-      <c r="B37" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>411</v>
-      </c>
-      <c r="B38" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>412</v>
-      </c>
-      <c r="B39" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>413</v>
-      </c>
-      <c r="B40" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>414</v>
-      </c>
-      <c r="B41" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>415</v>
-      </c>
-      <c r="B42" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>416</v>
-      </c>
-      <c r="B43" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>417</v>
-      </c>
-      <c r="B44" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>418</v>
-      </c>
-      <c r="B45" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>419</v>
-      </c>
-      <c r="B46" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>420</v>
-      </c>
-      <c r="B47" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>421</v>
-      </c>
-      <c r="B48" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>422</v>
-      </c>
-      <c r="B49" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>423</v>
-      </c>
-      <c r="B50" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>424</v>
-      </c>
-      <c r="B51" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>425</v>
-      </c>
-      <c r="B52" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" t="s">
-        <v>426</v>
-      </c>
-      <c r="B53" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" t="s">
-        <v>427</v>
-      </c>
-      <c r="B54" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>428</v>
-      </c>
-      <c r="B55" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>429</v>
-      </c>
-      <c r="B56" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>430</v>
-      </c>
-      <c r="B57" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" t="s">
-        <v>431</v>
-      </c>
-      <c r="B58" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" t="s">
-        <v>432</v>
-      </c>
-      <c r="B59" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>433</v>
-      </c>
-      <c r="B60" t="s">
-        <v>228</v>
+        <v>529</v>
+      </c>
+      <c r="C29" t="s">
+        <v>530</v>
+      </c>
+      <c r="D29" t="s">
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -5062,533 +5206,505 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>436</v>
+        <v>532</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>228</v>
+        <v>534</v>
       </c>
       <c r="B5" t="s">
-        <v>447</v>
-      </c>
-      <c r="C5" t="s">
-        <v>448</v>
-      </c>
-      <c r="D5" t="s">
-        <v>192</v>
-      </c>
-      <c r="E5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F5" t="s">
-        <v>450</v>
-      </c>
-      <c r="G5" t="s">
-        <v>449</v>
-      </c>
-      <c r="H5" t="s">
-        <v>451</v>
-      </c>
-      <c r="I5" t="s">
-        <v>452</v>
-      </c>
-      <c r="J5" t="s">
-        <v>453</v>
-      </c>
-      <c r="K5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>536</v>
       </c>
       <c r="B6" t="s">
-        <v>455</v>
-      </c>
-      <c r="C6" t="s">
-        <v>456</v>
-      </c>
-      <c r="D6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E6" t="s">
-        <v>449</v>
-      </c>
-      <c r="F6" t="s">
-        <v>450</v>
-      </c>
-      <c r="G6" t="s">
-        <v>449</v>
-      </c>
-      <c r="H6" t="s">
-        <v>451</v>
-      </c>
-      <c r="I6" t="s">
-        <v>457</v>
-      </c>
-      <c r="J6" t="s">
-        <v>453</v>
-      </c>
-      <c r="K6" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>538</v>
       </c>
       <c r="B7" t="s">
-        <v>458</v>
-      </c>
-      <c r="C7" t="s">
-        <v>459</v>
-      </c>
-      <c r="D7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E7" t="s">
-        <v>449</v>
-      </c>
-      <c r="F7" t="s">
-        <v>150</v>
-      </c>
-      <c r="G7" t="s">
-        <v>449</v>
-      </c>
-      <c r="H7" t="s">
-        <v>451</v>
-      </c>
-      <c r="I7" t="s">
-        <v>460</v>
-      </c>
-      <c r="J7" t="s">
-        <v>453</v>
-      </c>
-      <c r="K7" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>540</v>
       </c>
       <c r="B8" t="s">
-        <v>461</v>
-      </c>
-      <c r="C8" t="s">
-        <v>462</v>
-      </c>
-      <c r="D8" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" t="s">
-        <v>449</v>
-      </c>
-      <c r="F8" t="s">
-        <v>150</v>
-      </c>
-      <c r="G8" t="s">
-        <v>449</v>
-      </c>
-      <c r="H8" t="s">
-        <v>451</v>
-      </c>
-      <c r="I8" t="s">
-        <v>463</v>
-      </c>
-      <c r="J8" t="s">
-        <v>453</v>
-      </c>
-      <c r="K8" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>542</v>
       </c>
       <c r="B9" t="s">
-        <v>464</v>
-      </c>
-      <c r="C9" t="s">
-        <v>465</v>
-      </c>
-      <c r="D9" t="s">
-        <v>192</v>
-      </c>
-      <c r="E9" t="s">
-        <v>449</v>
-      </c>
-      <c r="F9" t="s">
-        <v>150</v>
-      </c>
-      <c r="G9" t="s">
-        <v>449</v>
-      </c>
-      <c r="H9" t="s">
-        <v>451</v>
-      </c>
-      <c r="I9" t="s">
-        <v>466</v>
-      </c>
-      <c r="J9" t="s">
-        <v>453</v>
-      </c>
-      <c r="K9" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>544</v>
       </c>
       <c r="B10" t="s">
-        <v>467</v>
-      </c>
-      <c r="C10" t="s">
-        <v>468</v>
-      </c>
-      <c r="D10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E10" t="s">
-        <v>449</v>
-      </c>
-      <c r="F10" t="s">
-        <v>150</v>
-      </c>
-      <c r="G10" t="s">
-        <v>449</v>
-      </c>
-      <c r="H10" t="s">
-        <v>451</v>
-      </c>
-      <c r="I10" t="s">
-        <v>469</v>
-      </c>
-      <c r="J10" t="s">
-        <v>453</v>
-      </c>
-      <c r="K10" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>470</v>
+        <v>545</v>
       </c>
       <c r="B11" t="s">
-        <v>471</v>
-      </c>
-      <c r="C11" t="s">
-        <v>472</v>
-      </c>
-      <c r="D11" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" t="s">
-        <v>449</v>
-      </c>
-      <c r="F11" t="s">
-        <v>150</v>
-      </c>
-      <c r="G11" t="s">
-        <v>449</v>
-      </c>
-      <c r="H11" t="s">
-        <v>451</v>
-      </c>
-      <c r="I11" t="s">
-        <v>473</v>
-      </c>
-      <c r="J11" t="s">
-        <v>453</v>
-      </c>
-      <c r="K11" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>546</v>
       </c>
       <c r="B12" t="s">
-        <v>449</v>
-      </c>
-      <c r="C12" t="s">
-        <v>474</v>
-      </c>
-      <c r="D12" t="s">
-        <v>192</v>
-      </c>
-      <c r="E12" t="s">
-        <v>449</v>
-      </c>
-      <c r="F12" t="s">
-        <v>190</v>
-      </c>
-      <c r="G12" t="s">
-        <v>449</v>
-      </c>
-      <c r="H12" t="s">
-        <v>451</v>
-      </c>
-      <c r="J12" t="s">
-        <v>453</v>
-      </c>
-      <c r="K12" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>393</v>
+        <v>548</v>
       </c>
       <c r="B13" t="s">
-        <v>475</v>
-      </c>
-      <c r="C13" t="s">
-        <v>476</v>
-      </c>
-      <c r="D13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E13" t="s">
-        <v>449</v>
-      </c>
-      <c r="F13" t="s">
-        <v>477</v>
-      </c>
-      <c r="G13" t="s">
-        <v>449</v>
-      </c>
-      <c r="H13" t="s">
-        <v>451</v>
-      </c>
-      <c r="I13" t="s">
-        <v>478</v>
-      </c>
-      <c r="J13" t="s">
-        <v>453</v>
-      </c>
-      <c r="K13" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>245</v>
+        <v>550</v>
       </c>
       <c r="B14" t="s">
-        <v>479</v>
-      </c>
-      <c r="C14" t="s">
-        <v>480</v>
-      </c>
-      <c r="D14" t="s">
-        <v>192</v>
-      </c>
-      <c r="E14" t="s">
-        <v>449</v>
-      </c>
-      <c r="F14" t="s">
-        <v>453</v>
-      </c>
-      <c r="G14" t="s">
-        <v>453</v>
-      </c>
-      <c r="H14" t="s">
-        <v>451</v>
-      </c>
-      <c r="J14" t="s">
-        <v>453</v>
-      </c>
-      <c r="K14" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>552</v>
       </c>
       <c r="B15" t="s">
-        <v>481</v>
-      </c>
-      <c r="C15" t="s">
-        <v>482</v>
-      </c>
-      <c r="D15" t="s">
-        <v>453</v>
-      </c>
-      <c r="E15" t="s">
-        <v>453</v>
-      </c>
-      <c r="F15" t="s">
-        <v>453</v>
-      </c>
-      <c r="G15" t="s">
-        <v>453</v>
-      </c>
-      <c r="H15" t="s">
-        <v>451</v>
-      </c>
-      <c r="J15" t="s">
-        <v>453</v>
-      </c>
-      <c r="K15" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>554</v>
       </c>
       <c r="B16" t="s">
-        <v>483</v>
-      </c>
-      <c r="C16" t="s">
-        <v>484</v>
-      </c>
-      <c r="D16" t="s">
-        <v>192</v>
-      </c>
-      <c r="E16" t="s">
-        <v>449</v>
-      </c>
-      <c r="F16" t="s">
-        <v>190</v>
-      </c>
-      <c r="G16" t="s">
-        <v>449</v>
-      </c>
-      <c r="H16" t="s">
-        <v>451</v>
-      </c>
-      <c r="I16" t="s">
-        <v>485</v>
-      </c>
-      <c r="J16" t="s">
-        <v>453</v>
-      </c>
-      <c r="K16" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>486</v>
+        <v>556</v>
       </c>
       <c r="B17" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>558</v>
+      </c>
+      <c r="B18" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>559</v>
+      </c>
+      <c r="B19" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>560</v>
+      </c>
+      <c r="B20" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>562</v>
+      </c>
+      <c r="B21" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>563</v>
+      </c>
+      <c r="B22" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>565</v>
+      </c>
+      <c r="B23" t="s">
         <v>487</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>566</v>
+      </c>
+      <c r="B24" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>567</v>
+      </c>
+      <c r="B25" t="s">
         <v>488</v>
       </c>
-      <c r="D17" t="s">
-        <v>192</v>
-      </c>
-      <c r="E17" t="s">
-        <v>449</v>
-      </c>
-      <c r="F17" t="s">
-        <v>150</v>
-      </c>
-      <c r="G17" t="s">
-        <v>449</v>
-      </c>
-      <c r="H17" t="s">
-        <v>451</v>
-      </c>
-      <c r="I17" t="s">
-        <v>489</v>
-      </c>
-      <c r="J17" t="s">
-        <v>453</v>
-      </c>
-      <c r="K17" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>490</v>
-      </c>
-      <c r="B18" t="s">
-        <v>491</v>
-      </c>
-      <c r="C18" t="s">
-        <v>492</v>
-      </c>
-      <c r="D18" t="s">
-        <v>192</v>
-      </c>
-      <c r="E18" t="s">
-        <v>449</v>
-      </c>
-      <c r="F18" t="s">
-        <v>150</v>
-      </c>
-      <c r="G18" t="s">
-        <v>449</v>
-      </c>
-      <c r="H18" t="s">
-        <v>451</v>
-      </c>
-      <c r="I18" t="s">
-        <v>493</v>
-      </c>
-      <c r="J18" t="s">
-        <v>453</v>
-      </c>
-      <c r="K18" t="s">
-        <v>454</v>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>568</v>
+      </c>
+      <c r="B26" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>569</v>
+      </c>
+      <c r="B27" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>570</v>
+      </c>
+      <c r="B28" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>571</v>
+      </c>
+      <c r="B29" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>572</v>
+      </c>
+      <c r="B30" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>573</v>
+      </c>
+      <c r="B31" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>574</v>
+      </c>
+      <c r="B32" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>575</v>
+      </c>
+      <c r="B33" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>576</v>
+      </c>
+      <c r="B34" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>577</v>
+      </c>
+      <c r="B35" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>578</v>
+      </c>
+      <c r="B36" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>579</v>
+      </c>
+      <c r="B37" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>580</v>
+      </c>
+      <c r="B38" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>581</v>
+      </c>
+      <c r="B39" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>582</v>
+      </c>
+      <c r="B40" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>583</v>
+      </c>
+      <c r="B41" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>584</v>
+      </c>
+      <c r="B42" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>585</v>
+      </c>
+      <c r="B43" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>586</v>
+      </c>
+      <c r="B44" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>587</v>
+      </c>
+      <c r="B45" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>588</v>
+      </c>
+      <c r="B46" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>589</v>
+      </c>
+      <c r="B47" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>590</v>
+      </c>
+      <c r="B48" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>591</v>
+      </c>
+      <c r="B49" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>592</v>
+      </c>
+      <c r="B50" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>593</v>
+      </c>
+      <c r="B51" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>594</v>
+      </c>
+      <c r="B52" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>595</v>
+      </c>
+      <c r="B53" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>596</v>
+      </c>
+      <c r="B54" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>597</v>
+      </c>
+      <c r="B55" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>598</v>
+      </c>
+      <c r="B56" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>599</v>
+      </c>
+      <c r="B57" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>600</v>
+      </c>
+      <c r="B58" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>601</v>
+      </c>
+      <c r="B59" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>602</v>
+      </c>
+      <c r="B60" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>603</v>
+      </c>
+      <c r="B61" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>604</v>
+      </c>
+      <c r="B62" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>605</v>
+      </c>
+      <c r="B63" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>606</v>
+      </c>
+      <c r="B64" t="s">
+        <v>357</v>
       </c>
     </row>
   </sheetData>
@@ -5598,27 +5714,463 @@
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>609</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>613</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>614</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>616</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>497</v>
+        <v>357</v>
+      </c>
+      <c r="B5" t="s">
+        <v>620</v>
+      </c>
+      <c r="C5" t="s">
+        <v>621</v>
+      </c>
+      <c r="D5" t="s">
+        <v>321</v>
+      </c>
+      <c r="E5" t="s">
+        <v>622</v>
+      </c>
+      <c r="F5" t="s">
+        <v>623</v>
+      </c>
+      <c r="G5" t="s">
+        <v>622</v>
+      </c>
+      <c r="H5" t="s">
+        <v>624</v>
+      </c>
+      <c r="I5" t="s">
+        <v>625</v>
+      </c>
+      <c r="J5" t="s">
+        <v>626</v>
+      </c>
+      <c r="K5" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B6" t="s">
+        <v>628</v>
+      </c>
+      <c r="C6" t="s">
+        <v>629</v>
+      </c>
+      <c r="D6" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" t="s">
+        <v>622</v>
+      </c>
+      <c r="F6" t="s">
+        <v>623</v>
+      </c>
+      <c r="G6" t="s">
+        <v>622</v>
+      </c>
+      <c r="H6" t="s">
+        <v>624</v>
+      </c>
+      <c r="I6" t="s">
+        <v>630</v>
+      </c>
+      <c r="J6" t="s">
+        <v>626</v>
+      </c>
+      <c r="K6" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>364</v>
+      </c>
+      <c r="B7" t="s">
+        <v>631</v>
+      </c>
+      <c r="C7" t="s">
+        <v>632</v>
+      </c>
+      <c r="D7" t="s">
+        <v>321</v>
+      </c>
+      <c r="E7" t="s">
+        <v>622</v>
+      </c>
+      <c r="F7" t="s">
+        <v>279</v>
+      </c>
+      <c r="G7" t="s">
+        <v>622</v>
+      </c>
+      <c r="H7" t="s">
+        <v>624</v>
+      </c>
+      <c r="I7" t="s">
+        <v>633</v>
+      </c>
+      <c r="J7" t="s">
+        <v>626</v>
+      </c>
+      <c r="K7" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>488</v>
+      </c>
+      <c r="B8" t="s">
+        <v>634</v>
+      </c>
+      <c r="C8" t="s">
+        <v>635</v>
+      </c>
+      <c r="D8" t="s">
+        <v>321</v>
+      </c>
+      <c r="E8" t="s">
+        <v>622</v>
+      </c>
+      <c r="F8" t="s">
+        <v>279</v>
+      </c>
+      <c r="G8" t="s">
+        <v>622</v>
+      </c>
+      <c r="H8" t="s">
+        <v>624</v>
+      </c>
+      <c r="I8" t="s">
+        <v>636</v>
+      </c>
+      <c r="J8" t="s">
+        <v>626</v>
+      </c>
+      <c r="K8" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>366</v>
+      </c>
+      <c r="B9" t="s">
+        <v>637</v>
+      </c>
+      <c r="C9" t="s">
+        <v>638</v>
+      </c>
+      <c r="D9" t="s">
+        <v>321</v>
+      </c>
+      <c r="E9" t="s">
+        <v>622</v>
+      </c>
+      <c r="F9" t="s">
+        <v>279</v>
+      </c>
+      <c r="G9" t="s">
+        <v>622</v>
+      </c>
+      <c r="H9" t="s">
+        <v>624</v>
+      </c>
+      <c r="I9" t="s">
+        <v>639</v>
+      </c>
+      <c r="J9" t="s">
+        <v>626</v>
+      </c>
+      <c r="K9" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>279</v>
+      </c>
+      <c r="B10" t="s">
+        <v>640</v>
+      </c>
+      <c r="C10" t="s">
+        <v>641</v>
+      </c>
+      <c r="D10" t="s">
+        <v>321</v>
+      </c>
+      <c r="E10" t="s">
+        <v>622</v>
+      </c>
+      <c r="F10" t="s">
+        <v>279</v>
+      </c>
+      <c r="G10" t="s">
+        <v>622</v>
+      </c>
+      <c r="H10" t="s">
+        <v>624</v>
+      </c>
+      <c r="I10" t="s">
+        <v>642</v>
+      </c>
+      <c r="J10" t="s">
+        <v>626</v>
+      </c>
+      <c r="K10" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>487</v>
+      </c>
+      <c r="B11" t="s">
+        <v>643</v>
+      </c>
+      <c r="C11" t="s">
+        <v>644</v>
+      </c>
+      <c r="D11" t="s">
+        <v>321</v>
+      </c>
+      <c r="E11" t="s">
+        <v>622</v>
+      </c>
+      <c r="F11" t="s">
+        <v>279</v>
+      </c>
+      <c r="G11" t="s">
+        <v>622</v>
+      </c>
+      <c r="H11" t="s">
+        <v>624</v>
+      </c>
+      <c r="I11" t="s">
+        <v>645</v>
+      </c>
+      <c r="J11" t="s">
+        <v>626</v>
+      </c>
+      <c r="K11" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>376</v>
+      </c>
+      <c r="B12" t="s">
+        <v>622</v>
+      </c>
+      <c r="C12" t="s">
+        <v>646</v>
+      </c>
+      <c r="D12" t="s">
+        <v>321</v>
+      </c>
+      <c r="E12" t="s">
+        <v>622</v>
+      </c>
+      <c r="F12" t="s">
+        <v>319</v>
+      </c>
+      <c r="G12" t="s">
+        <v>622</v>
+      </c>
+      <c r="H12" t="s">
+        <v>624</v>
+      </c>
+      <c r="J12" t="s">
+        <v>626</v>
+      </c>
+      <c r="K12" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>564</v>
+      </c>
+      <c r="B13" t="s">
+        <v>647</v>
+      </c>
+      <c r="C13" t="s">
+        <v>648</v>
+      </c>
+      <c r="D13" t="s">
+        <v>321</v>
+      </c>
+      <c r="E13" t="s">
+        <v>622</v>
+      </c>
+      <c r="F13" t="s">
+        <v>649</v>
+      </c>
+      <c r="G13" t="s">
+        <v>622</v>
+      </c>
+      <c r="H13" t="s">
+        <v>624</v>
+      </c>
+      <c r="I13" t="s">
+        <v>650</v>
+      </c>
+      <c r="J13" t="s">
+        <v>626</v>
+      </c>
+      <c r="K13" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>374</v>
+      </c>
+      <c r="B14" t="s">
+        <v>651</v>
+      </c>
+      <c r="C14" t="s">
+        <v>652</v>
+      </c>
+      <c r="D14" t="s">
+        <v>321</v>
+      </c>
+      <c r="E14" t="s">
+        <v>622</v>
+      </c>
+      <c r="F14" t="s">
+        <v>626</v>
+      </c>
+      <c r="G14" t="s">
+        <v>626</v>
+      </c>
+      <c r="H14" t="s">
+        <v>624</v>
+      </c>
+      <c r="J14" t="s">
+        <v>626</v>
+      </c>
+      <c r="K14" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>561</v>
+      </c>
+      <c r="B15" t="s">
+        <v>653</v>
+      </c>
+      <c r="C15" t="s">
+        <v>654</v>
+      </c>
+      <c r="D15" t="s">
+        <v>626</v>
+      </c>
+      <c r="E15" t="s">
+        <v>626</v>
+      </c>
+      <c r="F15" t="s">
+        <v>626</v>
+      </c>
+      <c r="G15" t="s">
+        <v>626</v>
+      </c>
+      <c r="H15" t="s">
+        <v>624</v>
+      </c>
+      <c r="J15" t="s">
+        <v>626</v>
+      </c>
+      <c r="K15" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>307</v>
+      </c>
+      <c r="B16" t="s">
+        <v>655</v>
+      </c>
+      <c r="C16" t="s">
+        <v>656</v>
+      </c>
+      <c r="D16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E16" t="s">
+        <v>622</v>
+      </c>
+      <c r="F16" t="s">
+        <v>319</v>
+      </c>
+      <c r="G16" t="s">
+        <v>622</v>
+      </c>
+      <c r="H16" t="s">
+        <v>624</v>
+      </c>
+      <c r="I16" t="s">
+        <v>657</v>
+      </c>
+      <c r="J16" t="s">
+        <v>626</v>
+      </c>
+      <c r="K16" t="s">
+        <v>627</v>
       </c>
     </row>
   </sheetData>
@@ -5633,22 +6185,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>498</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>495</v>
+        <v>659</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>496</v>
+        <v>660</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>497</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -5683,571 +6235,27 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>507</v>
-      </c>
-      <c r="B5" t="s">
-        <v>508</v>
-      </c>
-      <c r="C5" t="s">
-        <v>289</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>396</v>
-      </c>
-      <c r="F5" t="s">
-        <v>509</v>
-      </c>
-      <c r="G5" t="s">
-        <v>341</v>
-      </c>
-      <c r="I5" t="s">
-        <v>510</v>
-      </c>
-      <c r="J5" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>512</v>
-      </c>
-      <c r="B6" t="s">
-        <v>513</v>
-      </c>
-      <c r="C6" t="s">
-        <v>146</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" t="s">
-        <v>514</v>
-      </c>
-      <c r="G6" t="s">
-        <v>257</v>
-      </c>
-      <c r="I6" t="s">
-        <v>515</v>
-      </c>
-      <c r="J6" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>517</v>
-      </c>
-      <c r="B7" t="s">
-        <v>518</v>
-      </c>
-      <c r="C7" t="s">
-        <v>337</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>235</v>
-      </c>
-      <c r="F7" t="s">
-        <v>519</v>
-      </c>
-      <c r="G7" t="s">
-        <v>146</v>
-      </c>
-      <c r="I7" t="s">
-        <v>520</v>
-      </c>
-      <c r="J7" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>522</v>
-      </c>
-      <c r="B8" t="s">
-        <v>523</v>
-      </c>
-      <c r="C8" t="s">
-        <v>524</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" t="s">
-        <v>525</v>
-      </c>
-      <c r="G8" t="s">
-        <v>146</v>
-      </c>
-      <c r="I8" t="s">
-        <v>526</v>
-      </c>
-      <c r="J8" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>528</v>
-      </c>
-      <c r="B9" t="s">
-        <v>529</v>
-      </c>
-      <c r="C9" t="s">
-        <v>524</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>237</v>
-      </c>
-      <c r="F9" t="s">
-        <v>530</v>
-      </c>
-      <c r="G9" t="s">
-        <v>261</v>
-      </c>
-      <c r="I9" t="s">
-        <v>526</v>
-      </c>
-      <c r="J9" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>532</v>
-      </c>
-      <c r="B10" t="s">
-        <v>533</v>
-      </c>
-      <c r="C10" t="s">
-        <v>524</v>
-      </c>
-      <c r="D10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" t="s">
-        <v>514</v>
-      </c>
-      <c r="G10" t="s">
-        <v>261</v>
-      </c>
-      <c r="I10" t="s">
-        <v>526</v>
-      </c>
-      <c r="J10" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>535</v>
-      </c>
-      <c r="B11" t="s">
-        <v>536</v>
-      </c>
-      <c r="C11" t="s">
-        <v>537</v>
-      </c>
-      <c r="D11" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" t="s">
-        <v>237</v>
-      </c>
-      <c r="F11" t="s">
-        <v>514</v>
-      </c>
-      <c r="G11" t="s">
-        <v>257</v>
-      </c>
-      <c r="I11" t="s">
-        <v>538</v>
-      </c>
-      <c r="J11" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>540</v>
-      </c>
-      <c r="B12" t="s">
-        <v>541</v>
-      </c>
-      <c r="C12" t="s">
-        <v>537</v>
-      </c>
-      <c r="D12" t="s">
-        <v>228</v>
-      </c>
-      <c r="E12" t="s">
-        <v>228</v>
-      </c>
-      <c r="F12" t="s">
-        <v>542</v>
-      </c>
-      <c r="G12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" t="s">
-        <v>538</v>
-      </c>
-      <c r="J12" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>544</v>
-      </c>
-      <c r="B13" t="s">
-        <v>545</v>
-      </c>
-      <c r="C13" t="s">
-        <v>341</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>158</v>
-      </c>
-      <c r="F13" t="s">
-        <v>525</v>
-      </c>
-      <c r="G13" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" t="s">
-        <v>546</v>
-      </c>
-      <c r="J13" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>548</v>
-      </c>
-      <c r="B14" t="s">
-        <v>549</v>
-      </c>
-      <c r="C14" t="s">
-        <v>343</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" t="s">
-        <v>519</v>
-      </c>
-      <c r="G14" t="s">
-        <v>125</v>
-      </c>
-      <c r="I14" t="s">
-        <v>550</v>
-      </c>
-      <c r="J14" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>552</v>
-      </c>
-      <c r="B15" t="s">
-        <v>553</v>
-      </c>
-      <c r="C15" t="s">
-        <v>554</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>235</v>
-      </c>
-      <c r="F15" t="s">
-        <v>519</v>
-      </c>
-      <c r="G15" t="s">
-        <v>146</v>
-      </c>
-      <c r="I15" t="s">
-        <v>555</v>
-      </c>
-      <c r="J15" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>557</v>
-      </c>
-      <c r="B16" t="s">
-        <v>558</v>
-      </c>
-      <c r="C16" t="s">
-        <v>554</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>158</v>
-      </c>
-      <c r="F16" t="s">
-        <v>559</v>
-      </c>
-      <c r="G16" t="s">
-        <v>287</v>
-      </c>
-      <c r="I16" t="s">
-        <v>555</v>
-      </c>
-      <c r="J16" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>561</v>
-      </c>
-      <c r="B17" t="s">
-        <v>562</v>
-      </c>
-      <c r="C17" t="s">
-        <v>554</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>235</v>
-      </c>
-      <c r="F17" t="s">
-        <v>563</v>
-      </c>
-      <c r="G17" t="s">
-        <v>125</v>
-      </c>
-      <c r="I17" t="s">
-        <v>555</v>
-      </c>
-      <c r="J17" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>565</v>
-      </c>
-      <c r="B18" t="s">
-        <v>566</v>
-      </c>
-      <c r="C18" t="s">
-        <v>285</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>158</v>
-      </c>
-      <c r="F18" t="s">
-        <v>525</v>
-      </c>
-      <c r="G18" t="s">
-        <v>287</v>
-      </c>
-      <c r="I18" t="s">
-        <v>567</v>
-      </c>
-      <c r="J18" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>569</v>
-      </c>
-      <c r="B19" t="s">
-        <v>570</v>
-      </c>
-      <c r="C19" t="s">
-        <v>571</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>396</v>
-      </c>
-      <c r="F19" t="s">
-        <v>509</v>
-      </c>
-      <c r="G19" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" t="s">
-        <v>572</v>
-      </c>
-      <c r="J19" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>574</v>
-      </c>
-      <c r="B20" t="s">
-        <v>575</v>
-      </c>
-      <c r="C20" t="s">
-        <v>576</v>
-      </c>
-      <c r="D20" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" t="s">
-        <v>237</v>
-      </c>
-      <c r="F20" t="s">
-        <v>514</v>
-      </c>
-      <c r="G20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I20" t="s">
-        <v>577</v>
-      </c>
-      <c r="J20" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>574</v>
-      </c>
-      <c r="B21" t="s">
-        <v>575</v>
-      </c>
-      <c r="C21" t="s">
-        <v>576</v>
-      </c>
-      <c r="D21" t="s">
-        <v>235</v>
-      </c>
-      <c r="E21" t="s">
-        <v>237</v>
-      </c>
-      <c r="F21" t="s">
-        <v>514</v>
-      </c>
-      <c r="G21" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" t="s">
-        <v>577</v>
-      </c>
-      <c r="J21" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>579</v>
-      </c>
-      <c r="B22" t="s">
-        <v>580</v>
-      </c>
-      <c r="C22" t="s">
-        <v>216</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>158</v>
-      </c>
-      <c r="F22" t="s">
-        <v>525</v>
-      </c>
-      <c r="G22" t="s">
-        <v>125</v>
-      </c>
-      <c r="I22" t="s">
-        <v>581</v>
-      </c>
-      <c r="J22" t="s">
-        <v>582</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -6257,629 +6265,49 @@
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>583</v>
+        <v>663</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>354</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>438</v>
+        <v>611</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>437</v>
+        <v>610</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>501</v>
+        <v>664</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>502</v>
+        <v>665</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>503</v>
+        <v>666</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>504</v>
+        <v>667</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>446</v>
+        <v>619</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>505</v>
+        <v>668</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>584</v>
-      </c>
-      <c r="B5" t="s">
-        <v>585</v>
-      </c>
-      <c r="C5" t="s">
-        <v>287</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>237</v>
-      </c>
-      <c r="F5" t="s">
-        <v>514</v>
-      </c>
-      <c r="G5" t="s">
-        <v>125</v>
-      </c>
-      <c r="I5" t="s">
-        <v>586</v>
-      </c>
-      <c r="J5" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>584</v>
-      </c>
-      <c r="B6" t="s">
-        <v>585</v>
-      </c>
-      <c r="C6" t="s">
-        <v>287</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>235</v>
-      </c>
-      <c r="F6" t="s">
-        <v>563</v>
-      </c>
-      <c r="G6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I6" t="s">
-        <v>586</v>
-      </c>
-      <c r="J6" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>584</v>
-      </c>
-      <c r="B7" t="s">
-        <v>585</v>
-      </c>
-      <c r="C7" t="s">
-        <v>287</v>
-      </c>
-      <c r="D7" t="s">
-        <v>228</v>
-      </c>
-      <c r="E7" t="s">
-        <v>237</v>
-      </c>
-      <c r="F7" t="s">
-        <v>514</v>
-      </c>
-      <c r="G7" t="s">
-        <v>125</v>
-      </c>
-      <c r="I7" t="s">
-        <v>586</v>
-      </c>
-      <c r="J7" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>584</v>
-      </c>
-      <c r="B8" t="s">
-        <v>585</v>
-      </c>
-      <c r="C8" t="s">
-        <v>287</v>
-      </c>
-      <c r="D8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E8" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" t="s">
-        <v>563</v>
-      </c>
-      <c r="G8" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" t="s">
-        <v>586</v>
-      </c>
-      <c r="J8" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>588</v>
-      </c>
-      <c r="B9" t="s">
-        <v>589</v>
-      </c>
-      <c r="C9" t="s">
-        <v>590</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>247</v>
-      </c>
-      <c r="F9" t="s">
-        <v>591</v>
-      </c>
-      <c r="G9" t="s">
-        <v>125</v>
-      </c>
-      <c r="I9" t="s">
-        <v>592</v>
-      </c>
-      <c r="J9" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>594</v>
-      </c>
-      <c r="B10" t="s">
-        <v>595</v>
-      </c>
-      <c r="C10" t="s">
-        <v>590</v>
-      </c>
-      <c r="D10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E10" t="s">
-        <v>247</v>
-      </c>
-      <c r="F10" t="s">
-        <v>591</v>
-      </c>
-      <c r="G10" t="s">
-        <v>125</v>
-      </c>
-      <c r="I10" t="s">
-        <v>592</v>
-      </c>
-      <c r="J10" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>597</v>
-      </c>
-      <c r="B11" t="s">
-        <v>598</v>
-      </c>
-      <c r="C11" t="s">
-        <v>590</v>
-      </c>
-      <c r="D11" t="s">
-        <v>158</v>
-      </c>
-      <c r="E11" t="s">
-        <v>247</v>
-      </c>
-      <c r="F11" t="s">
-        <v>591</v>
-      </c>
-      <c r="G11" t="s">
-        <v>125</v>
-      </c>
-      <c r="I11" t="s">
-        <v>592</v>
-      </c>
-      <c r="J11" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>535</v>
-      </c>
-      <c r="B12" t="s">
-        <v>536</v>
-      </c>
-      <c r="C12" t="s">
-        <v>537</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>247</v>
-      </c>
-      <c r="F12" t="s">
-        <v>591</v>
-      </c>
-      <c r="G12" t="s">
-        <v>125</v>
-      </c>
-      <c r="I12" t="s">
-        <v>538</v>
-      </c>
-      <c r="J12" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>600</v>
-      </c>
-      <c r="B13" t="s">
-        <v>601</v>
-      </c>
-      <c r="C13" t="s">
-        <v>537</v>
-      </c>
-      <c r="D13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E13" t="s">
-        <v>396</v>
-      </c>
-      <c r="F13" t="s">
-        <v>509</v>
-      </c>
-      <c r="G13" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" t="s">
-        <v>538</v>
-      </c>
-      <c r="J13" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>603</v>
-      </c>
-      <c r="B14" t="s">
-        <v>604</v>
-      </c>
-      <c r="C14" t="s">
-        <v>339</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>235</v>
-      </c>
-      <c r="F14" t="s">
-        <v>519</v>
-      </c>
-      <c r="G14" t="s">
-        <v>125</v>
-      </c>
-      <c r="I14" t="s">
-        <v>605</v>
-      </c>
-      <c r="J14" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" t="s">
-        <v>607</v>
-      </c>
-      <c r="B15" t="s">
-        <v>608</v>
-      </c>
-      <c r="C15" t="s">
-        <v>285</v>
-      </c>
-      <c r="D15" t="s">
-        <v>228</v>
-      </c>
-      <c r="E15" t="s">
-        <v>247</v>
-      </c>
-      <c r="F15" t="s">
-        <v>591</v>
-      </c>
-      <c r="G15" t="s">
-        <v>125</v>
-      </c>
-      <c r="I15" t="s">
-        <v>567</v>
-      </c>
-      <c r="J15" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" t="s">
-        <v>610</v>
-      </c>
-      <c r="B16" t="s">
-        <v>611</v>
-      </c>
-      <c r="C16" t="s">
-        <v>285</v>
-      </c>
-      <c r="D16" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" t="s">
-        <v>470</v>
-      </c>
-      <c r="F16" t="s">
-        <v>612</v>
-      </c>
-      <c r="G16" t="s">
-        <v>125</v>
-      </c>
-      <c r="I16" t="s">
-        <v>567</v>
-      </c>
-      <c r="J16" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" t="s">
-        <v>610</v>
-      </c>
-      <c r="B17" t="s">
-        <v>611</v>
-      </c>
-      <c r="C17" t="s">
-        <v>285</v>
-      </c>
-      <c r="D17" t="s">
-        <v>235</v>
-      </c>
-      <c r="E17" t="s">
-        <v>470</v>
-      </c>
-      <c r="F17" t="s">
-        <v>612</v>
-      </c>
-      <c r="G17" t="s">
-        <v>125</v>
-      </c>
-      <c r="I17" t="s">
-        <v>567</v>
-      </c>
-      <c r="J17" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" t="s">
-        <v>614</v>
-      </c>
-      <c r="B18" t="s">
-        <v>615</v>
-      </c>
-      <c r="C18" t="s">
-        <v>285</v>
-      </c>
-      <c r="D18" t="s">
-        <v>396</v>
-      </c>
-      <c r="E18" t="s">
-        <v>470</v>
-      </c>
-      <c r="F18" t="s">
-        <v>612</v>
-      </c>
-      <c r="G18" t="s">
-        <v>125</v>
-      </c>
-      <c r="I18" t="s">
-        <v>567</v>
-      </c>
-      <c r="J18" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" t="s">
-        <v>614</v>
-      </c>
-      <c r="B19" t="s">
-        <v>615</v>
-      </c>
-      <c r="C19" t="s">
-        <v>285</v>
-      </c>
-      <c r="D19" t="s">
-        <v>237</v>
-      </c>
-      <c r="E19" t="s">
-        <v>470</v>
-      </c>
-      <c r="F19" t="s">
-        <v>612</v>
-      </c>
-      <c r="G19" t="s">
-        <v>125</v>
-      </c>
-      <c r="I19" t="s">
-        <v>567</v>
-      </c>
-      <c r="J19" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" t="s">
-        <v>574</v>
-      </c>
-      <c r="B20" t="s">
-        <v>575</v>
-      </c>
-      <c r="C20" t="s">
-        <v>576</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>150</v>
-      </c>
-      <c r="F20" t="s">
-        <v>617</v>
-      </c>
-      <c r="G20" t="s">
-        <v>125</v>
-      </c>
-      <c r="I20" t="s">
-        <v>577</v>
-      </c>
-      <c r="J20" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" t="s">
-        <v>574</v>
-      </c>
-      <c r="B21" t="s">
-        <v>575</v>
-      </c>
-      <c r="C21" t="s">
-        <v>576</v>
-      </c>
-      <c r="D21" t="s">
-        <v>228</v>
-      </c>
-      <c r="E21" t="s">
-        <v>470</v>
-      </c>
-      <c r="F21" t="s">
-        <v>612</v>
-      </c>
-      <c r="G21" t="s">
-        <v>125</v>
-      </c>
-      <c r="I21" t="s">
-        <v>577</v>
-      </c>
-      <c r="J21" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" t="s">
-        <v>618</v>
-      </c>
-      <c r="B22" t="s">
-        <v>619</v>
-      </c>
-      <c r="C22" t="s">
-        <v>576</v>
-      </c>
-      <c r="D22" t="s">
-        <v>396</v>
-      </c>
-      <c r="E22" t="s">
-        <v>247</v>
-      </c>
-      <c r="F22" t="s">
-        <v>591</v>
-      </c>
-      <c r="G22" t="s">
-        <v>125</v>
-      </c>
-      <c r="I22" t="s">
-        <v>577</v>
-      </c>
-      <c r="J22" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" t="s">
-        <v>618</v>
-      </c>
-      <c r="B23" t="s">
-        <v>619</v>
-      </c>
-      <c r="C23" t="s">
-        <v>576</v>
-      </c>
-      <c r="D23" t="s">
-        <v>237</v>
-      </c>
-      <c r="E23" t="s">
-        <v>247</v>
-      </c>
-      <c r="F23" t="s">
-        <v>591</v>
-      </c>
-      <c r="G23" t="s">
-        <v>125</v>
-      </c>
-      <c r="I23" t="s">
-        <v>577</v>
-      </c>
-      <c r="J23" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" t="s">
-        <v>618</v>
-      </c>
-      <c r="B24" t="s">
-        <v>619</v>
-      </c>
-      <c r="C24" t="s">
-        <v>576</v>
-      </c>
-      <c r="D24" t="s">
-        <v>150</v>
-      </c>
-      <c r="E24" t="s">
-        <v>247</v>
-      </c>
-      <c r="F24" t="s">
-        <v>591</v>
-      </c>
-      <c r="G24" t="s">
-        <v>125</v>
-      </c>
-      <c r="I24" t="s">
-        <v>577</v>
-      </c>
-      <c r="J24" t="s">
-        <v>620</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -6889,27 +6317,49 @@
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>624</v>
+        <v>611</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -6919,27 +6369,122 @@
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>625</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>623</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>624</v>
+        <v>672</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>679</v>
       </c>
     </row>
   </sheetData>
@@ -6949,32 +6494,17 @@
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>626</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>627</v>
+        <v>680</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>164</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -6984,92 +6514,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>624</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>628</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>629</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>630</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>628</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>228</v>
+        <v>682</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>697</v>
       </c>
     </row>
   </sheetData>
@@ -7107,136 +6632,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>228</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>647</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>649</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>651</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A5"/>
@@ -7264,7 +6659,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -7280,6 +6675,326 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -7289,22 +7004,52 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -7314,17 +7059,52 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -7334,17 +7114,342 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A79"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="704">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -232,6 +232,18 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.VSENSE(105)</t>
+  </si>
+  <si>
+    <t>Floating pin XU3.IREPLICA(100)</t>
+  </si>
+  <si>
+    <t>Floating pin XNC66.noconn(66)</t>
+  </si>
+  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -289,22 +301,22 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
+    <t>Floating pin XSERDESdftNoNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otpdone(otp_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_pgenb(otp_pgenb)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.otp_clock_enable(otp_clock_enable)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
@@ -325,22 +337,22 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftNoNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
@@ -349,22 +361,22 @@
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
@@ -445,6 +457,15 @@
     <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
   </si>
   <si>
+    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -505,22 +526,22 @@
     <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_pgenb - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_pgenb", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -569,6 +590,9 @@
   </si>
   <si>
     <t>All Nestos have Verilog File</t>
+  </si>
+  <si>
+    <t>NESTO fetdn_359003a8 not found in verilog...</t>
   </si>
   <si>
     <t>Zero Length Verilog Files</t>
@@ -689,9 +713,6 @@
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
   </si>
   <si>
@@ -866,7 +887,7 @@
     <t>serdes_memory_program</t>
   </si>
   <si>
-    <t>Auto</t>
+    <t>Single</t>
   </si>
   <si>
     <t>serdes_memory_bist</t>
@@ -902,9 +923,6 @@
     <t>serdes_supply</t>
   </si>
   <si>
-    <t>Single</t>
-  </si>
-  <si>
     <t>serdes_split_vi2c_pad</t>
   </si>
   <si>
@@ -2132,13 +2150,13 @@
     <t>pad_WALTZ_IN.PIN 60V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.DRAIN 60V -0.3V</t>
   </si>
   <si>
-    <t>pad_WALTZ_PGND.PGND 0.3V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU5.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU14.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU16.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,Xfetdriver1.HVNEG 6V 0.0V</t>
+    <t>pad_WALTZ_PGND.PGND 0.3V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU5.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU16.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,Xfetdriver1.HVNEG 6V 0.0V</t>
   </si>
   <si>
     <t>pad_WALTZ_POK.POK 6V -0.3V connects to XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN,XU4.PAD 6V -0.3V</t>
   </si>
   <si>
-    <t>pad_WALTZ_SW.SW 60V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU5.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU14.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU16.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU2.CELNEG 60V 2.2V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.SOURCEk 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU17.CELNEG 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,Xfetdriver.HVNEG 60V 54.0V</t>
+    <t>pad_WALTZ_SW.SW 60V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU5.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU16.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU2.CELNEG 60V 2.2V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.SOURCEk 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU17.CELNEG 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,Xfetdriver.HVNEG 60V 54.0V</t>
   </si>
   <si>
     <t>pad_WALTZ_SYNC.SYNC 6V -0.3V connects to XWALTZ,XceleraCORE,XCLOCK,XMAIN,XU24.IN 6V -0.3V</t>
@@ -2515,7 +2533,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2535,7 +2553,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2550,7 +2568,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2565,17 +2583,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2590,12 +2608,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2610,17 +2628,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -2630,17 +2648,22 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>170</v>
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2655,7 +2678,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2675,127 +2698,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2810,7 +2833,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2830,17 +2853,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3065,32 +3088,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -3100,37 +3123,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>212</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3140,62 +3163,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -3205,17 +3228,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -3225,57 +3248,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -3290,17 +3313,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -3315,52 +3338,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -3375,81 +3398,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B6" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B7" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B10" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="B11" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3457,1268 +3480,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="B20" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B21" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B27" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B35" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B36" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B38" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B40" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B41" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B42" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B43" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B46" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B47" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B48" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B49" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B50" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B51" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B52" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B55" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B56" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B57" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B64" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="B67" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B68" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B69" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B70" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B77" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B78" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B79" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B80" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B81" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B82" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B83" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B84" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B85" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B86" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B87" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B88" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B89" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B90" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B91" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B92" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B93" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B94" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B95" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B96" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B97" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B98" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B100" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B101" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B102" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B103" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B106" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B107" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B108" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B109" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B110" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B111" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B112" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B113" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B116" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B117" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B118" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B119" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B120" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B121" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B122" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B123" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B124" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B125" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="B126" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B127" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B128" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B129" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="B130" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B131" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B132" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B133" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B134" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B135" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B136" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B137" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B138" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="B139" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="B140" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="B141" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B142" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B143" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B144" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="B145" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B146" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B147" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B148" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B149" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B150" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="B151" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B152" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B153" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B154" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B155" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B156" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B157" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="B158" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="B159" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B160" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B161" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="B162" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B163" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B164" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="B165" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="B166" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="B167" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B168" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="B169" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B170" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B171" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B172" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B173" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B174" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="B175" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B176" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="B177" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B178" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="B179" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="B180" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -4733,47 +4756,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4781,15 +4804,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4797,7 +4820,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
@@ -4812,7 +4835,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -4827,68 +4850,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B5" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C5" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D5" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B6" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C6" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D6" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B7" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C7" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="D7" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4896,13 +4919,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C8" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D8" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4910,55 +4933,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C9" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D9" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>212</v>
+        <v>61</v>
       </c>
       <c r="B10" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C10" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D10" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B11" t="s">
+        <v>513</v>
+      </c>
+      <c r="C11" t="s">
+        <v>514</v>
+      </c>
+      <c r="D11" t="s">
         <v>507</v>
-      </c>
-      <c r="C11" t="s">
-        <v>508</v>
-      </c>
-      <c r="D11" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B12" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C12" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D12" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4966,111 +4989,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C13" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D13" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B14" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C14" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D14" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B15" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C15" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D15" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B16" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C16" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D16" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B17" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C17" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D17" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B18" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C18" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="D18" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="B19" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C19" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D19" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C20" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D20" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5078,27 +5101,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C21" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D21" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="C22" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D22" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5106,13 +5129,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C23" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D23" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5120,83 +5143,83 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C24" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D24" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B25" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C25" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D25" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B26" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C26" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D26" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="B27" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="C27" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D27" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="B28" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="C28" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D28" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="B29" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C29" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="D29" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -5211,7 +5234,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5221,490 +5244,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="B5" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="B6" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="B7" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="B8" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B9" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B10" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B11" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B12" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B13" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B14" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B15" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="B16" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="B17" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B18" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B19" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="B20" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="B21" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B22" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B23" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="B24" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B25" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="B26" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B27" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="B28" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="B29" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B30" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="B31" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="B32" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="B33" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="B34" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="B35" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B36" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="B37" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="B39" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="B40" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="B41" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="B42" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="B43" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B44" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B45" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B46" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="B47" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="B48" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="B49" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="B50" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="B51" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="B52" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B53" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="B54" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B55" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B56" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="B57" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B58" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="B59" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="B60" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="B61" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B62" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B63" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="B64" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
@@ -5719,458 +5742,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B5" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="C5" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D5" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F5" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="G5" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H5" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I5" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="J5" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K5" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B6" t="s">
+        <v>634</v>
+      </c>
+      <c r="C6" t="s">
+        <v>635</v>
+      </c>
+      <c r="D6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E6" t="s">
         <v>628</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>629</v>
       </c>
-      <c r="D6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E6" t="s">
-        <v>622</v>
-      </c>
-      <c r="F6" t="s">
-        <v>623</v>
-      </c>
       <c r="G6" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H6" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I6" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="J6" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K6" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B7" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="C7" t="s">
+        <v>638</v>
+      </c>
+      <c r="D7" t="s">
+        <v>327</v>
+      </c>
+      <c r="E7" t="s">
+        <v>628</v>
+      </c>
+      <c r="F7" t="s">
+        <v>286</v>
+      </c>
+      <c r="G7" t="s">
+        <v>628</v>
+      </c>
+      <c r="H7" t="s">
+        <v>630</v>
+      </c>
+      <c r="I7" t="s">
+        <v>639</v>
+      </c>
+      <c r="J7" t="s">
         <v>632</v>
       </c>
-      <c r="D7" t="s">
-        <v>321</v>
-      </c>
-      <c r="E7" t="s">
-        <v>622</v>
-      </c>
-      <c r="F7" t="s">
-        <v>279</v>
-      </c>
-      <c r="G7" t="s">
-        <v>622</v>
-      </c>
-      <c r="H7" t="s">
-        <v>624</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>633</v>
-      </c>
-      <c r="J7" t="s">
-        <v>626</v>
-      </c>
-      <c r="K7" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="B8" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C8" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D8" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E8" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F8" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="G8" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H8" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I8" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="J8" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K8" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B9" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C9" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="D9" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E9" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F9" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="G9" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H9" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I9" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="J9" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K9" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="B10" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C10" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D10" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E10" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F10" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="G10" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H10" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I10" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="J10" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K10" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B11" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="C11" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="D11" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E11" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F11" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="G11" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H11" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I11" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="J11" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K11" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B12" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="C12" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="D12" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E12" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F12" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="G12" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H12" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="J12" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K12" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="B13" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="C13" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="D13" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E13" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F13" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="G13" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H13" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I13" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="J13" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K13" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B14" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C14" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D14" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E14" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F14" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="G14" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="H14" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="J14" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K14" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B15" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="C15" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="D15" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="E15" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="F15" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="G15" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="H15" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="J15" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K15" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B16" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C16" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="D16" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="E16" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="F16" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="G16" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="H16" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="I16" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="J16" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="K16" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
     </row>
   </sheetData>
@@ -6185,22 +6208,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -6240,22 +6263,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -6270,44 +6293,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -6322,44 +6345,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
@@ -6374,92 +6397,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6469,22 +6492,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -6499,7 +6522,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6514,87 +6537,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
     </row>
   </sheetData>
@@ -6659,7 +6682,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A80"/>
+  <dimension ref="A1:A85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6819,132 +6842,132 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
+      <c r="A41" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
+      <c r="A53" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
+      <c r="A63" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
+      <c r="A68" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -6958,43 +6981,63 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" t="s">
+      <c r="A73" s="1" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
         <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -7009,47 +7052,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -7064,47 +7107,47 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -7114,12 +7157,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A79"/>
+  <dimension ref="A1:A84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7129,22 +7172,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -7154,27 +7197,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -7184,17 +7227,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -7204,252 +7247,272 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
+      <c r="A38" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="1" t="s">
         <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
-      <c r="A47" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>140</v>
+      <c r="A50" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
+      <c r="A55" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
+      <c r="A60" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>150</v>
+      <c r="A65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>154</v>
+      <c r="A70" s="1" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>162</v>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="687">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -232,18 +232,6 @@
     <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.VSENSE(105)</t>
-  </si>
-  <si>
-    <t>Floating pin XU3.IREPLICA(100)</t>
-  </si>
-  <si>
-    <t>Floating pin XNC66.noconn(66)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -325,15 +313,6 @@
     <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
   </si>
   <si>
-    <t>Floating pin XSERDEScontrolDFT.scl_serdes(scl_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.sda_serdes(sda_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.enable_hardware(enable_hardware)</t>
-  </si>
-  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -355,9 +334,6 @@
     <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
-    <t>Floating pin XSERDEScontrolDFT.sdao(sdao)</t>
-  </si>
-  <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
@@ -379,9 +355,6 @@
     <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
-    <t>sdao - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sdao", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>No Connects - Inputs</t>
   </si>
   <si>
@@ -457,15 +430,6 @@
     <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
   </si>
   <si>
-    <t>105 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "VSENSE", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>100 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU3", "instance": "XU3", "symbol": "IREPLICA", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XNC66", "instance": "XNC66", "symbol": "noconn", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -520,12 +484,6 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>DFTSCL - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSCL", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
-    <t>DFTSDA - {"path": "XWALTZ,XceleraSERDES", "instance": "XceleraSERDES", "symbol": "DFTSDA", "io": "inout", "bus": "", "type": "node"}</t>
-  </si>
-  <si>
     <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -550,15 +508,6 @@
     <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
   </si>
   <si>
-    <t>scl_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "scl_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>sda_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "sda_serdes", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>enable_hardware - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "enable_hardware", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>Mixed Mode Conflicts</t>
   </si>
   <si>
@@ -590,9 +539,6 @@
   </si>
   <si>
     <t>All Nestos have Verilog File</t>
-  </si>
-  <si>
-    <t>NESTO fetdn_359003a8 not found in verilog...</t>
   </si>
   <si>
     <t>Zero Length Verilog Files</t>
@@ -713,6 +659,9 @@
     <t>{'name': 'DFTtm8d', 'bits': 8, 'noconns': 1, 'efficiency': '87.5%'}</t>
   </si>
   <si>
+    <t>XWALTZ,XceleraCORE,XDRIVER,XBOTSW</t>
+  </si>
+  <si>
     <t>XWALTZ,XceleraCORE,XDRIVER,XDEBUG</t>
   </si>
   <si>
@@ -2150,13 +2099,13 @@
     <t>pad_WALTZ_IN.PIN 60V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.DRAIN 60V -0.3V</t>
   </si>
   <si>
-    <t>pad_WALTZ_PGND.PGND 0.3V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU5.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU16.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,Xfetdriver1.HVNEG 6V 0.0V</t>
+    <t>pad_WALTZ_PGND.PGND 0.3V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU5.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU14.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU16.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,Xfetdriver1.HVNEG 6V 0.0V</t>
   </si>
   <si>
     <t>pad_WALTZ_POK.POK 6V -0.3V connects to XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN,XU4.PAD 6V -0.3V</t>
   </si>
   <si>
-    <t>pad_WALTZ_SW.SW 60V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU5.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU16.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU2.CELNEG 60V 2.2V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.SOURCEk 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU17.CELNEG 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,Xfetdriver.HVNEG 60V 54.0V</t>
+    <t>pad_WALTZ_SW.SW 60V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU5.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU14.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XBOTSW,XU16.DRAIN 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU2.CELNEG 60V 2.2V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.SOURCE 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU5.SOURCEk 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU17.CELNEG 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,Xfetdriver.HVNEG 60V 54.0V</t>
   </si>
   <si>
     <t>pad_WALTZ_SYNC.SYNC 6V -0.3V connects to XWALTZ,XceleraCORE,XCLOCK,XMAIN,XU24.IN 6V -0.3V</t>
@@ -2533,7 +2482,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2553,7 +2502,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2568,7 +2517,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -2583,17 +2532,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -2608,12 +2557,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2628,17 +2577,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2648,22 +2597,17 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -2678,7 +2622,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2698,127 +2642,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>189</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>190</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>194</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>196</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>199</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>200</v>
+        <v>182</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>204</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>
@@ -2833,7 +2777,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2853,17 +2797,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -3088,32 +3032,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>217</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -3123,37 +3067,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3163,62 +3107,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>215</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -3228,17 +3172,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -3248,57 +3192,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>200</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3313,17 +3257,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -3338,52 +3282,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3398,81 +3342,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="B5" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="B6" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="B7" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="B8" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="B9" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="B10" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="B11" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3480,1268 +3424,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="B21" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="B30" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="B31" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="B36" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B39" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B41" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B42" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="B43" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="B46" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="B47" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="B48" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="B49" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="B50" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="B51" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="B52" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="B55" t="s">
-        <v>311</v>
+        <v>294</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="B56" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>314</v>
+        <v>297</v>
       </c>
       <c r="B57" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>315</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>316</v>
+        <v>299</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="B64" t="s">
-        <v>321</v>
+        <v>304</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
       <c r="B67" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
       <c r="B68" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="B69" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>329</v>
+        <v>312</v>
       </c>
       <c r="B70" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>333</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>334</v>
+        <v>317</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>335</v>
+        <v>318</v>
       </c>
       <c r="B77" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="B78" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B79" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="B80" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B81" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="B82" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="B83" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="B84" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="B85" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B86" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="B87" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B88" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B89" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B90" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B91" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="B92" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B93" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B94" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B95" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B96" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B97" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="B98" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B99" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="B100" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B101" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="B102" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="B103" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B106" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="B107" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B108" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B109" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="B110" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="B111" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="B112" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B113" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="B116" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="B117" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="B118" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B119" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="B120" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="B121" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="B122" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="B123" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="B124" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="B125" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="B126" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="B127" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="B128" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="B129" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B130" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="B131" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B132" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B133" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="B134" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B135" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B136" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B137" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="B138" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="B139" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="B140" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="B141" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="B142" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="B143" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="B144" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="B145" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="B146" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="B147" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="B148" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="B149" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="B150" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="B151" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="B152" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="B153" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="B154" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="B155" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="B156" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="B157" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="B158" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="B159" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="B160" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="B161" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="B162" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>461</v>
+        <v>444</v>
       </c>
       <c r="B163" t="s">
-        <v>462</v>
+        <v>445</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>463</v>
+        <v>446</v>
       </c>
       <c r="B164" t="s">
-        <v>464</v>
+        <v>447</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>465</v>
+        <v>448</v>
       </c>
       <c r="B165" t="s">
-        <v>466</v>
+        <v>449</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>467</v>
+        <v>450</v>
       </c>
       <c r="B166" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>468</v>
+        <v>451</v>
       </c>
       <c r="B167" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="B168" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>470</v>
+        <v>453</v>
       </c>
       <c r="B169" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>471</v>
+        <v>454</v>
       </c>
       <c r="B170" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="B171" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>475</v>
+        <v>458</v>
       </c>
       <c r="B172" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>477</v>
+        <v>460</v>
       </c>
       <c r="B173" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="B174" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="B175" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>481</v>
+        <v>464</v>
       </c>
       <c r="B176" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="B177" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>483</v>
+        <v>466</v>
       </c>
       <c r="B178" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>484</v>
+        <v>467</v>
       </c>
       <c r="B179" t="s">
-        <v>485</v>
+        <v>468</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>486</v>
+        <v>469</v>
       </c>
       <c r="B180" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -4756,47 +4700,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>487</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4804,15 +4748,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>495</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>496</v>
+        <v>479</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>497</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4820,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -4835,7 +4779,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>499</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -4850,68 +4794,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>489</v>
+        <v>472</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>490</v>
+        <v>473</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>484</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>492</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B5" t="s">
-        <v>502</v>
+        <v>485</v>
       </c>
       <c r="C5" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="D5" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="B6" t="s">
-        <v>504</v>
+        <v>487</v>
       </c>
       <c r="C6" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="D6" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>506</v>
+        <v>489</v>
       </c>
       <c r="C7" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4919,13 +4863,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>508</v>
+        <v>491</v>
       </c>
       <c r="C8" t="s">
-        <v>472</v>
+        <v>455</v>
       </c>
       <c r="D8" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4933,55 +4877,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>509</v>
+        <v>492</v>
       </c>
       <c r="C9" t="s">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="D9" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>511</v>
+        <v>494</v>
       </c>
       <c r="C10" t="s">
-        <v>512</v>
+        <v>495</v>
       </c>
       <c r="D10" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B11" t="s">
-        <v>513</v>
+        <v>496</v>
       </c>
       <c r="C11" t="s">
-        <v>514</v>
+        <v>497</v>
       </c>
       <c r="D11" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>515</v>
+        <v>498</v>
       </c>
       <c r="C12" t="s">
-        <v>474</v>
+        <v>457</v>
       </c>
       <c r="D12" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4989,111 +4933,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="C13" t="s">
-        <v>476</v>
+        <v>459</v>
       </c>
       <c r="D13" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="C14" t="s">
-        <v>478</v>
+        <v>461</v>
       </c>
       <c r="D14" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>518</v>
+        <v>501</v>
       </c>
       <c r="C15" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="D15" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="B16" t="s">
-        <v>520</v>
+        <v>503</v>
       </c>
       <c r="C16" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="D16" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>521</v>
+        <v>504</v>
       </c>
       <c r="C17" t="s">
-        <v>522</v>
+        <v>505</v>
       </c>
       <c r="D17" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
-        <v>523</v>
+        <v>506</v>
       </c>
       <c r="C18" t="s">
-        <v>524</v>
+        <v>507</v>
       </c>
       <c r="D18" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>525</v>
+        <v>508</v>
       </c>
       <c r="C19" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="D19" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s">
-        <v>526</v>
+        <v>509</v>
       </c>
       <c r="C20" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="D20" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5101,27 +5045,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="C21" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="D21" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>528</v>
+        <v>511</v>
       </c>
       <c r="C22" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="D22" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5129,13 +5073,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>529</v>
+        <v>512</v>
       </c>
       <c r="C23" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D23" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5143,83 +5087,83 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>530</v>
+        <v>513</v>
       </c>
       <c r="C24" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="D24" t="s">
-        <v>507</v>
+        <v>490</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>531</v>
+        <v>514</v>
       </c>
       <c r="C25" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D25" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>532</v>
+        <v>515</v>
       </c>
       <c r="C26" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="D26" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s">
-        <v>533</v>
+        <v>516</v>
       </c>
       <c r="C27" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="D27" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>534</v>
+        <v>517</v>
       </c>
       <c r="C28" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="D28" t="s">
-        <v>503</v>
+        <v>486</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="C29" t="s">
-        <v>536</v>
+        <v>519</v>
       </c>
       <c r="D29" t="s">
-        <v>505</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -5234,7 +5178,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>537</v>
+        <v>520</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5244,490 +5188,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>538</v>
+        <v>521</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>539</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>540</v>
+        <v>523</v>
       </c>
       <c r="B5" t="s">
-        <v>541</v>
+        <v>524</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>542</v>
+        <v>525</v>
       </c>
       <c r="B6" t="s">
-        <v>543</v>
+        <v>526</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="B7" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>546</v>
+        <v>529</v>
       </c>
       <c r="B8" t="s">
-        <v>547</v>
+        <v>530</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="B9" t="s">
-        <v>549</v>
+        <v>532</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>550</v>
+        <v>533</v>
       </c>
       <c r="B10" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>551</v>
+        <v>534</v>
       </c>
       <c r="B11" t="s">
-        <v>498</v>
+        <v>481</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>552</v>
+        <v>535</v>
       </c>
       <c r="B12" t="s">
-        <v>553</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="B13" t="s">
-        <v>555</v>
+        <v>538</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="B14" t="s">
-        <v>557</v>
+        <v>540</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>558</v>
+        <v>541</v>
       </c>
       <c r="B15" t="s">
-        <v>559</v>
+        <v>542</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="B16" t="s">
-        <v>561</v>
+        <v>544</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
       <c r="B17" t="s">
-        <v>563</v>
+        <v>546</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>564</v>
+        <v>547</v>
       </c>
       <c r="B18" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>565</v>
+        <v>548</v>
       </c>
       <c r="B19" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>566</v>
+        <v>549</v>
       </c>
       <c r="B20" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>568</v>
+        <v>551</v>
       </c>
       <c r="B21" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>569</v>
+        <v>552</v>
       </c>
       <c r="B22" t="s">
-        <v>570</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>571</v>
+        <v>554</v>
       </c>
       <c r="B23" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>572</v>
+        <v>555</v>
       </c>
       <c r="B24" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>573</v>
+        <v>556</v>
       </c>
       <c r="B25" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="B26" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>575</v>
+        <v>558</v>
       </c>
       <c r="B27" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>576</v>
+        <v>559</v>
       </c>
       <c r="B28" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>577</v>
+        <v>560</v>
       </c>
       <c r="B29" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>578</v>
+        <v>561</v>
       </c>
       <c r="B30" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>579</v>
+        <v>562</v>
       </c>
       <c r="B31" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>580</v>
+        <v>563</v>
       </c>
       <c r="B32" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>581</v>
+        <v>564</v>
       </c>
       <c r="B33" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>582</v>
+        <v>565</v>
       </c>
       <c r="B34" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>583</v>
+        <v>566</v>
       </c>
       <c r="B35" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>584</v>
+        <v>567</v>
       </c>
       <c r="B36" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>585</v>
+        <v>568</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>586</v>
+        <v>569</v>
       </c>
       <c r="B38" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="B39" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>588</v>
+        <v>571</v>
       </c>
       <c r="B40" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>589</v>
+        <v>572</v>
       </c>
       <c r="B41" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="B42" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="B43" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="B44" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="B45" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>594</v>
+        <v>577</v>
       </c>
       <c r="B46" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>595</v>
+        <v>578</v>
       </c>
       <c r="B47" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>596</v>
+        <v>579</v>
       </c>
       <c r="B48" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>597</v>
+        <v>580</v>
       </c>
       <c r="B49" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>598</v>
+        <v>581</v>
       </c>
       <c r="B50" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>599</v>
+        <v>582</v>
       </c>
       <c r="B51" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="B52" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>601</v>
+        <v>584</v>
       </c>
       <c r="B53" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>602</v>
+        <v>585</v>
       </c>
       <c r="B54" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>603</v>
+        <v>586</v>
       </c>
       <c r="B55" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="B56" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>605</v>
+        <v>588</v>
       </c>
       <c r="B57" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="B58" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>607</v>
+        <v>590</v>
       </c>
       <c r="B59" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>608</v>
+        <v>591</v>
       </c>
       <c r="B60" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="B61" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>610</v>
+        <v>593</v>
       </c>
       <c r="B62" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="B63" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="B64" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5742,458 +5686,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>614</v>
+        <v>597</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>618</v>
+        <v>601</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>619</v>
+        <v>602</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>620</v>
+        <v>603</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>621</v>
+        <v>604</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>622</v>
+        <v>605</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>623</v>
+        <v>606</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>624</v>
+        <v>607</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="B5" t="s">
-        <v>626</v>
+        <v>609</v>
       </c>
       <c r="C5" t="s">
-        <v>627</v>
+        <v>610</v>
       </c>
       <c r="D5" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E5" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F5" t="s">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="G5" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H5" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="I5" t="s">
-        <v>631</v>
+        <v>614</v>
       </c>
       <c r="J5" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K5" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="B6" t="s">
-        <v>634</v>
+        <v>617</v>
       </c>
       <c r="C6" t="s">
-        <v>635</v>
+        <v>618</v>
       </c>
       <c r="D6" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E6" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F6" t="s">
-        <v>629</v>
+        <v>612</v>
       </c>
       <c r="G6" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H6" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="I6" t="s">
-        <v>636</v>
+        <v>619</v>
       </c>
       <c r="J6" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K6" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="B7" t="s">
-        <v>637</v>
+        <v>620</v>
       </c>
       <c r="C7" t="s">
-        <v>638</v>
+        <v>621</v>
       </c>
       <c r="D7" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E7" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F7" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="G7" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H7" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="I7" t="s">
-        <v>639</v>
+        <v>622</v>
       </c>
       <c r="J7" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K7" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>494</v>
+        <v>477</v>
       </c>
       <c r="B8" t="s">
-        <v>640</v>
+        <v>623</v>
       </c>
       <c r="C8" t="s">
-        <v>641</v>
+        <v>624</v>
       </c>
       <c r="D8" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E8" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F8" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="G8" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H8" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="I8" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="J8" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K8" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="B9" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="C9" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="D9" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E9" t="s">
+        <v>611</v>
+      </c>
+      <c r="F9" t="s">
+        <v>269</v>
+      </c>
+      <c r="G9" t="s">
+        <v>611</v>
+      </c>
+      <c r="H9" t="s">
+        <v>613</v>
+      </c>
+      <c r="I9" t="s">
         <v>628</v>
       </c>
-      <c r="F9" t="s">
-        <v>286</v>
-      </c>
-      <c r="G9" t="s">
-        <v>628</v>
-      </c>
-      <c r="H9" t="s">
-        <v>630</v>
-      </c>
-      <c r="I9" t="s">
-        <v>645</v>
-      </c>
       <c r="J9" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K9" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="C10" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="D10" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E10" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F10" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="G10" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H10" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="I10" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="J10" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K10" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>493</v>
+        <v>476</v>
       </c>
       <c r="B11" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="C11" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="D11" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E11" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F11" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="G11" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H11" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="I11" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="J11" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K11" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="B12" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="C12" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="D12" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E12" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F12" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="G12" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H12" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="J12" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K12" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>570</v>
+        <v>553</v>
       </c>
       <c r="B13" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="C13" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="D13" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E13" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F13" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="G13" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H13" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="I13" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="J13" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K13" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="B14" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="C14" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="D14" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E14" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F14" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="G14" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="H14" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="J14" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K14" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>567</v>
+        <v>550</v>
       </c>
       <c r="B15" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="C15" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="D15" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="E15" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="F15" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="G15" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="H15" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="J15" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K15" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>313</v>
+        <v>296</v>
       </c>
       <c r="B16" t="s">
-        <v>661</v>
+        <v>644</v>
       </c>
       <c r="C16" t="s">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="D16" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="E16" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="F16" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="G16" t="s">
-        <v>628</v>
+        <v>611</v>
       </c>
       <c r="H16" t="s">
-        <v>630</v>
+        <v>613</v>
       </c>
       <c r="I16" t="s">
-        <v>663</v>
+        <v>646</v>
       </c>
       <c r="J16" t="s">
-        <v>632</v>
+        <v>615</v>
       </c>
       <c r="K16" t="s">
-        <v>633</v>
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -6208,22 +6152,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>664</v>
+        <v>647</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -6263,22 +6207,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>668</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>665</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
     </row>
   </sheetData>
@@ -6293,44 +6237,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -6345,44 +6289,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>676</v>
+        <v>659</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>488</v>
+        <v>471</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>616</v>
+        <v>599</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>491</v>
+        <v>474</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>670</v>
+        <v>653</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>672</v>
+        <v>655</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>673</v>
+        <v>656</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>674</v>
+        <v>657</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>675</v>
+        <v>658</v>
       </c>
     </row>
   </sheetData>
@@ -6397,92 +6341,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>213</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6492,22 +6436,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
     </row>
   </sheetData>
@@ -6522,7 +6466,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6537,87 +6481,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>691</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>692</v>
+        <v>675</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>693</v>
+        <v>676</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -6682,7 +6626,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A85"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6842,132 +6786,132 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
-      <c r="A41" t="s">
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
-      <c r="A42" t="s">
+    <row r="45" spans="1:1">
+      <c r="A45" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
+    <row r="48" spans="1:1">
+      <c r="A48" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
-      <c r="A53" s="1" t="s">
-        <v>19</v>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>73</v>
+      <c r="A58" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
-      <c r="A63" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>77</v>
+    <row r="64" spans="1:1">
+      <c r="A64" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:1">
@@ -6981,63 +6925,28 @@
       </c>
     </row>
     <row r="73" spans="1:1">
-      <c r="A73" s="1" t="s">
+      <c r="A73" t="s">
         <v>83</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -7047,52 +6956,47 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -7102,52 +7006,47 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -7157,12 +7056,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A84"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7172,22 +7071,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -7197,27 +7096,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -7227,17 +7126,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -7247,272 +7146,227 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>138</v>
+      <c r="A38" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="1" t="s">
-        <v>16</v>
+      <c r="A40" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>17</v>
+      <c r="A42" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>141</v>
+      <c r="A45" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="1" t="s">
-        <v>18</v>
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="1" t="s">
-        <v>19</v>
+      <c r="A50" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>147</v>
+      <c r="A55" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>151</v>
+      <c r="A60" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:1">
-      <c r="A65" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" s="1" t="s">
-        <v>26</v>
+      <c r="A65" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" s="1" t="s">
-        <v>83</v>
+      <c r="A70" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="687">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="688">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -289,22 +289,22 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftNoNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otpdone(otp_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_pgenb(otp_pgenb)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.otp_clock_enable(otp_clock_enable)</t>
+    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
   </si>
   <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
@@ -316,43 +316,43 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftNoNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftNoNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
+  </si>
+  <si>
+    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -484,22 +484,22 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_pgenb - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_pgenb", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftNoNo", "instance": "XSERDESdftNoNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
+    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
+  </si>
+  <si>
+    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -836,40 +836,43 @@
     <t>serdes_memory_program</t>
   </si>
   <si>
+    <t>Auto</t>
+  </si>
+  <si>
+    <t>serdes_memory_bist</t>
+  </si>
+  <si>
+    <t>serdes_address</t>
+  </si>
+  <si>
+    <t>serdes_password</t>
+  </si>
+  <si>
+    <t>0x03</t>
+  </si>
+  <si>
+    <t>serdes_pad</t>
+  </si>
+  <si>
+    <t>dedicated</t>
+  </si>
+  <si>
+    <t>serdes_vmax</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>serdes_clock</t>
+  </si>
+  <si>
+    <t>3200</t>
+  </si>
+  <si>
+    <t>serdes_supply</t>
+  </si>
+  <si>
     <t>Single</t>
-  </si>
-  <si>
-    <t>serdes_memory_bist</t>
-  </si>
-  <si>
-    <t>serdes_address</t>
-  </si>
-  <si>
-    <t>serdes_password</t>
-  </si>
-  <si>
-    <t>0x03</t>
-  </si>
-  <si>
-    <t>serdes_pad</t>
-  </si>
-  <si>
-    <t>dedicated</t>
-  </si>
-  <si>
-    <t>serdes_vmax</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>serdes_clock</t>
-  </si>
-  <si>
-    <t>3200</t>
-  </si>
-  <si>
-    <t>serdes_supply</t>
   </si>
   <si>
     <t>serdes_split_vi2c_pad</t>
@@ -3584,17 +3587,17 @@
         <v>272</v>
       </c>
       <c r="B36" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B38" t="s">
         <v>238</v>
@@ -3602,15 +3605,15 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s">
         <v>244</v>
@@ -3618,7 +3621,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B41" t="s">
         <v>244</v>
@@ -3626,7 +3629,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B42" t="s">
         <v>244</v>
@@ -3634,15 +3637,15 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B43" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3655,15 +3658,15 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B46" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B47" t="s">
         <v>236</v>
@@ -3671,15 +3674,15 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B48" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B49" t="s">
         <v>236</v>
@@ -3687,7 +3690,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B50" t="s">
         <v>236</v>
@@ -3695,15 +3698,15 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B52" t="s">
         <v>238</v>
@@ -3711,7 +3714,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3724,23 +3727,23 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B57" t="s">
         <v>238</v>
@@ -3748,7 +3751,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3761,97 +3764,97 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B64" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B69" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B70" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -3864,7 +3867,7 @@
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B77" t="s">
         <v>238</v>
@@ -3872,7 +3875,7 @@
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B78" t="s">
         <v>238</v>
@@ -3880,7 +3883,7 @@
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B79" t="s">
         <v>238</v>
@@ -3888,23 +3891,23 @@
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B82" t="s">
         <v>244</v>
@@ -3912,7 +3915,7 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B83" t="s">
         <v>244</v>
@@ -3920,7 +3923,7 @@
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B84" t="s">
         <v>244</v>
@@ -3928,7 +3931,7 @@
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B85" t="s">
         <v>244</v>
@@ -3936,7 +3939,7 @@
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B86" t="s">
         <v>244</v>
@@ -3944,7 +3947,7 @@
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B87" t="s">
         <v>244</v>
@@ -3952,7 +3955,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B88" t="s">
         <v>244</v>
@@ -3960,7 +3963,7 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B89" t="s">
         <v>244</v>
@@ -3968,15 +3971,15 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B90" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B91" t="s">
         <v>244</v>
@@ -3984,7 +3987,7 @@
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B92" t="s">
         <v>238</v>
@@ -3992,7 +3995,7 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B93" t="s">
         <v>238</v>
@@ -4000,7 +4003,7 @@
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B94" t="s">
         <v>244</v>
@@ -4008,7 +4011,7 @@
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B95" t="s">
         <v>244</v>
@@ -4016,7 +4019,7 @@
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B96" t="s">
         <v>244</v>
@@ -4024,7 +4027,7 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B97" t="s">
         <v>244</v>
@@ -4032,7 +4035,7 @@
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B98" t="s">
         <v>244</v>
@@ -4040,7 +4043,7 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B99" t="s">
         <v>244</v>
@@ -4048,7 +4051,7 @@
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B100" t="s">
         <v>244</v>
@@ -4056,15 +4059,15 @@
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B101" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B102" t="s">
         <v>238</v>
@@ -4072,7 +4075,7 @@
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B103" t="s">
         <v>269</v>
@@ -4080,7 +4083,7 @@
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -4093,71 +4096,71 @@
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B106" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B107" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B108" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B109" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B111" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B113" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -4170,431 +4173,431 @@
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B117" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B118" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B120" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B121" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B123" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B124" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B125" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B126" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B127" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B128" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B129" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B135" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B138" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B139" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B140" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B141" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B142" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B143" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B144" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B145" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B146" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B147" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B148" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B149" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B150" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B151" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B152" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B153" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B154" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B155" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B156" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B157" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B158" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B159" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B160" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B161" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B162" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B163" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B164" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B165" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B166" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B167" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B168" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B169" t="s">
         <v>265</v>
@@ -4602,39 +4605,39 @@
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B170" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B171" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B172" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B173" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B174" t="s">
         <v>244</v>
@@ -4642,50 +4645,50 @@
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B175" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B176" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B177" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B178" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B179" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B180" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -4700,47 +4703,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>269</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4748,15 +4751,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4764,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
   </sheetData>
@@ -4779,7 +4782,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -4794,26 +4797,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -4821,13 +4824,13 @@
         <v>195</v>
       </c>
       <c r="B5" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C5" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -4835,13 +4838,13 @@
         <v>195</v>
       </c>
       <c r="B6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -4849,13 +4852,13 @@
         <v>198</v>
       </c>
       <c r="B7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C7" t="s">
         <v>265</v>
       </c>
       <c r="D7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4863,13 +4866,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>492</v>
+      </c>
+      <c r="C8" t="s">
+        <v>456</v>
+      </c>
+      <c r="D8" t="s">
         <v>491</v>
-      </c>
-      <c r="C8" t="s">
-        <v>455</v>
-      </c>
-      <c r="D8" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4877,13 +4880,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4891,13 +4894,13 @@
         <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D10" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4905,13 +4908,13 @@
         <v>203</v>
       </c>
       <c r="B11" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D11" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -4919,13 +4922,13 @@
         <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D12" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4933,13 +4936,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D13" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -4947,13 +4950,13 @@
         <v>206</v>
       </c>
       <c r="B14" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C14" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D14" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4961,13 +4964,13 @@
         <v>206</v>
       </c>
       <c r="B15" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D15" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4975,13 +4978,13 @@
         <v>206</v>
       </c>
       <c r="B16" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C16" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D16" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4989,13 +4992,13 @@
         <v>209</v>
       </c>
       <c r="B17" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C17" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D17" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -5003,13 +5006,13 @@
         <v>210</v>
       </c>
       <c r="B18" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C18" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D18" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -5017,13 +5020,13 @@
         <v>210</v>
       </c>
       <c r="B19" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D19" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -5031,13 +5034,13 @@
         <v>211</v>
       </c>
       <c r="B20" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C20" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D20" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5045,13 +5048,13 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C21" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D21" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -5059,13 +5062,13 @@
         <v>214</v>
       </c>
       <c r="B22" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C22" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D22" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5073,13 +5076,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C23" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D23" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5087,13 +5090,13 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C24" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="D24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -5101,13 +5104,13 @@
         <v>215</v>
       </c>
       <c r="B25" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C25" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D25" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -5115,13 +5118,13 @@
         <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C26" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D26" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -5129,13 +5132,13 @@
         <v>216</v>
       </c>
       <c r="B27" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C27" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D27" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -5143,13 +5146,13 @@
         <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C28" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D28" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5157,13 +5160,13 @@
         <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D29" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -5178,7 +5181,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5188,167 +5191,167 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B10" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B11" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B18" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B19" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B20" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>552</v>
+      </c>
+      <c r="B21" t="s">
         <v>551</v>
-      </c>
-      <c r="B21" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B22" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B24" t="s">
         <v>269</v>
@@ -5356,322 +5359,322 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B25" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B26" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B28" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B29" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B30" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B31" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B32" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B34" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B35" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B38" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B40" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B42" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B43" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B44" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B45" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B46" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B47" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B48" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B49" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B50" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B51" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B52" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B53" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B54" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B55" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B56" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B57" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B58" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B59" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B60" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B61" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B62" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B63" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B64" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
   </sheetData>
@@ -5686,222 +5689,222 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D5" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F5" t="s">
+        <v>613</v>
+      </c>
+      <c r="G5" t="s">
         <v>612</v>
       </c>
-      <c r="G5" t="s">
-        <v>611</v>
-      </c>
       <c r="H5" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B6" t="s">
+        <v>618</v>
+      </c>
+      <c r="C6" t="s">
+        <v>619</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+      <c r="E6" t="s">
+        <v>612</v>
+      </c>
+      <c r="F6" t="s">
+        <v>613</v>
+      </c>
+      <c r="G6" t="s">
+        <v>612</v>
+      </c>
+      <c r="H6" t="s">
+        <v>614</v>
+      </c>
+      <c r="I6" t="s">
+        <v>620</v>
+      </c>
+      <c r="J6" t="s">
+        <v>616</v>
+      </c>
+      <c r="K6" t="s">
         <v>617</v>
-      </c>
-      <c r="C6" t="s">
-        <v>618</v>
-      </c>
-      <c r="D6" t="s">
-        <v>310</v>
-      </c>
-      <c r="E6" t="s">
-        <v>611</v>
-      </c>
-      <c r="F6" t="s">
-        <v>612</v>
-      </c>
-      <c r="G6" t="s">
-        <v>611</v>
-      </c>
-      <c r="H6" t="s">
-        <v>613</v>
-      </c>
-      <c r="I6" t="s">
-        <v>619</v>
-      </c>
-      <c r="J6" t="s">
-        <v>615</v>
-      </c>
-      <c r="K6" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B7" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F7" t="s">
         <v>269</v>
       </c>
       <c r="G7" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H7" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I7" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="J7" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B8" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C8" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D8" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F8" t="s">
         <v>269</v>
       </c>
       <c r="G8" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H8" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I8" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="J8" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B9" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F9" t="s">
         <v>269</v>
       </c>
       <c r="G9" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H9" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I9" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="J9" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -5909,235 +5912,235 @@
         <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C10" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D10" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F10" t="s">
         <v>269</v>
       </c>
       <c r="G10" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H10" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="J10" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B11" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="C11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F11" t="s">
         <v>269</v>
       </c>
       <c r="G11" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H11" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J11" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K11" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C12" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D12" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G12" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H12" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J12" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B13" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E13" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F13" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="G13" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H13" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I13" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J13" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K13" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B14" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E14" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H14" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J14" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K14" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B15" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C15" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D15" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="E15" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="F15" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G15" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H15" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="J15" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B16" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C16" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E16" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="F16" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G16" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H16" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="I16" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="J16" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="K16" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
   </sheetData>
@@ -6152,22 +6155,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -6207,22 +6210,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
   </sheetData>
@@ -6237,44 +6240,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -6289,44 +6292,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>601</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>599</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>
@@ -6341,7 +6344,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6351,7 +6354,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -6361,17 +6364,17 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -6381,37 +6384,37 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -6421,12 +6424,12 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6436,7 +6439,7 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -6446,12 +6449,12 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
   </sheetData>
@@ -6466,7 +6469,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6481,87 +6484,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="688">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="689">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -620,6 +620,15 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdriver_e53ed485.v:218: error: Unknown module type: fet_fetdriver_e53ed485_Xpmos0
+2 error(s) during elaboration.
+*** These modules were missing:
+        fet_fetdriver_e53ed485_Xpmos0 referenced 1 times.
+***
 </t>
   </si>
   <si>
@@ -2640,7 +2649,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2766,6 +2775,11 @@
     <row r="48" spans="1:1">
       <c r="A48" t="s">
         <v>189</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -2780,7 +2794,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2800,17 +2814,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3035,32 +3049,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -3070,37 +3084,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3110,62 +3124,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -3175,17 +3189,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -3195,47 +3209,47 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -3245,7 +3259,7 @@
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -3260,17 +3274,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3285,52 +3299,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -3345,81 +3359,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B11" t="s">
         <v>245</v>
-      </c>
-      <c r="B11" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3427,1268 +3441,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B20" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B33" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B35" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B40" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B41" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B42" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B43" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B46" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B47" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B48" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B51" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B52" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B56" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B57" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B64" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B67" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B68" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B69" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B70" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B77" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B78" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B79" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B80" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B81" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B82" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B83" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B84" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B85" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B86" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B88" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B89" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B90" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B91" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B92" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B93" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B94" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B95" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B96" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B97" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B98" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B99" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B100" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B101" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B102" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B106" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B107" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B108" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B109" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B110" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B111" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B112" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B113" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B116" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B117" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B118" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B119" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B120" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B121" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B122" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B123" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B124" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B125" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B126" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B127" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B128" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B130" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B132" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B133" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B134" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B135" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B136" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B137" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B138" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B139" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B140" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B141" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B142" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B143" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B144" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B145" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B146" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B147" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B148" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B149" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B150" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B151" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B152" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B153" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B154" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B155" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B156" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B157" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B158" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B159" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B160" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B161" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B162" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B163" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B164" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B165" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B166" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B167" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B168" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B169" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B170" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B171" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B172" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B173" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B174" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B175" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B176" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B177" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B178" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B179" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B180" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -4703,47 +4717,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4751,15 +4765,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4767,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>
@@ -4782,7 +4796,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
   </sheetData>
@@ -4797,68 +4811,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C5" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D5" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D6" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B7" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4866,13 +4880,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
+        <v>493</v>
+      </c>
+      <c r="C8" t="s">
+        <v>457</v>
+      </c>
+      <c r="D8" t="s">
         <v>492</v>
-      </c>
-      <c r="C8" t="s">
-        <v>456</v>
-      </c>
-      <c r="D8" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4880,55 +4894,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D9" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B10" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C10" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D10" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B11" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C11" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D11" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B12" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C12" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4936,111 +4950,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C13" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D13" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B14" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C14" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D14" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B15" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C15" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D15" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B16" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C16" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D16" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B17" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C17" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D17" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B18" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C18" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D18" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B19" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D19" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C20" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D20" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5048,27 +5062,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C21" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D21" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B22" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C22" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D22" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5076,13 +5090,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C23" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D23" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5090,69 +5104,69 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C24" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D24" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C25" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D25" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B26" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C26" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D26" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B27" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C27" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D27" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B28" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C28" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D28" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -5160,13 +5174,13 @@
         <v>157</v>
       </c>
       <c r="B29" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C29" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D29" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -5181,7 +5195,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5191,490 +5205,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B8" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B10" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B11" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B12" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B13" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B14" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B15" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B16" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B17" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B18" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B19" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B20" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
+        <v>553</v>
+      </c>
+      <c r="B21" t="s">
         <v>552</v>
-      </c>
-      <c r="B21" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B22" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B24" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B25" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B26" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B28" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B29" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B30" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B31" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B32" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B33" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B34" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B35" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B36" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B38" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B39" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B40" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B43" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B44" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B45" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B46" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B47" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B48" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B49" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B50" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B51" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B52" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B53" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B54" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B55" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B56" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B57" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B58" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B59" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B60" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B61" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B62" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B63" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B64" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -5689,458 +5703,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B5" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C5" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D5" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E5" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F5" t="s">
+        <v>614</v>
+      </c>
+      <c r="G5" t="s">
         <v>613</v>
       </c>
-      <c r="G5" t="s">
-        <v>612</v>
-      </c>
       <c r="H5" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="J5" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K5" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B6" t="s">
+        <v>619</v>
+      </c>
+      <c r="C6" t="s">
+        <v>620</v>
+      </c>
+      <c r="D6" t="s">
+        <v>312</v>
+      </c>
+      <c r="E6" t="s">
+        <v>613</v>
+      </c>
+      <c r="F6" t="s">
+        <v>614</v>
+      </c>
+      <c r="G6" t="s">
+        <v>613</v>
+      </c>
+      <c r="H6" t="s">
+        <v>615</v>
+      </c>
+      <c r="I6" t="s">
+        <v>621</v>
+      </c>
+      <c r="J6" t="s">
+        <v>617</v>
+      </c>
+      <c r="K6" t="s">
         <v>618</v>
-      </c>
-      <c r="C6" t="s">
-        <v>619</v>
-      </c>
-      <c r="D6" t="s">
-        <v>311</v>
-      </c>
-      <c r="E6" t="s">
-        <v>612</v>
-      </c>
-      <c r="F6" t="s">
-        <v>613</v>
-      </c>
-      <c r="G6" t="s">
-        <v>612</v>
-      </c>
-      <c r="H6" t="s">
-        <v>614</v>
-      </c>
-      <c r="I6" t="s">
-        <v>620</v>
-      </c>
-      <c r="J6" t="s">
-        <v>616</v>
-      </c>
-      <c r="K6" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B7" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C7" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E7" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G7" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H7" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I7" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="J7" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K7" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B8" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C8" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="D8" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E8" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G8" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H8" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I8" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="J8" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K8" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B9" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C9" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G9" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H9" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I9" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="J9" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K9" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B10" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C10" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F10" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G10" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H10" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I10" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J10" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K10" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B11" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C11" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D11" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F11" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G11" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H11" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I11" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="J11" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K11" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C12" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D12" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F12" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G12" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H12" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J12" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K12" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C13" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="D13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F13" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G13" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H13" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I13" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J13" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K13" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C14" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E14" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F14" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G14" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H14" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J14" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K14" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B15" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C15" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="D15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="G15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H15" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="J15" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K15" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B16" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C16" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="D16" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E16" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F16" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G16" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H16" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="I16" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="J16" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="K16" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -6155,22 +6169,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -6210,22 +6224,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>
@@ -6240,44 +6254,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -6292,44 +6306,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>600</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
   </sheetData>
@@ -6344,92 +6358,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6439,22 +6453,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
   </sheetData>
@@ -6469,7 +6483,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6484,87 +6498,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1113" uniqueCount="689">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="668">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -289,24 +289,9 @@
     <t>XWALTZ,XceleraSERDES</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_nr(otp_nr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otpdone(otp_program_done)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock(otp_clock)</t>
-  </si>
-  <si>
     <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.otp_loadok(otp_loadok)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.otp_clock_enable(otp_clock_enable)</t>
-  </si>
-  <si>
     <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
   </si>
   <si>
@@ -316,43 +301,13 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdext(tdext)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_serdes(ten_serdes)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_on(ten_oscillator_on)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_off(ten_oscillator_off)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_div8(ten_oscillator_div8)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.ten_oscillator_external(ten_oscillator_external)</t>
+    <t>Floating pin XSERDESdftYesNo.tdo(tdo_noconn)</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
   </si>
   <si>
-    <t>tdext - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdext", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_serdes - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_serdes", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_on - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_on", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_off - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_off", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_div8 - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_div8", "io": "output", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>ten_oscillator_external - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "ten_oscillator_external", "io": "output", "bus": "", "type": "component"}</t>
+    <t>tdo_noconn - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdo", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -484,22 +439,7 @@
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
-    <t>otp_nr - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_nr", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_program_done - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otpdone", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
     <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_loadok - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_loadok", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>otp_clock_enable - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "otp_clock_enable", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
@@ -620,15 +560,6 @@
     <t xml:space="preserve">* Running ALL verilog files through iverilog.
 * Process may take a few minutes....
 * Report is done when 'END REPORT' appears.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">!!! Iverilog Error !!!
-/celera/projects/Sunnyvale/software/WALTZ/verilog5/fetdriver_e53ed485.v:218: error: Unknown module type: fet_fetdriver_e53ed485_Xpmos0
-2 error(s) during elaboration.
-*** These modules were missing:
-        fet_fetdriver_e53ed485_Xpmos0 referenced 1 times.
-***
 </t>
   </si>
   <si>
@@ -2494,7 +2425,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2514,7 +2445,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2529,7 +2460,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -2544,17 +2475,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2569,12 +2500,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2589,17 +2520,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2614,12 +2545,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2634,7 +2565,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2649,137 +2580,132 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2794,7 +2720,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2814,17 +2740,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>194</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3049,32 +2975,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -3084,37 +3010,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>202</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3124,62 +3050,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -3189,17 +3115,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -3209,57 +3135,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>201</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3274,17 +3200,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -3299,52 +3225,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3359,81 +3285,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>215</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="B6" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="B7" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>241</v>
+        <v>220</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>221</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>225</v>
       </c>
       <c r="B11" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3441,1268 +3367,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>249</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>251</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>253</v>
+        <v>232</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>255</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>235</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>257</v>
+        <v>236</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>258</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>259</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="B28" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s">
-        <v>262</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>263</v>
+        <v>242</v>
       </c>
       <c r="B30" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>264</v>
+        <v>243</v>
       </c>
       <c r="B31" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>265</v>
+        <v>244</v>
       </c>
       <c r="B32" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>267</v>
+        <v>246</v>
       </c>
       <c r="B33" t="s">
-        <v>268</v>
+        <v>247</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B34" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="B35" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="B36" t="s">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>275</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>276</v>
+        <v>255</v>
       </c>
       <c r="B38" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="B39" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>279</v>
+        <v>258</v>
       </c>
       <c r="B40" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>280</v>
+        <v>259</v>
       </c>
       <c r="B41" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="B42" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>282</v>
+        <v>261</v>
       </c>
       <c r="B43" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>284</v>
+        <v>263</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="B46" t="s">
-        <v>286</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>287</v>
+        <v>266</v>
       </c>
       <c r="B47" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>288</v>
+        <v>267</v>
       </c>
       <c r="B48" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>289</v>
+        <v>268</v>
       </c>
       <c r="B49" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>290</v>
+        <v>269</v>
       </c>
       <c r="B50" t="s">
-        <v>237</v>
+        <v>216</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="B52" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="B55" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="B56" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="B57" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>302</v>
+        <v>281</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>304</v>
+        <v>283</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B64" t="s">
-        <v>306</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>308</v>
+        <v>287</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>309</v>
+        <v>288</v>
       </c>
       <c r="B67" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="B68" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
       <c r="B69" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>314</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>315</v>
+        <v>294</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>316</v>
+        <v>295</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>317</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>318</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>319</v>
+        <v>298</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>320</v>
+        <v>299</v>
       </c>
       <c r="B77" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>321</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>322</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>323</v>
+        <v>302</v>
       </c>
       <c r="B80" t="s">
-        <v>324</v>
+        <v>303</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s">
-        <v>326</v>
+        <v>305</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>327</v>
+        <v>306</v>
       </c>
       <c r="B82" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>328</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>329</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>330</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>331</v>
+        <v>310</v>
       </c>
       <c r="B86" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>332</v>
+        <v>311</v>
       </c>
       <c r="B87" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>334</v>
+        <v>313</v>
       </c>
       <c r="B89" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>335</v>
+        <v>314</v>
       </c>
       <c r="B90" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>337</v>
+        <v>316</v>
       </c>
       <c r="B91" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="B92" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
       <c r="B93" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>340</v>
+        <v>319</v>
       </c>
       <c r="B94" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>341</v>
+        <v>320</v>
       </c>
       <c r="B95" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>342</v>
+        <v>321</v>
       </c>
       <c r="B96" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="B97" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="B98" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="B99" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="B100" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="B101" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>349</v>
+        <v>328</v>
       </c>
       <c r="B102" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
       <c r="B103" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>351</v>
+        <v>330</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>352</v>
+        <v>331</v>
       </c>
       <c r="B106" t="s">
-        <v>353</v>
+        <v>332</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>354</v>
+        <v>333</v>
       </c>
       <c r="B107" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>356</v>
+        <v>335</v>
       </c>
       <c r="B108" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>358</v>
+        <v>337</v>
       </c>
       <c r="B109" t="s">
-        <v>359</v>
+        <v>338</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>360</v>
+        <v>339</v>
       </c>
       <c r="B110" t="s">
-        <v>361</v>
+        <v>340</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>362</v>
+        <v>341</v>
       </c>
       <c r="B111" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="B112" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>366</v>
+        <v>345</v>
       </c>
       <c r="B113" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>368</v>
+        <v>347</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>369</v>
+        <v>348</v>
       </c>
       <c r="B116" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>370</v>
+        <v>349</v>
       </c>
       <c r="B117" t="s">
-        <v>371</v>
+        <v>350</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>372</v>
+        <v>351</v>
       </c>
       <c r="B118" t="s">
-        <v>373</v>
+        <v>352</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>374</v>
+        <v>353</v>
       </c>
       <c r="B119" t="s">
-        <v>375</v>
+        <v>354</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>376</v>
+        <v>355</v>
       </c>
       <c r="B120" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="B121" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>380</v>
+        <v>359</v>
       </c>
       <c r="B122" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>382</v>
+        <v>361</v>
       </c>
       <c r="B123" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>383</v>
+        <v>362</v>
       </c>
       <c r="B124" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>384</v>
+        <v>363</v>
       </c>
       <c r="B125" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B126" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="B127" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="B128" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="B129" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="B130" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>344</v>
+        <v>323</v>
       </c>
       <c r="B131" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>345</v>
+        <v>324</v>
       </c>
       <c r="B132" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>347</v>
+        <v>326</v>
       </c>
       <c r="B133" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>346</v>
+        <v>325</v>
       </c>
       <c r="B134" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="B135" t="s">
-        <v>283</v>
+        <v>262</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
       <c r="B136" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="B137" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="B138" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
       <c r="B139" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
       <c r="B140" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="B141" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="B142" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="B143" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="B144" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="B145" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="B146" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="B147" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="B148" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="B149" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="B150" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="B151" t="s">
-        <v>423</v>
+        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>424</v>
+        <v>403</v>
       </c>
       <c r="B152" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="B153" t="s">
-        <v>427</v>
+        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>428</v>
+        <v>407</v>
       </c>
       <c r="B154" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="B155" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="B156" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="B157" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="B158" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="B159" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="B160" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="B161" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="B162" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="B163" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="B164" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="B165" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="B166" t="s">
-        <v>425</v>
+        <v>404</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="B167" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="B168" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="B169" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="B170" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="B171" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="B172" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="B173" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="B174" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="B175" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="B176" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="B177" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="B178" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="B179" t="s">
-        <v>470</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="B180" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -4717,47 +4643,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4765,15 +4691,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>480</v>
+        <v>459</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>481</v>
+        <v>460</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4781,7 +4707,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -4796,7 +4722,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
@@ -4811,68 +4737,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>475</v>
+        <v>454</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>477</v>
+        <v>456</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="C5" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
       <c r="D5" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="C6" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="D6" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="C7" t="s">
-        <v>266</v>
+        <v>245</v>
       </c>
       <c r="D7" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4880,13 +4806,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="C8" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="D8" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4894,55 +4820,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="C9" t="s">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="D9" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="C10" t="s">
-        <v>497</v>
+        <v>476</v>
       </c>
       <c r="D10" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>498</v>
+        <v>477</v>
       </c>
       <c r="C11" t="s">
-        <v>499</v>
+        <v>478</v>
       </c>
       <c r="D11" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="B12" t="s">
-        <v>500</v>
+        <v>479</v>
       </c>
       <c r="C12" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="D12" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4950,111 +4876,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="C13" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="D13" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="B14" t="s">
-        <v>502</v>
+        <v>481</v>
       </c>
       <c r="C14" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="D14" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s">
-        <v>503</v>
+        <v>482</v>
       </c>
       <c r="C15" t="s">
-        <v>504</v>
+        <v>483</v>
       </c>
       <c r="D15" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>505</v>
+        <v>484</v>
       </c>
       <c r="C16" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="D16" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s">
-        <v>506</v>
+        <v>485</v>
       </c>
       <c r="C17" t="s">
-        <v>507</v>
+        <v>486</v>
       </c>
       <c r="D17" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="C18" t="s">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="D18" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="B19" t="s">
-        <v>510</v>
+        <v>489</v>
       </c>
       <c r="C19" t="s">
-        <v>336</v>
+        <v>315</v>
       </c>
       <c r="D19" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="B20" t="s">
-        <v>511</v>
+        <v>490</v>
       </c>
       <c r="C20" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="D20" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -5062,27 +4988,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>512</v>
+        <v>491</v>
       </c>
       <c r="C21" t="s">
-        <v>379</v>
+        <v>358</v>
       </c>
       <c r="D21" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="B22" t="s">
-        <v>513</v>
+        <v>492</v>
       </c>
       <c r="C22" t="s">
-        <v>381</v>
+        <v>360</v>
       </c>
       <c r="D22" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5090,13 +5016,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="C23" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="D23" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5104,83 +5030,83 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>515</v>
+        <v>494</v>
       </c>
       <c r="C24" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="D24" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="B25" t="s">
-        <v>516</v>
+        <v>495</v>
       </c>
       <c r="C25" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="D25" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="B26" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="C26" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="D26" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s">
-        <v>518</v>
+        <v>497</v>
       </c>
       <c r="C27" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="D27" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="C28" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="D28" t="s">
-        <v>488</v>
+        <v>467</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="B29" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="C29" t="s">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="D29" t="s">
-        <v>490</v>
+        <v>469</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +5121,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>522</v>
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5205,490 +5131,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>523</v>
+        <v>502</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>524</v>
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>525</v>
+        <v>504</v>
       </c>
       <c r="B5" t="s">
-        <v>526</v>
+        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>527</v>
+        <v>506</v>
       </c>
       <c r="B6" t="s">
-        <v>528</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>529</v>
+        <v>508</v>
       </c>
       <c r="B7" t="s">
-        <v>530</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>531</v>
+        <v>510</v>
       </c>
       <c r="B8" t="s">
-        <v>532</v>
+        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>533</v>
+        <v>512</v>
       </c>
       <c r="B9" t="s">
-        <v>534</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>535</v>
+        <v>514</v>
       </c>
       <c r="B10" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
       <c r="B11" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="B12" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="B13" t="s">
-        <v>540</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="B14" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="B15" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="B16" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="B17" t="s">
-        <v>548</v>
+        <v>527</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="B18" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="B19" t="s">
-        <v>292</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="B20" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="B21" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="B22" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="B23" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="B24" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>558</v>
+        <v>537</v>
       </c>
       <c r="B25" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
       <c r="B26" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="B27" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="B28" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="B29" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="B30" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
       <c r="B31" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="B32" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>566</v>
+        <v>545</v>
       </c>
       <c r="B33" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>567</v>
+        <v>546</v>
       </c>
       <c r="B34" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>568</v>
+        <v>547</v>
       </c>
       <c r="B35" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>569</v>
+        <v>548</v>
       </c>
       <c r="B36" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>570</v>
+        <v>549</v>
       </c>
       <c r="B37" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>571</v>
+        <v>550</v>
       </c>
       <c r="B38" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>572</v>
+        <v>551</v>
       </c>
       <c r="B39" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>573</v>
+        <v>552</v>
       </c>
       <c r="B40" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>574</v>
+        <v>553</v>
       </c>
       <c r="B41" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="B42" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>576</v>
+        <v>555</v>
       </c>
       <c r="B43" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="B44" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>578</v>
+        <v>557</v>
       </c>
       <c r="B45" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="B46" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>580</v>
+        <v>559</v>
       </c>
       <c r="B47" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>581</v>
+        <v>560</v>
       </c>
       <c r="B48" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>582</v>
+        <v>561</v>
       </c>
       <c r="B49" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>583</v>
+        <v>562</v>
       </c>
       <c r="B50" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>584</v>
+        <v>563</v>
       </c>
       <c r="B51" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="B52" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>586</v>
+        <v>565</v>
       </c>
       <c r="B53" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>587</v>
+        <v>566</v>
       </c>
       <c r="B54" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>588</v>
+        <v>567</v>
       </c>
       <c r="B55" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
       <c r="B56" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>590</v>
+        <v>569</v>
       </c>
       <c r="B57" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>591</v>
+        <v>570</v>
       </c>
       <c r="B58" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>592</v>
+        <v>571</v>
       </c>
       <c r="B59" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="B60" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>594</v>
+        <v>573</v>
       </c>
       <c r="B61" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="B62" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="B63" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="B64" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -5703,458 +5629,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>598</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>348</v>
+        <v>327</v>
       </c>
       <c r="B5" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="C5" t="s">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="D5" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E5" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F5" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="G5" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H5" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="I5" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="J5" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K5" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>278</v>
+        <v>257</v>
       </c>
       <c r="B6" t="s">
-        <v>619</v>
+        <v>598</v>
       </c>
       <c r="C6" t="s">
-        <v>620</v>
+        <v>599</v>
       </c>
       <c r="D6" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E6" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F6" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="G6" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H6" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="I6" t="s">
-        <v>621</v>
+        <v>600</v>
       </c>
       <c r="J6" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K6" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="B7" t="s">
-        <v>622</v>
+        <v>601</v>
       </c>
       <c r="C7" t="s">
-        <v>623</v>
+        <v>602</v>
       </c>
       <c r="D7" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E7" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F7" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="G7" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H7" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="I7" t="s">
-        <v>624</v>
+        <v>603</v>
       </c>
       <c r="J7" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K7" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>479</v>
+        <v>458</v>
       </c>
       <c r="B8" t="s">
-        <v>625</v>
+        <v>604</v>
       </c>
       <c r="C8" t="s">
-        <v>626</v>
+        <v>605</v>
       </c>
       <c r="D8" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E8" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F8" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="G8" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H8" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="I8" t="s">
-        <v>627</v>
+        <v>606</v>
       </c>
       <c r="J8" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K8" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>357</v>
+        <v>336</v>
       </c>
       <c r="B9" t="s">
-        <v>628</v>
+        <v>607</v>
       </c>
       <c r="C9" t="s">
-        <v>629</v>
+        <v>608</v>
       </c>
       <c r="D9" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E9" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F9" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="G9" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H9" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="I9" t="s">
-        <v>630</v>
+        <v>609</v>
       </c>
       <c r="J9" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K9" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="B10" t="s">
-        <v>631</v>
+        <v>610</v>
       </c>
       <c r="C10" t="s">
-        <v>632</v>
+        <v>611</v>
       </c>
       <c r="D10" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E10" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F10" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="G10" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H10" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="I10" t="s">
-        <v>633</v>
+        <v>612</v>
       </c>
       <c r="J10" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K10" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>478</v>
+        <v>457</v>
       </c>
       <c r="B11" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="C11" t="s">
-        <v>635</v>
+        <v>614</v>
       </c>
       <c r="D11" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E11" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F11" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="G11" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H11" t="s">
+        <v>594</v>
+      </c>
+      <c r="I11" t="s">
         <v>615</v>
       </c>
-      <c r="I11" t="s">
-        <v>636</v>
-      </c>
       <c r="J11" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K11" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="B12" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="C12" t="s">
-        <v>637</v>
+        <v>616</v>
       </c>
       <c r="D12" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E12" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F12" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="G12" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H12" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="J12" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K12" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
       <c r="B13" t="s">
-        <v>638</v>
+        <v>617</v>
       </c>
       <c r="C13" t="s">
-        <v>639</v>
+        <v>618</v>
       </c>
       <c r="D13" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E13" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F13" t="s">
-        <v>640</v>
+        <v>619</v>
       </c>
       <c r="G13" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H13" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="I13" t="s">
-        <v>641</v>
+        <v>620</v>
       </c>
       <c r="J13" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K13" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>365</v>
+        <v>344</v>
       </c>
       <c r="B14" t="s">
-        <v>642</v>
+        <v>621</v>
       </c>
       <c r="C14" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="D14" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E14" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F14" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="G14" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="H14" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="J14" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K14" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="B15" t="s">
-        <v>644</v>
+        <v>623</v>
       </c>
       <c r="C15" t="s">
-        <v>645</v>
+        <v>624</v>
       </c>
       <c r="D15" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="E15" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="F15" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="G15" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="H15" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="J15" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K15" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="B16" t="s">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="C16" t="s">
-        <v>647</v>
+        <v>626</v>
       </c>
       <c r="D16" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="E16" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="F16" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="G16" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="H16" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="I16" t="s">
-        <v>648</v>
+        <v>627</v>
       </c>
       <c r="J16" t="s">
-        <v>617</v>
+        <v>596</v>
       </c>
       <c r="K16" t="s">
-        <v>618</v>
+        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -6169,22 +6095,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>649</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -6224,22 +6150,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>653</v>
+        <v>632</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>650</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>651</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>652</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -6254,44 +6180,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>657</v>
+        <v>636</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -6306,44 +6232,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>473</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>476</v>
+        <v>455</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>657</v>
+        <v>636</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>658</v>
+        <v>637</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -6358,92 +6284,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>662</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>663</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>665</v>
+        <v>644</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>668</v>
+        <v>647</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6453,22 +6379,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>669</v>
+        <v>648</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>670</v>
+        <v>649</v>
       </c>
     </row>
   </sheetData>
@@ -6483,7 +6409,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>671</v>
+        <v>650</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6498,87 +6424,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>673</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>674</v>
+        <v>653</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>675</v>
+        <v>654</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>676</v>
+        <v>655</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>677</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>678</v>
+        <v>657</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>679</v>
+        <v>658</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>680</v>
+        <v>659</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>681</v>
+        <v>660</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>682</v>
+        <v>661</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>683</v>
+        <v>662</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>684</v>
+        <v>663</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>685</v>
+        <v>664</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>686</v>
+        <v>665</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>687</v>
+        <v>666</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>688</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -6643,7 +6569,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A77"/>
+  <dimension ref="A1:A72"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6939,31 +6865,6 @@
     <row r="72" spans="1:1">
       <c r="A72" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -6973,12 +6874,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6988,32 +6889,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -7023,12 +6899,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7038,32 +6914,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -7073,12 +6924,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7088,22 +6939,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -7113,27 +6964,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -7143,17 +6994,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -7163,62 +7014,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -7228,7 +7079,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -7238,12 +7089,12 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -7253,7 +7104,7 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -7263,42 +7114,42 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -7308,22 +7159,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -7333,12 +7184,12 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -7348,42 +7199,17 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="667">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -301,13 +301,10 @@
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>Floating pin XSERDESdftYesNo.tdo(tdo_noconn)</t>
+    <t>No Floating Output Nets found.</t>
   </si>
   <si>
     <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>tdo_noconn - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdo", "io": "output", "bus": "", "type": "component"}</t>
   </si>
   <si>
     <t>No Connects - Inputs</t>
@@ -2425,7 +2422,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2445,7 +2442,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2460,7 +2457,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -2475,17 +2472,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -2500,12 +2497,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2520,17 +2517,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -2545,12 +2542,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2565,7 +2562,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2585,127 +2582,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2720,7 +2717,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2740,17 +2737,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2975,32 +2972,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -3010,37 +3007,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3050,62 +3047,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -3115,17 +3112,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -3135,57 +3132,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -3200,17 +3197,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -3225,52 +3222,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -3285,81 +3282,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B5" t="s">
         <v>215</v>
-      </c>
-      <c r="B5" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" t="s">
         <v>217</v>
-      </c>
-      <c r="B6" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B9" t="s">
         <v>221</v>
-      </c>
-      <c r="B9" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B10" t="s">
         <v>223</v>
-      </c>
-      <c r="B10" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3367,1268 +3364,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
+        <v>239</v>
+      </c>
+      <c r="B29" t="s">
         <v>240</v>
-      </c>
-      <c r="B29" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B31" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
+        <v>243</v>
+      </c>
+      <c r="B32" t="s">
         <v>244</v>
-      </c>
-      <c r="B32" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
+        <v>245</v>
+      </c>
+      <c r="B33" t="s">
         <v>246</v>
-      </c>
-      <c r="B33" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
+        <v>247</v>
+      </c>
+      <c r="B34" t="s">
         <v>248</v>
-      </c>
-      <c r="B34" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
+        <v>249</v>
+      </c>
+      <c r="B35" t="s">
         <v>250</v>
-      </c>
-      <c r="B35" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
+        <v>251</v>
+      </c>
+      <c r="B36" t="s">
         <v>252</v>
-      </c>
-      <c r="B36" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B38" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
+        <v>255</v>
+      </c>
+      <c r="B39" t="s">
         <v>256</v>
-      </c>
-      <c r="B39" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B40" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B42" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
+        <v>260</v>
+      </c>
+      <c r="B43" t="s">
         <v>261</v>
-      </c>
-      <c r="B43" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
+        <v>263</v>
+      </c>
+      <c r="B46" t="s">
         <v>264</v>
-      </c>
-      <c r="B46" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B47" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B48" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B49" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B50" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
+        <v>269</v>
+      </c>
+      <c r="B51" t="s">
         <v>270</v>
-      </c>
-      <c r="B51" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B52" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
+        <v>273</v>
+      </c>
+      <c r="B55" t="s">
         <v>274</v>
-      </c>
-      <c r="B55" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
+        <v>275</v>
+      </c>
+      <c r="B56" t="s">
         <v>276</v>
-      </c>
-      <c r="B56" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
+        <v>283</v>
+      </c>
+      <c r="B64" t="s">
         <v>284</v>
-      </c>
-      <c r="B64" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
+        <v>287</v>
+      </c>
+      <c r="B67" t="s">
         <v>288</v>
-      </c>
-      <c r="B67" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
+        <v>289</v>
+      </c>
+      <c r="B68" t="s">
         <v>290</v>
-      </c>
-      <c r="B68" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B69" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B70" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B79" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
+        <v>301</v>
+      </c>
+      <c r="B80" t="s">
         <v>302</v>
-      </c>
-      <c r="B80" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
+        <v>303</v>
+      </c>
+      <c r="B81" t="s">
         <v>304</v>
-      </c>
-      <c r="B81" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B82" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B83" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B84" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B85" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B86" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B87" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B88" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B89" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
+        <v>313</v>
+      </c>
+      <c r="B90" t="s">
         <v>314</v>
-      </c>
-      <c r="B90" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B91" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B92" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B93" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B94" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B95" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B96" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B97" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B98" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B99" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B100" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
+        <v>325</v>
+      </c>
+      <c r="B101" t="s">
         <v>326</v>
-      </c>
-      <c r="B101" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B103" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
+        <v>330</v>
+      </c>
+      <c r="B106" t="s">
         <v>331</v>
-      </c>
-      <c r="B106" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
+        <v>332</v>
+      </c>
+      <c r="B107" t="s">
         <v>333</v>
-      </c>
-      <c r="B107" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
+        <v>334</v>
+      </c>
+      <c r="B108" t="s">
         <v>335</v>
-      </c>
-      <c r="B108" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>336</v>
+      </c>
+      <c r="B109" t="s">
         <v>337</v>
-      </c>
-      <c r="B109" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>338</v>
+      </c>
+      <c r="B110" t="s">
         <v>339</v>
-      </c>
-      <c r="B110" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
+        <v>340</v>
+      </c>
+      <c r="B111" t="s">
         <v>341</v>
-      </c>
-      <c r="B111" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
+        <v>342</v>
+      </c>
+      <c r="B112" t="s">
         <v>343</v>
-      </c>
-      <c r="B112" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
+        <v>344</v>
+      </c>
+      <c r="B113" t="s">
         <v>345</v>
-      </c>
-      <c r="B113" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B116" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>348</v>
+      </c>
+      <c r="B117" t="s">
         <v>349</v>
-      </c>
-      <c r="B117" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>350</v>
+      </c>
+      <c r="B118" t="s">
         <v>351</v>
-      </c>
-      <c r="B118" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>352</v>
+      </c>
+      <c r="B119" t="s">
         <v>353</v>
-      </c>
-      <c r="B119" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>354</v>
+      </c>
+      <c r="B120" t="s">
         <v>355</v>
-      </c>
-      <c r="B120" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
+        <v>356</v>
+      </c>
+      <c r="B121" t="s">
         <v>357</v>
-      </c>
-      <c r="B121" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
+        <v>358</v>
+      </c>
+      <c r="B122" t="s">
         <v>359</v>
-      </c>
-      <c r="B122" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B123" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B124" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B125" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
+        <v>363</v>
+      </c>
+      <c r="B126" t="s">
         <v>364</v>
-      </c>
-      <c r="B126" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>365</v>
+      </c>
+      <c r="B127" t="s">
         <v>366</v>
-      </c>
-      <c r="B127" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>367</v>
+      </c>
+      <c r="B128" t="s">
         <v>368</v>
-      </c>
-      <c r="B128" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>369</v>
+      </c>
+      <c r="B129" t="s">
         <v>370</v>
-      </c>
-      <c r="B129" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
+        <v>371</v>
+      </c>
+      <c r="B130" t="s">
         <v>372</v>
-      </c>
-      <c r="B130" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B131" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B132" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B133" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B134" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B135" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>378</v>
+      </c>
+      <c r="B136" t="s">
         <v>379</v>
-      </c>
-      <c r="B136" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
+        <v>380</v>
+      </c>
+      <c r="B137" t="s">
         <v>381</v>
-      </c>
-      <c r="B137" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>382</v>
+      </c>
+      <c r="B138" t="s">
         <v>383</v>
-      </c>
-      <c r="B138" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>384</v>
+      </c>
+      <c r="B139" t="s">
         <v>385</v>
-      </c>
-      <c r="B139" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
+        <v>386</v>
+      </c>
+      <c r="B140" t="s">
         <v>387</v>
-      </c>
-      <c r="B140" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B141" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B142" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B143" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B144" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B145" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B146" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B147" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B148" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>396</v>
+      </c>
+      <c r="B149" t="s">
         <v>397</v>
-      </c>
-      <c r="B149" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>398</v>
+      </c>
+      <c r="B150" t="s">
         <v>399</v>
-      </c>
-      <c r="B150" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>400</v>
+      </c>
+      <c r="B151" t="s">
         <v>401</v>
-      </c>
-      <c r="B151" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
+        <v>402</v>
+      </c>
+      <c r="B152" t="s">
         <v>403</v>
-      </c>
-      <c r="B152" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
+        <v>404</v>
+      </c>
+      <c r="B153" t="s">
         <v>405</v>
-      </c>
-      <c r="B153" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>406</v>
+      </c>
+      <c r="B154" t="s">
         <v>407</v>
-      </c>
-      <c r="B154" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>408</v>
+      </c>
+      <c r="B155" t="s">
         <v>409</v>
-      </c>
-      <c r="B155" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>410</v>
+      </c>
+      <c r="B156" t="s">
         <v>411</v>
-      </c>
-      <c r="B156" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>412</v>
+      </c>
+      <c r="B157" t="s">
         <v>413</v>
-      </c>
-      <c r="B157" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>414</v>
+      </c>
+      <c r="B158" t="s">
         <v>415</v>
-      </c>
-      <c r="B158" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
+        <v>416</v>
+      </c>
+      <c r="B159" t="s">
         <v>417</v>
-      </c>
-      <c r="B159" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
+        <v>418</v>
+      </c>
+      <c r="B160" t="s">
         <v>419</v>
-      </c>
-      <c r="B160" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>420</v>
+      </c>
+      <c r="B161" t="s">
         <v>421</v>
-      </c>
-      <c r="B161" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>422</v>
+      </c>
+      <c r="B162" t="s">
         <v>423</v>
-      </c>
-      <c r="B162" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>424</v>
+      </c>
+      <c r="B163" t="s">
         <v>425</v>
-      </c>
-      <c r="B163" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>426</v>
+      </c>
+      <c r="B164" t="s">
         <v>427</v>
-      </c>
-      <c r="B164" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>428</v>
+      </c>
+      <c r="B165" t="s">
         <v>429</v>
-      </c>
-      <c r="B165" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B166" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B167" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B168" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B169" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>434</v>
+      </c>
+      <c r="B170" t="s">
         <v>435</v>
-      </c>
-      <c r="B170" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
+        <v>436</v>
+      </c>
+      <c r="B171" t="s">
         <v>437</v>
-      </c>
-      <c r="B171" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>438</v>
+      </c>
+      <c r="B172" t="s">
         <v>439</v>
-      </c>
-      <c r="B172" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
+        <v>440</v>
+      </c>
+      <c r="B173" t="s">
         <v>441</v>
-      </c>
-      <c r="B173" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B174" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B175" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B176" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B177" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B178" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
+        <v>447</v>
+      </c>
+      <c r="B179" t="s">
         <v>448</v>
-      </c>
-      <c r="B179" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B180" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -4643,47 +4640,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>458</v>
-      </c>
       <c r="I4" s="1" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4691,15 +4688,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>460</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4707,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
   </sheetData>
@@ -4722,7 +4719,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -4737,68 +4734,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>454</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B5" t="s">
+        <v>465</v>
+      </c>
+      <c r="C5" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" t="s">
         <v>466</v>
-      </c>
-      <c r="C5" t="s">
-        <v>386</v>
-      </c>
-      <c r="D5" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D6" t="s">
         <v>468</v>
-      </c>
-      <c r="C6" t="s">
-        <v>388</v>
-      </c>
-      <c r="D6" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" t="s">
         <v>470</v>
-      </c>
-      <c r="C7" t="s">
-        <v>245</v>
-      </c>
-      <c r="D7" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4806,13 +4803,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C8" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4820,55 +4817,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
+        <v>472</v>
+      </c>
+      <c r="C9" t="s">
         <v>473</v>
       </c>
-      <c r="C9" t="s">
-        <v>474</v>
-      </c>
       <c r="D9" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C10" t="s">
         <v>475</v>
       </c>
-      <c r="C10" t="s">
-        <v>476</v>
-      </c>
       <c r="D10" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
+        <v>476</v>
+      </c>
+      <c r="C11" t="s">
         <v>477</v>
       </c>
-      <c r="C11" t="s">
-        <v>478</v>
-      </c>
       <c r="D11" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="D12" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4876,111 +4873,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D13" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C14" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D14" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B15" t="s">
+        <v>481</v>
+      </c>
+      <c r="C15" t="s">
         <v>482</v>
       </c>
-      <c r="C15" t="s">
-        <v>483</v>
-      </c>
       <c r="D15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C16" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D16" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B17" t="s">
+        <v>484</v>
+      </c>
+      <c r="C17" t="s">
         <v>485</v>
       </c>
-      <c r="C17" t="s">
-        <v>486</v>
-      </c>
       <c r="D17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
+        <v>486</v>
+      </c>
+      <c r="C18" t="s">
         <v>487</v>
       </c>
-      <c r="C18" t="s">
-        <v>488</v>
-      </c>
       <c r="D18" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D19" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B20" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C20" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D20" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4988,27 +4985,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C21" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D21" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B22" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C22" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D22" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5016,13 +5013,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D23" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5030,83 +5027,83 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C24" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D24" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B25" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C25" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D25" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C26" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D26" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B27" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C27" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D27" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B28" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C28" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D28" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B29" t="s">
+        <v>498</v>
+      </c>
+      <c r="C29" t="s">
         <v>499</v>
       </c>
-      <c r="C29" t="s">
-        <v>500</v>
-      </c>
       <c r="D29" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -5121,7 +5118,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5131,490 +5128,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>502</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>503</v>
+      </c>
+      <c r="B5" t="s">
         <v>504</v>
-      </c>
-      <c r="B5" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B6" t="s">
         <v>506</v>
-      </c>
-      <c r="B6" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>507</v>
+      </c>
+      <c r="B7" t="s">
         <v>508</v>
-      </c>
-      <c r="B7" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B8" t="s">
         <v>510</v>
-      </c>
-      <c r="B8" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
+        <v>511</v>
+      </c>
+      <c r="B9" t="s">
         <v>512</v>
-      </c>
-      <c r="B9" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B10" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B11" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
+        <v>515</v>
+      </c>
+      <c r="B12" t="s">
         <v>516</v>
-      </c>
-      <c r="B12" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
+        <v>517</v>
+      </c>
+      <c r="B13" t="s">
         <v>518</v>
-      </c>
-      <c r="B13" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
+        <v>519</v>
+      </c>
+      <c r="B14" t="s">
         <v>520</v>
-      </c>
-      <c r="B14" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
+        <v>521</v>
+      </c>
+      <c r="B15" t="s">
         <v>522</v>
-      </c>
-      <c r="B15" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
+        <v>523</v>
+      </c>
+      <c r="B16" t="s">
         <v>524</v>
-      </c>
-      <c r="B16" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
+        <v>525</v>
+      </c>
+      <c r="B17" t="s">
         <v>526</v>
-      </c>
-      <c r="B17" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B18" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
+        <v>529</v>
+      </c>
+      <c r="B20" t="s">
         <v>530</v>
-      </c>
-      <c r="B20" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B21" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
+        <v>532</v>
+      </c>
+      <c r="B22" t="s">
         <v>533</v>
-      </c>
-      <c r="B22" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B23" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B24" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B25" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B26" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B27" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B28" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B29" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B30" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B31" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B32" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B33" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B34" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B35" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B36" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B37" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B38" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B40" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B41" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B42" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B43" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B45" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B46" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B47" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B49" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B50" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B51" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B52" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B53" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B54" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B55" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B56" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B57" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B58" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B59" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B60" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B61" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B62" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B63" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B64" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
   </sheetData>
@@ -5629,458 +5626,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>584</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="K4" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B5" t="s">
+        <v>589</v>
+      </c>
+      <c r="C5" t="s">
         <v>590</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>290</v>
+      </c>
+      <c r="E5" t="s">
         <v>591</v>
       </c>
-      <c r="D5" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>592</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>591</v>
+      </c>
+      <c r="H5" t="s">
         <v>593</v>
       </c>
-      <c r="G5" t="s">
-        <v>592</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>594</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>595</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>596</v>
-      </c>
-      <c r="K5" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B6" t="s">
+        <v>597</v>
+      </c>
+      <c r="C6" t="s">
         <v>598</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>290</v>
+      </c>
+      <c r="E6" t="s">
+        <v>591</v>
+      </c>
+      <c r="F6" t="s">
+        <v>592</v>
+      </c>
+      <c r="G6" t="s">
+        <v>591</v>
+      </c>
+      <c r="H6" t="s">
+        <v>593</v>
+      </c>
+      <c r="I6" t="s">
         <v>599</v>
       </c>
-      <c r="D6" t="s">
-        <v>291</v>
-      </c>
-      <c r="E6" t="s">
-        <v>592</v>
-      </c>
-      <c r="F6" t="s">
-        <v>593</v>
-      </c>
-      <c r="G6" t="s">
-        <v>592</v>
-      </c>
-      <c r="H6" t="s">
-        <v>594</v>
-      </c>
-      <c r="I6" t="s">
-        <v>600</v>
-      </c>
       <c r="J6" t="s">
+        <v>595</v>
+      </c>
+      <c r="K6" t="s">
         <v>596</v>
-      </c>
-      <c r="K6" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B7" t="s">
+        <v>600</v>
+      </c>
+      <c r="C7" t="s">
         <v>601</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E7" t="s">
+        <v>591</v>
+      </c>
+      <c r="F7" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" t="s">
+        <v>591</v>
+      </c>
+      <c r="H7" t="s">
+        <v>593</v>
+      </c>
+      <c r="I7" t="s">
         <v>602</v>
       </c>
-      <c r="D7" t="s">
-        <v>291</v>
-      </c>
-      <c r="E7" t="s">
-        <v>592</v>
-      </c>
-      <c r="F7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G7" t="s">
-        <v>592</v>
-      </c>
-      <c r="H7" t="s">
-        <v>594</v>
-      </c>
-      <c r="I7" t="s">
-        <v>603</v>
-      </c>
       <c r="J7" t="s">
+        <v>595</v>
+      </c>
+      <c r="K7" t="s">
         <v>596</v>
-      </c>
-      <c r="K7" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B8" t="s">
+        <v>603</v>
+      </c>
+      <c r="C8" t="s">
         <v>604</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>290</v>
+      </c>
+      <c r="E8" t="s">
+        <v>591</v>
+      </c>
+      <c r="F8" t="s">
+        <v>248</v>
+      </c>
+      <c r="G8" t="s">
+        <v>591</v>
+      </c>
+      <c r="H8" t="s">
+        <v>593</v>
+      </c>
+      <c r="I8" t="s">
         <v>605</v>
       </c>
-      <c r="D8" t="s">
-        <v>291</v>
-      </c>
-      <c r="E8" t="s">
-        <v>592</v>
-      </c>
-      <c r="F8" t="s">
-        <v>249</v>
-      </c>
-      <c r="G8" t="s">
-        <v>592</v>
-      </c>
-      <c r="H8" t="s">
-        <v>594</v>
-      </c>
-      <c r="I8" t="s">
-        <v>606</v>
-      </c>
       <c r="J8" t="s">
+        <v>595</v>
+      </c>
+      <c r="K8" t="s">
         <v>596</v>
-      </c>
-      <c r="K8" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B9" t="s">
+        <v>606</v>
+      </c>
+      <c r="C9" t="s">
         <v>607</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>290</v>
+      </c>
+      <c r="E9" t="s">
+        <v>591</v>
+      </c>
+      <c r="F9" t="s">
+        <v>248</v>
+      </c>
+      <c r="G9" t="s">
+        <v>591</v>
+      </c>
+      <c r="H9" t="s">
+        <v>593</v>
+      </c>
+      <c r="I9" t="s">
         <v>608</v>
       </c>
-      <c r="D9" t="s">
-        <v>291</v>
-      </c>
-      <c r="E9" t="s">
-        <v>592</v>
-      </c>
-      <c r="F9" t="s">
-        <v>249</v>
-      </c>
-      <c r="G9" t="s">
-        <v>592</v>
-      </c>
-      <c r="H9" t="s">
-        <v>594</v>
-      </c>
-      <c r="I9" t="s">
-        <v>609</v>
-      </c>
       <c r="J9" t="s">
+        <v>595</v>
+      </c>
+      <c r="K9" t="s">
         <v>596</v>
-      </c>
-      <c r="K9" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B10" t="s">
+        <v>609</v>
+      </c>
+      <c r="C10" t="s">
         <v>610</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>290</v>
+      </c>
+      <c r="E10" t="s">
+        <v>591</v>
+      </c>
+      <c r="F10" t="s">
+        <v>248</v>
+      </c>
+      <c r="G10" t="s">
+        <v>591</v>
+      </c>
+      <c r="H10" t="s">
+        <v>593</v>
+      </c>
+      <c r="I10" t="s">
         <v>611</v>
       </c>
-      <c r="D10" t="s">
-        <v>291</v>
-      </c>
-      <c r="E10" t="s">
-        <v>592</v>
-      </c>
-      <c r="F10" t="s">
-        <v>249</v>
-      </c>
-      <c r="G10" t="s">
-        <v>592</v>
-      </c>
-      <c r="H10" t="s">
-        <v>594</v>
-      </c>
-      <c r="I10" t="s">
-        <v>612</v>
-      </c>
       <c r="J10" t="s">
+        <v>595</v>
+      </c>
+      <c r="K10" t="s">
         <v>596</v>
-      </c>
-      <c r="K10" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B11" t="s">
+        <v>612</v>
+      </c>
+      <c r="C11" t="s">
         <v>613</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>290</v>
+      </c>
+      <c r="E11" t="s">
+        <v>591</v>
+      </c>
+      <c r="F11" t="s">
+        <v>248</v>
+      </c>
+      <c r="G11" t="s">
+        <v>591</v>
+      </c>
+      <c r="H11" t="s">
+        <v>593</v>
+      </c>
+      <c r="I11" t="s">
         <v>614</v>
       </c>
-      <c r="D11" t="s">
-        <v>291</v>
-      </c>
-      <c r="E11" t="s">
-        <v>592</v>
-      </c>
-      <c r="F11" t="s">
-        <v>249</v>
-      </c>
-      <c r="G11" t="s">
-        <v>592</v>
-      </c>
-      <c r="H11" t="s">
-        <v>594</v>
-      </c>
-      <c r="I11" t="s">
-        <v>615</v>
-      </c>
       <c r="J11" t="s">
+        <v>595</v>
+      </c>
+      <c r="K11" t="s">
         <v>596</v>
-      </c>
-      <c r="K11" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C12" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="G12" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H12" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="J12" t="s">
+        <v>595</v>
+      </c>
+      <c r="K12" t="s">
         <v>596</v>
-      </c>
-      <c r="K12" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B13" t="s">
+        <v>616</v>
+      </c>
+      <c r="C13" t="s">
         <v>617</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
+        <v>290</v>
+      </c>
+      <c r="E13" t="s">
+        <v>591</v>
+      </c>
+      <c r="F13" t="s">
         <v>618</v>
       </c>
-      <c r="D13" t="s">
-        <v>291</v>
-      </c>
-      <c r="E13" t="s">
-        <v>592</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>591</v>
+      </c>
+      <c r="H13" t="s">
+        <v>593</v>
+      </c>
+      <c r="I13" t="s">
         <v>619</v>
       </c>
-      <c r="G13" t="s">
-        <v>592</v>
-      </c>
-      <c r="H13" t="s">
-        <v>594</v>
-      </c>
-      <c r="I13" t="s">
-        <v>620</v>
-      </c>
       <c r="J13" t="s">
+        <v>595</v>
+      </c>
+      <c r="K13" t="s">
         <v>596</v>
-      </c>
-      <c r="K13" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B14" t="s">
+        <v>620</v>
+      </c>
+      <c r="C14" t="s">
         <v>621</v>
       </c>
-      <c r="C14" t="s">
-        <v>622</v>
-      </c>
       <c r="D14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E14" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F14" t="s">
+        <v>595</v>
+      </c>
+      <c r="G14" t="s">
+        <v>595</v>
+      </c>
+      <c r="H14" t="s">
+        <v>593</v>
+      </c>
+      <c r="J14" t="s">
+        <v>595</v>
+      </c>
+      <c r="K14" t="s">
         <v>596</v>
-      </c>
-      <c r="G14" t="s">
-        <v>596</v>
-      </c>
-      <c r="H14" t="s">
-        <v>594</v>
-      </c>
-      <c r="J14" t="s">
-        <v>596</v>
-      </c>
-      <c r="K14" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B15" t="s">
+        <v>622</v>
+      </c>
+      <c r="C15" t="s">
         <v>623</v>
       </c>
-      <c r="C15" t="s">
-        <v>624</v>
-      </c>
       <c r="D15" t="s">
+        <v>595</v>
+      </c>
+      <c r="E15" t="s">
+        <v>595</v>
+      </c>
+      <c r="F15" t="s">
+        <v>595</v>
+      </c>
+      <c r="G15" t="s">
+        <v>595</v>
+      </c>
+      <c r="H15" t="s">
+        <v>593</v>
+      </c>
+      <c r="J15" t="s">
+        <v>595</v>
+      </c>
+      <c r="K15" t="s">
         <v>596</v>
-      </c>
-      <c r="E15" t="s">
-        <v>596</v>
-      </c>
-      <c r="F15" t="s">
-        <v>596</v>
-      </c>
-      <c r="G15" t="s">
-        <v>596</v>
-      </c>
-      <c r="H15" t="s">
-        <v>594</v>
-      </c>
-      <c r="J15" t="s">
-        <v>596</v>
-      </c>
-      <c r="K15" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B16" t="s">
+        <v>624</v>
+      </c>
+      <c r="C16" t="s">
         <v>625</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>290</v>
+      </c>
+      <c r="E16" t="s">
+        <v>591</v>
+      </c>
+      <c r="F16" t="s">
+        <v>288</v>
+      </c>
+      <c r="G16" t="s">
+        <v>591</v>
+      </c>
+      <c r="H16" t="s">
+        <v>593</v>
+      </c>
+      <c r="I16" t="s">
         <v>626</v>
       </c>
-      <c r="D16" t="s">
-        <v>291</v>
-      </c>
-      <c r="E16" t="s">
-        <v>592</v>
-      </c>
-      <c r="F16" t="s">
-        <v>289</v>
-      </c>
-      <c r="G16" t="s">
-        <v>592</v>
-      </c>
-      <c r="H16" t="s">
-        <v>594</v>
-      </c>
-      <c r="I16" t="s">
-        <v>627</v>
-      </c>
       <c r="J16" t="s">
+        <v>595</v>
+      </c>
+      <c r="K16" t="s">
         <v>596</v>
-      </c>
-      <c r="K16" t="s">
-        <v>597</v>
       </c>
     </row>
   </sheetData>
@@ -6095,22 +6092,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -6150,22 +6147,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
   </sheetData>
@@ -6180,44 +6177,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -6232,44 +6229,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>637</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="I4" s="1" t="s">
+      <c r="J4" s="1" t="s">
         <v>638</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>639</v>
       </c>
     </row>
   </sheetData>
@@ -6284,92 +6281,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6379,22 +6376,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -6409,7 +6406,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6424,87 +6421,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
   </sheetData>
@@ -6884,7 +6881,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -6899,7 +6896,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6909,12 +6906,7 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>86</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6929,7 +6921,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6939,22 +6931,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -6964,27 +6956,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -6994,17 +6986,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -7014,62 +7006,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:1">
@@ -7079,7 +7071,7 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:1">
@@ -7089,12 +7081,12 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:1">
@@ -7104,7 +7096,7 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -7114,42 +7106,42 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="1:1">
@@ -7159,22 +7151,22 @@
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:1">
@@ -7184,12 +7176,12 @@
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:1">
@@ -7199,17 +7191,17 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -2018,13 +2018,13 @@
     <t>Pad Connections to Nestos</t>
   </si>
   <si>
-    <t>pad_WALTZ_BIAS.BIAS 20V -0.3V connects to XWALTZ,XceleraCORE,XSERVICE,XMAIN,Xvbias1.IN2 20V -0.3V</t>
+    <t>pad_WALTZ_BIAS.BIAS 20V -0.3V connects to XWALTZ,XceleraCORE,XSERVICE,XMAIN,Xvbias1.IN2 20V ////////////////////////////////////////V</t>
   </si>
   <si>
     <t>pad_WALTZ_BST.BST 60V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU2.CELPOS 60V 2.2V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU17.CBOOT 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,Xfetdriver.HVPOS 60V 54.0V</t>
   </si>
   <si>
-    <t>pad_WALTZ_EN.EN 60V -0.3V connects to XWALTZ,XceleraCORE,XSERVICE,XMAIN,Xvbias1.ENABLE_VBIASHV 60V -0.3V</t>
+    <t>pad_WALTZ_EN.EN 60V -0.3V connects to XWALTZ,XceleraCORE,XSERVICE,XMAIN,Xvbias1.ENABLE_VBIASHV 60V ////////////////////////////////////////V</t>
   </si>
   <si>
     <t>pad_WALTZ_FB.sense_FB 6V -0.3V connects to XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN,XU3.INP_COMPARATOR 6V -0.3V --&gt; XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN,XU22.INN_COMPARATOR 6V -0.3V</t>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="641">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -202,36 +202,6 @@
     <t>Floating pin XU22.i0(49)</t>
   </si>
   <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(69)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(68)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(67)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(66)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew1.factory_timingskew(65)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(74)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(73)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(72)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(71)</t>
-  </si>
-  <si>
-    <t>Floating pin Xtimingskew2.factory_timingskew(70)</t>
-  </si>
-  <si>
     <t>Floating pin XU11.enable_switchb(102)</t>
   </si>
   <si>
@@ -286,18 +256,6 @@
     <t>Floating pin XMAIN8.softstart_1ms(35)</t>
   </si>
   <si>
-    <t>XWALTZ,XceleraSERDES</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDESdftYesNo.tdi_clock(tdi_clock)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2caddr(i2caddr)</t>
-  </si>
-  <si>
-    <t>Floating pin XSERDEScontrolDFT.i2cpasswd(i2cpasswd)</t>
-  </si>
-  <si>
     <t>Floating Outputs</t>
   </si>
   <si>
@@ -352,36 +310,6 @@
     <t>49 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,XU22", "instance": "XU22", "symbol": "i0", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
-    <t>69 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>68 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>67 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>66 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>65 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew1", "instance": "Xtimingskew1", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>74 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>73 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>72 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>71 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>70 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XBBM,Xtimingskew2", "instance": "Xtimingskew2", "symbol": "factory_timingskew", "io": "input", "bus": "[4:0]", "type": "component"}</t>
-  </si>
-  <si>
     <t>102 - {"path": "XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU11", "instance": "XU11", "symbol": "enable_switchb", "io": "input", "bus": "", "type": "component"}</t>
   </si>
   <si>
@@ -434,15 +362,6 @@
   </si>
   <si>
     <t>35 - {"path": "XWALTZ,XceleraCORE,XSOFTSTART,XMAIN8", "instance": "XMAIN8", "symbol": "softstart_1ms", "io": "input", "bus": "", "type": "child"}</t>
-  </si>
-  <si>
-    <t>tdi_clock - {"path": "XWALTZ,XceleraSERDES,XSERDESdftYesNo", "instance": "XSERDESdftYesNo", "symbol": "tdi_clock", "io": "input", "bus": "", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2caddr - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2caddr", "io": "input", "bus": "[1:0]", "type": "component"}</t>
-  </si>
-  <si>
-    <t>i2cpasswd - {"path": "XWALTZ,XceleraSERDES,XSERDEScontrolDFT", "instance": "XSERDEScontrolDFT", "symbol": "i2cpasswd", "io": "input", "bus": "[1:0]", "type": "component"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -560,6 +479,14 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">!!! Iverilog Error !!!
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177: warning: Port 9 (i2caddr) of SERDEScontrolDFT expects 2 bits, got 8.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177:        : Pruning 6 high bits of the expression.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177: warning: Port 10 (i2cpasswd) of SERDEScontrolDFT expects 2 bits, got 8.
+/celera/projects/Sunnyvale/software/WALTZ/verilog12/WALTZceleraSERDES.v:177:        : Pruning 6 high bits of the expression.
+</t>
+  </si>
+  <si>
     <t>DRM Efficiency</t>
   </si>
   <si>
@@ -1694,6 +1621,9 @@
     <t>amux2</t>
   </si>
   <si>
+    <t>PEBBLEtiehi</t>
+  </si>
+  <si>
     <t>wrapper</t>
   </si>
   <si>
@@ -1715,9 +1645,6 @@
     <t>capacitorfixed</t>
   </si>
   <si>
-    <t>PEBBLEtiehi</t>
-  </si>
-  <si>
     <t>voltage2current</t>
   </si>
   <si>
@@ -2018,13 +1945,13 @@
     <t>Pad Connections to Nestos</t>
   </si>
   <si>
-    <t>pad_WALTZ_BIAS.BIAS 20V -0.3V connects to XWALTZ,XceleraCORE,XSERVICE,XMAIN,Xvbias1.IN2 20V ////////////////////////////////////////V</t>
+    <t>pad_WALTZ_BIAS.BIAS 20V -0.3V connects to XWALTZ,XceleraCORE,XSERVICE,XMAIN,Xvbias1.IN2 20V -0.3V</t>
   </si>
   <si>
     <t>pad_WALTZ_BST.BST 60V -0.3V connects to XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU2.CELPOS 60V 2.2V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,XU17.CBOOT 60V -0.3V --&gt; XWALTZ,XceleraCORE,XDRIVER,XTOPSW,Xfetdriver.HVPOS 60V 54.0V</t>
   </si>
   <si>
-    <t>pad_WALTZ_EN.EN 60V -0.3V connects to XWALTZ,XceleraCORE,XSERVICE,XMAIN,Xvbias1.ENABLE_VBIASHV 60V ////////////////////////////////////////V</t>
+    <t>pad_WALTZ_EN.EN 60V -0.3V connects to XWALTZ,XceleraCORE,XSERVICE,XMAIN,Xvbias1.ENABLE_VBIASHV 60V -0.3V</t>
   </si>
   <si>
     <t>pad_WALTZ_FB.sense_FB 6V -0.3V connects to XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN,XU3.INP_COMPARATOR 6V -0.3V --&gt; XWALTZ,XceleraCORE,XPOWERGOOD,XMAIN,XU22.INN_COMPARATOR 6V -0.3V</t>
@@ -2422,7 +2349,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2442,7 +2369,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2457,7 +2384,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -2472,17 +2399,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>137</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -2497,12 +2424,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2517,17 +2444,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>141</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2542,12 +2469,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -2562,7 +2489,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2577,132 +2504,137 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>145</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>150</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>151</v>
+        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>152</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>153</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>168</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2717,7 +2649,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2737,17 +2669,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>172</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2972,32 +2904,32 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:1">
@@ -3007,37 +2939,37 @@
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3047,62 +2979,62 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -3112,17 +3044,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -3132,57 +3064,57 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>175</v>
+        <v>149</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -3197,17 +3129,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>171</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -3222,52 +3154,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>204</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>205</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>207</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>208</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3282,81 +3214,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>214</v>
+        <v>188</v>
       </c>
       <c r="B5" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>219</v>
+        <v>193</v>
       </c>
       <c r="B8" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>220</v>
+        <v>194</v>
       </c>
       <c r="B9" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="B10" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>224</v>
+        <v>198</v>
       </c>
       <c r="B11" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>225</v>
+        <v>199</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3364,1268 +3296,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>227</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>228</v>
+        <v>202</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>230</v>
+        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>231</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>232</v>
+        <v>206</v>
       </c>
       <c r="B20" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>233</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>234</v>
+        <v>208</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>236</v>
+        <v>210</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>237</v>
+        <v>211</v>
       </c>
       <c r="B27" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>238</v>
+        <v>212</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>239</v>
+        <v>213</v>
       </c>
       <c r="B29" t="s">
-        <v>240</v>
+        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>241</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="B31" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="B32" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>245</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s">
-        <v>246</v>
+        <v>220</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>247</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>249</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s">
-        <v>250</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>251</v>
+        <v>225</v>
       </c>
       <c r="B36" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>254</v>
+        <v>228</v>
       </c>
       <c r="B38" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>257</v>
+        <v>231</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>258</v>
+        <v>232</v>
       </c>
       <c r="B41" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>259</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>260</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>262</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
       <c r="B46" t="s">
-        <v>264</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>265</v>
+        <v>239</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>266</v>
+        <v>240</v>
       </c>
       <c r="B48" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="B49" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>268</v>
+        <v>242</v>
       </c>
       <c r="B50" t="s">
-        <v>215</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>269</v>
+        <v>243</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>272</v>
+        <v>246</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>273</v>
+        <v>247</v>
       </c>
       <c r="B55" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>275</v>
+        <v>249</v>
       </c>
       <c r="B56" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>278</v>
+        <v>252</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>279</v>
+        <v>253</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>280</v>
+        <v>254</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>281</v>
+        <v>255</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="B64" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>286</v>
+        <v>260</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>287</v>
+        <v>261</v>
       </c>
       <c r="B67" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>289</v>
+        <v>263</v>
       </c>
       <c r="B68" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>291</v>
+        <v>265</v>
       </c>
       <c r="B69" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="B70" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>297</v>
+        <v>271</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="B77" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="B78" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="B79" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c r="B80" t="s">
-        <v>302</v>
+        <v>276</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>303</v>
+        <v>277</v>
       </c>
       <c r="B81" t="s">
-        <v>304</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="B82" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="B83" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="B84" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>308</v>
+        <v>282</v>
       </c>
       <c r="B85" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>309</v>
+        <v>283</v>
       </c>
       <c r="B86" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>310</v>
+        <v>284</v>
       </c>
       <c r="B87" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="B88" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="B89" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="B90" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>315</v>
+        <v>289</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>316</v>
+        <v>290</v>
       </c>
       <c r="B92" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>317</v>
+        <v>291</v>
       </c>
       <c r="B93" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>318</v>
+        <v>292</v>
       </c>
       <c r="B94" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>319</v>
+        <v>293</v>
       </c>
       <c r="B95" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>320</v>
+        <v>294</v>
       </c>
       <c r="B96" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>321</v>
+        <v>295</v>
       </c>
       <c r="B97" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="B98" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="B99" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="B101" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>327</v>
+        <v>301</v>
       </c>
       <c r="B102" t="s">
-        <v>217</v>
+        <v>191</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>328</v>
+        <v>302</v>
       </c>
       <c r="B103" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>329</v>
+        <v>303</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>330</v>
+        <v>304</v>
       </c>
       <c r="B106" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>332</v>
+        <v>306</v>
       </c>
       <c r="B107" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>334</v>
+        <v>308</v>
       </c>
       <c r="B108" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>336</v>
+        <v>310</v>
       </c>
       <c r="B109" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="B110" t="s">
-        <v>339</v>
+        <v>313</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="B111" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>342</v>
+        <v>316</v>
       </c>
       <c r="B112" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>344</v>
+        <v>318</v>
       </c>
       <c r="B113" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>212</v>
+        <v>186</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>213</v>
+        <v>187</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>347</v>
+        <v>321</v>
       </c>
       <c r="B116" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="B117" t="s">
-        <v>349</v>
+        <v>323</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>350</v>
+        <v>324</v>
       </c>
       <c r="B118" t="s">
-        <v>351</v>
+        <v>325</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="B119" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="B120" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="B121" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>358</v>
+        <v>332</v>
       </c>
       <c r="B122" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>360</v>
+        <v>334</v>
       </c>
       <c r="B123" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>361</v>
+        <v>335</v>
       </c>
       <c r="B124" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>362</v>
+        <v>336</v>
       </c>
       <c r="B125" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>363</v>
+        <v>337</v>
       </c>
       <c r="B126" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="B127" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="B128" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>369</v>
+        <v>343</v>
       </c>
       <c r="B129" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>371</v>
+        <v>345</v>
       </c>
       <c r="B130" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="B131" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>323</v>
+        <v>297</v>
       </c>
       <c r="B132" t="s">
-        <v>374</v>
+        <v>348</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>325</v>
+        <v>299</v>
       </c>
       <c r="B133" t="s">
-        <v>375</v>
+        <v>349</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>324</v>
+        <v>298</v>
       </c>
       <c r="B134" t="s">
-        <v>376</v>
+        <v>350</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>377</v>
+        <v>351</v>
       </c>
       <c r="B135" t="s">
-        <v>261</v>
+        <v>235</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="B136" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="B137" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="B138" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="B139" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="B140" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="B141" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="B142" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="B143" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="B144" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="B145" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="B146" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="B147" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="B148" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="B149" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="B150" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="B151" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
       <c r="B152" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="B153" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="B154" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="B155" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="B156" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="B157" t="s">
-        <v>413</v>
+        <v>387</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>414</v>
+        <v>388</v>
       </c>
       <c r="B158" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="B159" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="B160" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="B161" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="B162" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="B163" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="B164" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="B165" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="B166" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="B167" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="B168" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="B169" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="B170" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="B171" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="B172" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="B173" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="B174" t="s">
-        <v>223</v>
+        <v>197</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="B175" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="B176" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="B177" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="B178" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="B179" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="B180" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
     </row>
   </sheetData>
@@ -4640,47 +4572,47 @@
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>1</v>
@@ -4688,15 +4620,15 @@
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -4704,7 +4636,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
     </row>
   </sheetData>
@@ -4719,7 +4651,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
     </row>
   </sheetData>
@@ -4734,68 +4666,68 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="B5" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="C5" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="D5" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="C6" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="D6" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>218</v>
       </c>
       <c r="D7" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -4803,13 +4735,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="C8" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="D8" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4817,55 +4749,55 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
       <c r="C9" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="D9" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>181</v>
+        <v>155</v>
       </c>
       <c r="B10" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="C10" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="D10" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s">
-        <v>476</v>
+        <v>450</v>
       </c>
       <c r="C11" t="s">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="D11" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="B12" t="s">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="C12" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="D12" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -4873,111 +4805,111 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="C13" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="D13" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="C14" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="D14" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="B15" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="C15" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="D15" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="B16" t="s">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="C16" t="s">
-        <v>383</v>
+        <v>357</v>
       </c>
       <c r="D16" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="B17" t="s">
-        <v>484</v>
+        <v>458</v>
       </c>
       <c r="C17" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="D17" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="C18" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="D18" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="B19" t="s">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="C19" t="s">
-        <v>314</v>
+        <v>288</v>
       </c>
       <c r="D19" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="B20" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="C20" t="s">
-        <v>355</v>
+        <v>329</v>
       </c>
       <c r="D20" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4985,27 +4917,27 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="C21" t="s">
-        <v>357</v>
+        <v>331</v>
       </c>
       <c r="D21" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="B22" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="C22" t="s">
-        <v>359</v>
+        <v>333</v>
       </c>
       <c r="D22" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -5013,13 +4945,13 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="C23" t="s">
-        <v>364</v>
+        <v>338</v>
       </c>
       <c r="D23" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -5027,83 +4959,83 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="C24" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="D24" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="C25" t="s">
-        <v>368</v>
+        <v>342</v>
       </c>
       <c r="D25" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="B26" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="C26" t="s">
-        <v>370</v>
+        <v>344</v>
       </c>
       <c r="D26" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="C27" t="s">
-        <v>372</v>
+        <v>346</v>
       </c>
       <c r="D27" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="B28" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="C28" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="D28" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="B29" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="C29" t="s">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="D29" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>
@@ -5118,7 +5050,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5128,490 +5060,490 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>502</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="B5" t="s">
-        <v>504</v>
+        <v>478</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
       <c r="B6" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="B7" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="B8" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="B9" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="B10" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="B11" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="B12" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B13" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="B14" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="B15" t="s">
-        <v>522</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="B16" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="B17" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>527</v>
+        <v>501</v>
       </c>
       <c r="B18" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="B19" t="s">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="B20" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>531</v>
+        <v>505</v>
       </c>
       <c r="B21" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
       <c r="B22" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="B23" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="B24" t="s">
-        <v>248</v>
+        <v>430</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>536</v>
+        <v>510</v>
       </c>
       <c r="B25" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="B26" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>538</v>
+        <v>512</v>
       </c>
       <c r="B27" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>539</v>
+        <v>513</v>
       </c>
       <c r="B28" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
       <c r="B29" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>541</v>
+        <v>515</v>
       </c>
       <c r="B30" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>542</v>
+        <v>516</v>
       </c>
       <c r="B31" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>543</v>
+        <v>517</v>
       </c>
       <c r="B32" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>544</v>
+        <v>518</v>
       </c>
       <c r="B33" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="B34" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="B35" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
       <c r="B36" t="s">
-        <v>256</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="B37" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="B38" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>551</v>
+        <v>525</v>
       </c>
       <c r="B40" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="B41" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="B42" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="B43" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="B44" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="B45" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="B46" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="B47" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="B48" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="B49" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="B50" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="B51" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="B52" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="B53" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>565</v>
+        <v>539</v>
       </c>
       <c r="B54" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="B55" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="B56" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="B57" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="B58" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="B59" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="B60" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="B61" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="B62" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="B63" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="B64" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -5626,458 +5558,458 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>576</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>577</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>581</v>
+        <v>555</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>582</v>
+        <v>556</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>586</v>
+        <v>560</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>588</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>300</v>
       </c>
       <c r="B5" t="s">
-        <v>589</v>
+        <v>563</v>
       </c>
       <c r="C5" t="s">
-        <v>590</v>
+        <v>564</v>
       </c>
       <c r="D5" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E5" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F5" t="s">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="G5" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H5" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="I5" t="s">
-        <v>594</v>
+        <v>568</v>
       </c>
       <c r="J5" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K5" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>256</v>
+        <v>230</v>
       </c>
       <c r="B6" t="s">
-        <v>597</v>
+        <v>571</v>
       </c>
       <c r="C6" t="s">
-        <v>598</v>
+        <v>572</v>
       </c>
       <c r="D6" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E6" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F6" t="s">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="G6" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H6" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="I6" t="s">
-        <v>599</v>
+        <v>573</v>
       </c>
       <c r="J6" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K6" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>307</v>
       </c>
       <c r="B7" t="s">
-        <v>600</v>
+        <v>574</v>
       </c>
       <c r="C7" t="s">
-        <v>601</v>
+        <v>575</v>
       </c>
       <c r="D7" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E7" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F7" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="G7" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H7" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="I7" t="s">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="J7" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K7" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="B8" t="s">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="C8" t="s">
-        <v>604</v>
+        <v>578</v>
       </c>
       <c r="D8" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E8" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F8" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="G8" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H8" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="I8" t="s">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="J8" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K8" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>335</v>
+        <v>309</v>
       </c>
       <c r="B9" t="s">
-        <v>606</v>
+        <v>580</v>
       </c>
       <c r="C9" t="s">
-        <v>607</v>
+        <v>581</v>
       </c>
       <c r="D9" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E9" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F9" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="G9" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H9" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="I9" t="s">
-        <v>608</v>
+        <v>582</v>
       </c>
       <c r="J9" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K9" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>609</v>
+        <v>583</v>
       </c>
       <c r="C10" t="s">
-        <v>610</v>
+        <v>584</v>
       </c>
       <c r="D10" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F10" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="G10" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H10" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="I10" t="s">
-        <v>611</v>
+        <v>585</v>
       </c>
       <c r="J10" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K10" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="B11" t="s">
-        <v>612</v>
+        <v>586</v>
       </c>
       <c r="C11" t="s">
-        <v>613</v>
+        <v>587</v>
       </c>
       <c r="D11" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E11" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F11" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="G11" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H11" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="I11" t="s">
-        <v>614</v>
+        <v>588</v>
       </c>
       <c r="J11" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K11" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>345</v>
+        <v>319</v>
       </c>
       <c r="B12" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="C12" t="s">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="D12" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E12" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F12" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="G12" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H12" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="J12" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K12" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="B13" t="s">
-        <v>616</v>
+        <v>590</v>
       </c>
       <c r="C13" t="s">
-        <v>617</v>
+        <v>591</v>
       </c>
       <c r="D13" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E13" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F13" t="s">
-        <v>618</v>
+        <v>592</v>
       </c>
       <c r="G13" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H13" t="s">
+        <v>567</v>
+      </c>
+      <c r="I13" t="s">
         <v>593</v>
       </c>
-      <c r="I13" t="s">
-        <v>619</v>
-      </c>
       <c r="J13" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K13" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>343</v>
+        <v>317</v>
       </c>
       <c r="B14" t="s">
-        <v>620</v>
+        <v>594</v>
       </c>
       <c r="C14" t="s">
-        <v>621</v>
+        <v>595</v>
       </c>
       <c r="D14" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E14" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F14" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="G14" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="H14" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="J14" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K14" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="B15" t="s">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="C15" t="s">
-        <v>623</v>
+        <v>597</v>
       </c>
       <c r="D15" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="E15" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="F15" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="G15" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="H15" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="J15" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K15" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="B16" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="C16" t="s">
-        <v>625</v>
+        <v>599</v>
       </c>
       <c r="D16" t="s">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="E16" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="F16" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="G16" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="H16" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="I16" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="J16" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="K16" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
   </sheetData>
@@ -6092,22 +6024,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>627</v>
+        <v>601</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>629</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -6147,22 +6079,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>631</v>
+        <v>605</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>628</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>629</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>630</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -6177,44 +6109,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>632</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>633</v>
+        <v>607</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>634</v>
+        <v>608</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>638</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -6229,44 +6161,44 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>639</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>633</v>
+        <v>607</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>634</v>
+        <v>608</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>635</v>
+        <v>609</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>636</v>
+        <v>610</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>637</v>
+        <v>611</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>638</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>
@@ -6281,92 +6213,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>640</v>
+        <v>614</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>641</v>
+        <v>615</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>642</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>643</v>
+        <v>617</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>643</v>
+        <v>617</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>643</v>
+        <v>617</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>644</v>
+        <v>618</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>645</v>
+        <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>646</v>
+        <v>620</v>
       </c>
     </row>
     <row r="24" spans="1:1">
@@ -6376,22 +6308,22 @@
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>647</v>
+        <v>621</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>648</v>
+        <v>622</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>648</v>
+        <v>622</v>
       </c>
     </row>
   </sheetData>
@@ -6406,7 +6338,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>649</v>
+        <v>623</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6421,87 +6353,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>650</v>
+        <v>624</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>651</v>
+        <v>625</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>652</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>653</v>
+        <v>627</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>654</v>
+        <v>628</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>655</v>
+        <v>629</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>656</v>
+        <v>630</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>657</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>658</v>
+        <v>632</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>659</v>
+        <v>633</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>660</v>
+        <v>634</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>661</v>
+        <v>635</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>662</v>
+        <v>636</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>663</v>
+        <v>637</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>664</v>
+        <v>638</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>665</v>
+        <v>639</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>666</v>
+        <v>640</v>
       </c>
     </row>
   </sheetData>
@@ -6566,7 +6498,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A72"/>
+  <dimension ref="A1:A57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -6675,193 +6607,123 @@
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>52</v>
+      <c r="A28" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>55</v>
+      <c r="A31" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>59</v>
+      <c r="A35" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>17</v>
+      <c r="A41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="1" t="s">
-        <v>18</v>
+      <c r="A45" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" t="s">
-        <v>70</v>
+      <c r="A54" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
-      <c r="A62" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
-      <c r="A71" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
-      <c r="A72" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -6876,7 +6738,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6886,7 +6748,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -6901,7 +6763,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6916,12 +6778,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A69"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -6931,22 +6793,22 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -6956,27 +6818,27 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:1">
@@ -6986,17 +6848,17 @@
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -7006,202 +6868,132 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>102</v>
+      <c r="A25" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>105</v>
+      <c r="A28" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>109</v>
+      <c r="A32" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>17</v>
+      <c r="A38" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>18</v>
+      <c r="A42" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>120</v>
+      <c r="A51" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
-      <c r="A61" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
-      <c r="A64" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
-      <c r="A65" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/WALTZ/project/Sanity.xlsx
+++ b/WALTZ/project/Sanity.xlsx
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="840">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1427" uniqueCount="841">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>XWALTZ,XceleraSERDES</t>
+  </si>
+  <si>
+    <t>ERROR: Net a1 - Shorted inputs (XtieHi.q --&gt; XSERDEScontrolDRMautoNo.a1 --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.i2cpassword --&gt; XSERDEScontrolDRMautoNo.enable_hardware)(a1)</t>
   </si>
   <si>
     <t>ERROR: Net a0 - Shorted inputs (XtieLo.q --&gt; Xoscillator.ten --&gt; XSERDEScontrolDRMautoNo.a0 --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.pd --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.otp_id --&gt; XSERDEScontrolDRMautoNo.i2caddress --&gt; XSERDEScontrolDRMautoNo.i2caddress)(a0)</t>
@@ -2947,7 +2950,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -2962,7 +2965,7 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -2977,17 +2980,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3002,12 +3005,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3022,17 +3025,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -3047,12 +3050,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3067,7 +3070,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3087,127 +3090,127 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3222,27 +3225,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -3252,7 +3255,7 @@
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:1">
@@ -3262,7 +3265,7 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:1">
@@ -3272,17 +3275,17 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -3292,17 +3295,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="27" spans="1:1">
@@ -3312,7 +3315,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -3322,7 +3325,7 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="1:1">
@@ -3332,17 +3335,17 @@
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -3352,17 +3355,17 @@
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -3372,7 +3375,7 @@
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3387,17 +3390,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -3412,7 +3415,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3642,17 +3645,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
   </sheetData>
@@ -3667,52 +3670,52 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3727,81 +3730,81 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B5" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" t="s">
         <v>306</v>
-      </c>
-      <c r="B6" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>315</v>
+      </c>
+      <c r="B11" t="s">
         <v>314</v>
-      </c>
-      <c r="B11" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -3809,1268 +3812,1268 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B20" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B21" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B27" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B28" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B30" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B32" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B33" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B34" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B38" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B39" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B40" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B41" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B42" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B47" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B48" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B49" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B51" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B52" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B55" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B56" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B57" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B64" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B67" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B68" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B69" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B70" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B77" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B78" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B79" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B80" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B81" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B82" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B83" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B84" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B85" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B86" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B87" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B88" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B89" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B90" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B91" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B92" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B93" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B94" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B95" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B96" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B97" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B99" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B100" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B101" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B102" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B103" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B106" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B107" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B108" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B109" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B110" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B111" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B112" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B113" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="1" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="1" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B116" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B117" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B118" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B119" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B120" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B121" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B122" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B123" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B124" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B125" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B126" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B127" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B128" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B129" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B130" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B131" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B132" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B133" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B134" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B135" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B136" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B137" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B138" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B139" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B140" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B141" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B142" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B143" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B144" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B145" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B146" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B147" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B148" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B149" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B150" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B151" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B152" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B153" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B154" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B155" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B156" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B157" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B158" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B159" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B160" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B161" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B162" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B163" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B164" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B165" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B166" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B167" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B168" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B169" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B170" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B171" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B172" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B173" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B174" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B175" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B176" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B177" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B178" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B179" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B180" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
   </sheetData>
@@ -5085,7 +5088,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
@@ -5100,26 +5103,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>
@@ -5134,7 +5137,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5144,458 +5147,458 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B5" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B6" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B7" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B8" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B9" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B10" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B11" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B12" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B13" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B14" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B15" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B16" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B17" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B18" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B19" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
+        <v>580</v>
+      </c>
+      <c r="B20" t="s">
         <v>579</v>
-      </c>
-      <c r="B20" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B21" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B23" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
+        <v>586</v>
+      </c>
+      <c r="B24" t="s">
         <v>585</v>
-      </c>
-      <c r="B24" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B25" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B26" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B27" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B28" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B29" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B30" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B31" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B32" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B33" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B34" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B36" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B37" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B38" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B39" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B40" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B41" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B42" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B43" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B44" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B45" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B46" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B47" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B48" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B49" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B50" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B51" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B52" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B53" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B54" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B55" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B56" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B57" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B58" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B59" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B60" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -5610,528 +5613,528 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="D5" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F5" t="s">
+        <v>639</v>
+      </c>
+      <c r="G5" t="s">
         <v>638</v>
       </c>
-      <c r="G5" t="s">
-        <v>637</v>
-      </c>
       <c r="H5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="J5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B6" t="s">
+        <v>644</v>
+      </c>
+      <c r="C6" t="s">
+        <v>645</v>
+      </c>
+      <c r="D6" t="s">
+        <v>381</v>
+      </c>
+      <c r="E6" t="s">
+        <v>638</v>
+      </c>
+      <c r="F6" t="s">
+        <v>639</v>
+      </c>
+      <c r="G6" t="s">
+        <v>638</v>
+      </c>
+      <c r="H6" t="s">
+        <v>640</v>
+      </c>
+      <c r="I6" t="s">
+        <v>646</v>
+      </c>
+      <c r="J6" t="s">
+        <v>642</v>
+      </c>
+      <c r="K6" t="s">
         <v>643</v>
-      </c>
-      <c r="C6" t="s">
-        <v>644</v>
-      </c>
-      <c r="D6" t="s">
-        <v>380</v>
-      </c>
-      <c r="E6" t="s">
-        <v>637</v>
-      </c>
-      <c r="F6" t="s">
-        <v>638</v>
-      </c>
-      <c r="G6" t="s">
-        <v>637</v>
-      </c>
-      <c r="H6" t="s">
-        <v>639</v>
-      </c>
-      <c r="I6" t="s">
-        <v>645</v>
-      </c>
-      <c r="J6" t="s">
-        <v>641</v>
-      </c>
-      <c r="K6" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B7" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C7" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G7" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H7" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I7" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="J7" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K7" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B8" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C8" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G8" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H8" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I8" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="J8" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K8" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B9" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C9" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E9" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G9" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H9" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I9" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="J9" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K9" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B10" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C10" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="D10" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E10" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G10" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H10" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I10" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="J10" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K10" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B11" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D11" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E11" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F11" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G11" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H11" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I11" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="J11" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K11" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C12" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="D12" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F12" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G12" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H12" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J12" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K12" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B13" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C13" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="D13" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F13" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G13" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H13" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I13" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="J13" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K13" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B14" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C14" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E14" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H14" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J14" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K14" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B15" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C15" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="D15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="E15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="G15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H15" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="J15" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K15" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B16" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C16" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D16" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E16" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F16" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G16" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H16" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I16" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="J16" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K16" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B17" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C17" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D17" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E17" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F17" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G17" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H17" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I17" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="J17" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K17" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B18" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C18" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D18" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E18" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="F18" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="G18" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H18" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="I18" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="J18" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K18" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
   </sheetData>
@@ -6146,22 +6149,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -6176,22 +6179,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
   </sheetData>
@@ -6206,566 +6209,566 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B5" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C5" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F5" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G5" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="I5" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="J5" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B6" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F6" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I6" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="J6" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B7" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C7" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D7" t="s">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F7" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I7" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="J7" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B8" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C8" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D8" t="s">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F8" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I8" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J8" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B9" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C9" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F9" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="G9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I9" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J9" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B10" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C10" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E10" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F10" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G10" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="I10" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="J10" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B11" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C11" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E11" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F11" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="I11" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J11" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B12" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C12" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D12" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E12" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="F12" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J12" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B13" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C13" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D13" t="s">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F13" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I13" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="J13" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B14" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C14" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D14" t="s">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F14" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I14" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="J14" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B15" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C15" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D15" t="s">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F15" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G15" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="I15" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J15" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B16" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C16" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D16" t="s">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F16" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="G16" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I16" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J16" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B17" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C17" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D17" t="s">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F17" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="G17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I17" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="J17" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B18" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C18" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D18" t="s">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F18" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G18" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I18" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J18" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B19" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C19" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D19" t="s">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F19" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I19" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="J19" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B20" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C20" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D20" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E20" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F20" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G20" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J20" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B21" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C21" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E21" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F21" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I21" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J21" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B22" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C22" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D22" t="s">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F22" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G22" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I22" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="J22" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
   </sheetData>
@@ -6805,624 +6808,624 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C5" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D5" t="s">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G5" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I5" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J5" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B6" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D6" t="s">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F6" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="G6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I6" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J6" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B7" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F7" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I7" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J7" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B8" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C8" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D8" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E8" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F8" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="G8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I8" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="J8" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B9" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C9" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D9" t="s">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F9" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I9" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J9" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B10" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C10" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D10" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E10" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F10" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I10" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J10" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B11" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C11" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E11" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F11" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G11" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I11" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="J11" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C12" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D12" t="s">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F12" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G12" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I12" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J12" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B13" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C13" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D13" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E13" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="F13" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="G13" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I13" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="J13" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B14" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C14" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D14" t="s">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F14" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="G14" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I14" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="J14" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B15" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="C15" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F15" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I15" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J15" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B16" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C16" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D16" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E16" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F16" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G16" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I16" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J16" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B17" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D17" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E17" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F17" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I17" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J17" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B18" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C18" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D18" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E18" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F18" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G18" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I18" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J18" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B19" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E19" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F19" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I19" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="J19" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B20" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C20" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D20" t="s">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F20" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="G20" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I20" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J20" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B21" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C21" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D21" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E21" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F21" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G21" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I21" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J21" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B22" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C22" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D22" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E22" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F22" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G22" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I22" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J22" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B23" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C23" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D23" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E23" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F23" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G23" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I23" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J23" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B24" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C24" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="D24" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E24" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F24" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="G24" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I24" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="J24" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -7437,22 +7440,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -7467,22 +7470,22 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -7497,7 +7500,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
   </sheetData>
@@ -7512,12 +7515,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -7527,12 +7530,12 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -7547,7 +7550,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
   </sheetData>
@@ -7562,7 +7565,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
   </sheetData>
@@ -7577,12 +7580,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="4" spans="1:1">
@@ -7592,7 +7595,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
   </sheetData>
@@ -7607,12 +7610,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -7627,12 +7630,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -7642,7 +7645,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -7658,6 +7661,11 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -7672,7 +7680,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7687,87 +7695,87 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
   </sheetData>
@@ -7782,7 +7790,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -7792,17 +7800,17 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -7817,17 +7825,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -7842,202 +7850,202 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -8047,97 +8055,97 @@
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -8152,92 +8160,92 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:1">
@@ -8247,77 +8255,77 @@
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:1">
@@ -8327,27 +8335,27 @@
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -8357,82 +8365,82 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:1">
@@ -8442,92 +8450,92 @@
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:1">
@@ -8537,82 +8545,82 @@
     </row>
     <row r="91" spans="1:1">
       <c r="A91" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="109" spans="1:1">
@@ -8622,102 +8630,102 @@
     </row>
     <row r="111" spans="1:1">
       <c r="A111" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="115" spans="1:1">
       <c r="A115" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="116" spans="1:1">
       <c r="A116" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:1">
       <c r="A122" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="123" spans="1:1">
       <c r="A123" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="132" spans="1:1">
@@ -8727,182 +8735,182 @@
     </row>
     <row r="134" spans="1:1">
       <c r="A134" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="135" spans="1:1">
       <c r="A135" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="136" spans="1:1">
       <c r="A136" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="141" spans="1:1">
       <c r="A141" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="142" spans="1:1">
       <c r="A142" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="145" spans="1:1">
       <c r="A145" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="148" spans="1:1">
       <c r="A148" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="149" spans="1:1">
       <c r="A149" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="151" spans="1:1">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="152" spans="1:1">
       <c r="A152" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="155" spans="1:1">
       <c r="A155" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="163" spans="1:1">
       <c r="A163" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="164" spans="1:1">
       <c r="A164" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="173" spans="1:1">
@@ -8912,42 +8920,42 @@
     </row>
     <row r="175" spans="1:1">
       <c r="A175" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="176" spans="1:1">
       <c r="A176" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="177" spans="1:1">
       <c r="A177" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="180" spans="1:1">
       <c r="A180" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:1">
       <c r="A181" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="183" spans="1:1">
       <c r="A183" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="184" spans="1:1">
@@ -8957,32 +8965,32 @@
     </row>
     <row r="186" spans="1:1">
       <c r="A186" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="188" spans="1:1">
       <c r="A188" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -8997,7 +9005,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:1">
